--- a/pages/video_analysis/TP_Master_Men.xlsx
+++ b/pages/video_analysis/TP_Master_Men.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43217025-DABF-4C90-9EAB-38AA68DEF7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABE7091-E2DC-4C89-A569-B97574EB6B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="24">
   <si>
     <t>Title</t>
   </si>
@@ -77,6 +77,21 @@
   </si>
   <si>
     <t>Aussie 4</t>
+  </si>
+  <si>
+    <t>Kyle</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Nick</t>
+  </si>
+  <si>
+    <t>Sam</t>
+  </si>
+  <si>
+    <t>Juniors WCH</t>
   </si>
 </sst>
 </file>
@@ -482,20 +497,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2385,6 +2388,1862 @@
         <v>17</v>
       </c>
     </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>23</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C66">
+        <v>62.5</v>
+      </c>
+      <c r="D66">
+        <v>8.32</v>
+      </c>
+      <c r="E66">
+        <v>8.32</v>
+      </c>
+      <c r="F66">
+        <v>27.04326923076923</v>
+      </c>
+      <c r="G66">
+        <v>27.04326923076923</v>
+      </c>
+      <c r="H66" t="s">
+        <v>11</v>
+      </c>
+      <c r="I66" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>23</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C67">
+        <v>125</v>
+      </c>
+      <c r="D67">
+        <v>13.2</v>
+      </c>
+      <c r="E67">
+        <v>4.8799999999999946</v>
+      </c>
+      <c r="F67">
+        <v>46.106557377049221</v>
+      </c>
+      <c r="G67">
+        <v>46.106557377049221</v>
+      </c>
+      <c r="H67" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C68">
+        <v>187.5</v>
+      </c>
+      <c r="D68">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="E68">
+        <v>4.0400000000000063</v>
+      </c>
+      <c r="F68">
+        <v>55.69306930693061</v>
+      </c>
+      <c r="G68">
+        <v>55.69306930693061</v>
+      </c>
+      <c r="H68" t="s">
+        <v>11</v>
+      </c>
+      <c r="I68" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C69">
+        <v>250</v>
+      </c>
+      <c r="D69">
+        <v>21.28</v>
+      </c>
+      <c r="E69">
+        <v>4.0399999999999991</v>
+      </c>
+      <c r="F69">
+        <v>55.693069306930703</v>
+      </c>
+      <c r="G69">
+        <v>55.693069306930703</v>
+      </c>
+      <c r="H69" t="s">
+        <v>11</v>
+      </c>
+      <c r="I69" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C70">
+        <v>312.5</v>
+      </c>
+      <c r="D70">
+        <v>25.03</v>
+      </c>
+      <c r="E70">
+        <v>3.75</v>
+      </c>
+      <c r="F70">
+        <v>60</v>
+      </c>
+      <c r="G70">
+        <v>60</v>
+      </c>
+      <c r="H70" t="s">
+        <v>11</v>
+      </c>
+      <c r="I70" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C71">
+        <v>375</v>
+      </c>
+      <c r="D71">
+        <v>28.53</v>
+      </c>
+      <c r="E71">
+        <v>3.5</v>
+      </c>
+      <c r="F71">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G71">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H71" t="s">
+        <v>11</v>
+      </c>
+      <c r="I71" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>23</v>
+      </c>
+      <c r="B72" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C72">
+        <v>437.5</v>
+      </c>
+      <c r="D72">
+        <v>32.319999999999993</v>
+      </c>
+      <c r="E72">
+        <v>3.789999999999992</v>
+      </c>
+      <c r="F72">
+        <v>63.2</v>
+      </c>
+      <c r="G72">
+        <v>59.366754617414372</v>
+      </c>
+      <c r="H72" t="s">
+        <v>12</v>
+      </c>
+      <c r="I72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C73">
+        <v>500</v>
+      </c>
+      <c r="D73">
+        <v>35.86</v>
+      </c>
+      <c r="E73">
+        <v>3.5400000000000058</v>
+      </c>
+      <c r="F73">
+        <v>63.559322033898191</v>
+      </c>
+      <c r="G73">
+        <v>63.559322033898191</v>
+      </c>
+      <c r="H73" t="s">
+        <v>11</v>
+      </c>
+      <c r="I73" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C74">
+        <v>562.5</v>
+      </c>
+      <c r="D74">
+        <v>39.61</v>
+      </c>
+      <c r="E74">
+        <v>3.75</v>
+      </c>
+      <c r="F74">
+        <v>60</v>
+      </c>
+      <c r="G74">
+        <v>60</v>
+      </c>
+      <c r="H74" t="s">
+        <v>11</v>
+      </c>
+      <c r="I74" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C75">
+        <v>625</v>
+      </c>
+      <c r="D75">
+        <v>43.61</v>
+      </c>
+      <c r="E75">
+        <v>4</v>
+      </c>
+      <c r="F75">
+        <v>56.25</v>
+      </c>
+      <c r="G75">
+        <v>56.25</v>
+      </c>
+      <c r="H75" t="s">
+        <v>11</v>
+      </c>
+      <c r="I75" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>23</v>
+      </c>
+      <c r="B76" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C76">
+        <v>687.5</v>
+      </c>
+      <c r="D76">
+        <v>47.39</v>
+      </c>
+      <c r="E76">
+        <v>3.7800000000000011</v>
+      </c>
+      <c r="F76">
+        <v>59.523809523809497</v>
+      </c>
+      <c r="G76">
+        <v>59.523809523809497</v>
+      </c>
+      <c r="H76" t="s">
+        <v>11</v>
+      </c>
+      <c r="I76" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>23</v>
+      </c>
+      <c r="B77" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C77">
+        <v>750</v>
+      </c>
+      <c r="D77">
+        <v>51.39</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>56.25</v>
+      </c>
+      <c r="G77">
+        <v>56.25</v>
+      </c>
+      <c r="H77" t="s">
+        <v>11</v>
+      </c>
+      <c r="I77" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C78">
+        <v>812.5</v>
+      </c>
+      <c r="D78">
+        <v>55.14</v>
+      </c>
+      <c r="E78">
+        <v>3.75</v>
+      </c>
+      <c r="F78">
+        <v>63.92</v>
+      </c>
+      <c r="G78">
+        <v>60</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>23</v>
+      </c>
+      <c r="B79" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C79">
+        <v>875</v>
+      </c>
+      <c r="D79">
+        <v>59.14</v>
+      </c>
+      <c r="E79">
+        <v>4</v>
+      </c>
+      <c r="F79">
+        <v>56.25</v>
+      </c>
+      <c r="G79">
+        <v>56.25</v>
+      </c>
+      <c r="H79" t="s">
+        <v>11</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>23</v>
+      </c>
+      <c r="B80" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C80">
+        <v>937.5</v>
+      </c>
+      <c r="D80">
+        <v>62.64</v>
+      </c>
+      <c r="E80">
+        <v>3.5</v>
+      </c>
+      <c r="F80">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G80">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H80" t="s">
+        <v>11</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>23</v>
+      </c>
+      <c r="B81" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C81">
+        <v>1000</v>
+      </c>
+      <c r="D81">
+        <v>66.39</v>
+      </c>
+      <c r="E81">
+        <v>3.75</v>
+      </c>
+      <c r="F81">
+        <v>60</v>
+      </c>
+      <c r="G81">
+        <v>60</v>
+      </c>
+      <c r="H81" t="s">
+        <v>11</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>23</v>
+      </c>
+      <c r="B82" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C82">
+        <v>1062.5</v>
+      </c>
+      <c r="D82">
+        <v>70.64</v>
+      </c>
+      <c r="E82">
+        <v>4.25</v>
+      </c>
+      <c r="F82">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="G82">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H82" t="s">
+        <v>11</v>
+      </c>
+      <c r="I82" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C83">
+        <v>1125</v>
+      </c>
+      <c r="D83">
+        <v>74.39</v>
+      </c>
+      <c r="E83">
+        <v>3.75</v>
+      </c>
+      <c r="F83">
+        <v>60</v>
+      </c>
+      <c r="G83">
+        <v>60</v>
+      </c>
+      <c r="H83" t="s">
+        <v>11</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>23</v>
+      </c>
+      <c r="B84" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C84">
+        <v>1187.5</v>
+      </c>
+      <c r="D84">
+        <v>78.14</v>
+      </c>
+      <c r="E84">
+        <v>3.75</v>
+      </c>
+      <c r="F84">
+        <v>60</v>
+      </c>
+      <c r="G84">
+        <v>60</v>
+      </c>
+      <c r="H84" t="s">
+        <v>11</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>23</v>
+      </c>
+      <c r="B85" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C85">
+        <v>1250</v>
+      </c>
+      <c r="D85">
+        <v>81.14</v>
+      </c>
+      <c r="E85">
+        <v>3</v>
+      </c>
+      <c r="F85">
+        <v>75</v>
+      </c>
+      <c r="G85">
+        <v>75</v>
+      </c>
+      <c r="H85" t="s">
+        <v>11</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>23</v>
+      </c>
+      <c r="B86" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C86">
+        <v>1312.5</v>
+      </c>
+      <c r="D86">
+        <v>85.64</v>
+      </c>
+      <c r="E86">
+        <v>4.5</v>
+      </c>
+      <c r="F86">
+        <v>52.69</v>
+      </c>
+      <c r="G86">
+        <v>50</v>
+      </c>
+      <c r="H86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>23</v>
+      </c>
+      <c r="B87" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C87">
+        <v>1375</v>
+      </c>
+      <c r="D87">
+        <v>89.39</v>
+      </c>
+      <c r="E87">
+        <v>3.75</v>
+      </c>
+      <c r="F87">
+        <v>60</v>
+      </c>
+      <c r="G87">
+        <v>60</v>
+      </c>
+      <c r="H87" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>23</v>
+      </c>
+      <c r="B88" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C88">
+        <v>1437.5</v>
+      </c>
+      <c r="D88">
+        <v>92.89</v>
+      </c>
+      <c r="E88">
+        <v>3.5</v>
+      </c>
+      <c r="F88">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G88">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H88" t="s">
+        <v>11</v>
+      </c>
+      <c r="I88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C89">
+        <v>1500</v>
+      </c>
+      <c r="D89">
+        <v>96.719999999999985</v>
+      </c>
+      <c r="E89">
+        <v>3.8299999999999841</v>
+      </c>
+      <c r="F89">
+        <v>58.746736292428437</v>
+      </c>
+      <c r="G89">
+        <v>58.746736292428437</v>
+      </c>
+      <c r="H89" t="s">
+        <v>11</v>
+      </c>
+      <c r="I89" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C90">
+        <v>1562.5</v>
+      </c>
+      <c r="D90">
+        <v>100.97</v>
+      </c>
+      <c r="E90">
+        <v>4.25</v>
+      </c>
+      <c r="F90">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="G90">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H90" t="s">
+        <v>11</v>
+      </c>
+      <c r="I90" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>23</v>
+      </c>
+      <c r="B91" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C91">
+        <v>1625</v>
+      </c>
+      <c r="D91">
+        <v>104.76</v>
+      </c>
+      <c r="E91">
+        <v>3.79000000000002</v>
+      </c>
+      <c r="F91">
+        <v>59.366754617413918</v>
+      </c>
+      <c r="G91">
+        <v>59.366754617413918</v>
+      </c>
+      <c r="H91" t="s">
+        <v>11</v>
+      </c>
+      <c r="I91" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>23</v>
+      </c>
+      <c r="B92" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C92">
+        <v>1687.5</v>
+      </c>
+      <c r="D92">
+        <v>108.26</v>
+      </c>
+      <c r="E92">
+        <v>3.5</v>
+      </c>
+      <c r="F92">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G92">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H92" t="s">
+        <v>11</v>
+      </c>
+      <c r="I92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>23</v>
+      </c>
+      <c r="B93" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C93">
+        <v>1750</v>
+      </c>
+      <c r="D93">
+        <v>111.76</v>
+      </c>
+      <c r="E93">
+        <v>3.5</v>
+      </c>
+      <c r="F93">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G93">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H93" t="s">
+        <v>11</v>
+      </c>
+      <c r="I93" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>23</v>
+      </c>
+      <c r="B94" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C94">
+        <v>1812.5</v>
+      </c>
+      <c r="D94">
+        <v>115.76</v>
+      </c>
+      <c r="E94">
+        <v>4</v>
+      </c>
+      <c r="F94">
+        <v>59.68</v>
+      </c>
+      <c r="G94">
+        <v>56.25</v>
+      </c>
+      <c r="H94" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>23</v>
+      </c>
+      <c r="B95" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C95">
+        <v>1875</v>
+      </c>
+      <c r="D95">
+        <v>120.26</v>
+      </c>
+      <c r="E95">
+        <v>4.5</v>
+      </c>
+      <c r="F95">
+        <v>50</v>
+      </c>
+      <c r="G95">
+        <v>50</v>
+      </c>
+      <c r="H95" t="s">
+        <v>11</v>
+      </c>
+      <c r="I95" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>23</v>
+      </c>
+      <c r="B96" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C96">
+        <v>1937.5</v>
+      </c>
+      <c r="D96">
+        <v>123.26</v>
+      </c>
+      <c r="E96">
+        <v>3</v>
+      </c>
+      <c r="F96">
+        <v>75</v>
+      </c>
+      <c r="G96">
+        <v>75</v>
+      </c>
+      <c r="H96" t="s">
+        <v>11</v>
+      </c>
+      <c r="I96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>23</v>
+      </c>
+      <c r="B97" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C97">
+        <v>2000</v>
+      </c>
+      <c r="D97">
+        <v>127.01</v>
+      </c>
+      <c r="E97">
+        <v>3.75</v>
+      </c>
+      <c r="F97">
+        <v>60</v>
+      </c>
+      <c r="G97">
+        <v>60</v>
+      </c>
+      <c r="H97" t="s">
+        <v>11</v>
+      </c>
+      <c r="I97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>23</v>
+      </c>
+      <c r="B98" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C98">
+        <v>2062.5</v>
+      </c>
+      <c r="D98">
+        <v>130.76</v>
+      </c>
+      <c r="E98">
+        <v>3.7499999999999858</v>
+      </c>
+      <c r="F98">
+        <v>60.000000000000227</v>
+      </c>
+      <c r="G98">
+        <v>60.000000000000227</v>
+      </c>
+      <c r="H98" t="s">
+        <v>11</v>
+      </c>
+      <c r="I98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>23</v>
+      </c>
+      <c r="B99" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C99">
+        <v>2125</v>
+      </c>
+      <c r="D99">
+        <v>135.01</v>
+      </c>
+      <c r="E99">
+        <v>4.25</v>
+      </c>
+      <c r="F99">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="G99">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H99" t="s">
+        <v>11</v>
+      </c>
+      <c r="I99" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>23</v>
+      </c>
+      <c r="B100" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C100">
+        <v>2187.5</v>
+      </c>
+      <c r="D100">
+        <v>138.26</v>
+      </c>
+      <c r="E100">
+        <v>3.25</v>
+      </c>
+      <c r="F100">
+        <v>69.230769230769226</v>
+      </c>
+      <c r="G100">
+        <v>69.230769230769226</v>
+      </c>
+      <c r="H100" t="s">
+        <v>11</v>
+      </c>
+      <c r="I100" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C101">
+        <v>2250</v>
+      </c>
+      <c r="D101">
+        <v>141.51</v>
+      </c>
+      <c r="E101">
+        <v>3.25</v>
+      </c>
+      <c r="F101">
+        <v>69.230769230769226</v>
+      </c>
+      <c r="G101">
+        <v>69.230769230769226</v>
+      </c>
+      <c r="H101" t="s">
+        <v>11</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C102">
+        <v>2312.5</v>
+      </c>
+      <c r="D102">
+        <v>145.76</v>
+      </c>
+      <c r="E102">
+        <v>4.25</v>
+      </c>
+      <c r="F102">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="G102">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H102" t="s">
+        <v>11</v>
+      </c>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C103">
+        <v>2375</v>
+      </c>
+      <c r="D103">
+        <v>149.51</v>
+      </c>
+      <c r="E103">
+        <v>3.75</v>
+      </c>
+      <c r="F103">
+        <v>60</v>
+      </c>
+      <c r="G103">
+        <v>60</v>
+      </c>
+      <c r="H103" t="s">
+        <v>11</v>
+      </c>
+      <c r="I103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>23</v>
+      </c>
+      <c r="B104" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C104">
+        <v>2437.5</v>
+      </c>
+      <c r="D104">
+        <v>153.01</v>
+      </c>
+      <c r="E104">
+        <v>3.5</v>
+      </c>
+      <c r="F104">
+        <v>68.81</v>
+      </c>
+      <c r="G104">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H104" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C105">
+        <v>2500</v>
+      </c>
+      <c r="D105">
+        <v>156.51</v>
+      </c>
+      <c r="E105">
+        <v>3.5</v>
+      </c>
+      <c r="F105">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G105">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H105" t="s">
+        <v>11</v>
+      </c>
+      <c r="I105" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C106">
+        <v>2562.5</v>
+      </c>
+      <c r="D106">
+        <v>160.80000000000001</v>
+      </c>
+      <c r="E106">
+        <v>4.2900000000000196</v>
+      </c>
+      <c r="F106">
+        <v>52.447552447552198</v>
+      </c>
+      <c r="G106">
+        <v>52.447552447552198</v>
+      </c>
+      <c r="H106" t="s">
+        <v>11</v>
+      </c>
+      <c r="I106" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>23</v>
+      </c>
+      <c r="B107" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C107">
+        <v>2625</v>
+      </c>
+      <c r="D107">
+        <v>165.05</v>
+      </c>
+      <c r="E107">
+        <v>4.25</v>
+      </c>
+      <c r="F107">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="G107">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H107" t="s">
+        <v>11</v>
+      </c>
+      <c r="I107" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>23</v>
+      </c>
+      <c r="B108" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C108">
+        <v>2687.5</v>
+      </c>
+      <c r="D108">
+        <v>168.8</v>
+      </c>
+      <c r="E108">
+        <v>3.75</v>
+      </c>
+      <c r="F108">
+        <v>60</v>
+      </c>
+      <c r="G108">
+        <v>60</v>
+      </c>
+      <c r="H108" t="s">
+        <v>11</v>
+      </c>
+      <c r="I108" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>23</v>
+      </c>
+      <c r="B109" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C109">
+        <v>2750</v>
+      </c>
+      <c r="D109">
+        <v>172.3</v>
+      </c>
+      <c r="E109">
+        <v>3.5</v>
+      </c>
+      <c r="F109">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G109">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H109" t="s">
+        <v>11</v>
+      </c>
+      <c r="I109" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>23</v>
+      </c>
+      <c r="B110" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C110">
+        <v>2812.5</v>
+      </c>
+      <c r="D110">
+        <v>176.56</v>
+      </c>
+      <c r="E110">
+        <v>4.2599999999999909</v>
+      </c>
+      <c r="F110">
+        <v>55.83</v>
+      </c>
+      <c r="G110">
+        <v>52.816901408450818</v>
+      </c>
+      <c r="H110" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>23</v>
+      </c>
+      <c r="B111" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C111">
+        <v>2875</v>
+      </c>
+      <c r="D111">
+        <v>180.56</v>
+      </c>
+      <c r="E111">
+        <v>4</v>
+      </c>
+      <c r="F111">
+        <v>56.25</v>
+      </c>
+      <c r="G111">
+        <v>56.25</v>
+      </c>
+      <c r="H111" t="s">
+        <v>11</v>
+      </c>
+      <c r="I111" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>23</v>
+      </c>
+      <c r="B112" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C112">
+        <v>2937.5</v>
+      </c>
+      <c r="D112">
+        <v>184.31</v>
+      </c>
+      <c r="E112">
+        <v>3.75</v>
+      </c>
+      <c r="F112">
+        <v>60</v>
+      </c>
+      <c r="G112">
+        <v>60</v>
+      </c>
+      <c r="H112" t="s">
+        <v>11</v>
+      </c>
+      <c r="I112" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C113">
+        <v>3000</v>
+      </c>
+      <c r="D113">
+        <v>187.81</v>
+      </c>
+      <c r="E113">
+        <v>3.5</v>
+      </c>
+      <c r="F113">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G113">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H113" t="s">
+        <v>11</v>
+      </c>
+      <c r="I113" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>23</v>
+      </c>
+      <c r="B114" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C114">
+        <v>3062.5</v>
+      </c>
+      <c r="D114">
+        <v>192.06</v>
+      </c>
+      <c r="E114">
+        <v>4.25</v>
+      </c>
+      <c r="F114">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="G114">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H114" t="s">
+        <v>11</v>
+      </c>
+      <c r="I114" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C115">
+        <v>3125</v>
+      </c>
+      <c r="D115">
+        <v>196.31</v>
+      </c>
+      <c r="E115">
+        <v>4.25</v>
+      </c>
+      <c r="F115">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="G115">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H115" t="s">
+        <v>11</v>
+      </c>
+      <c r="I115" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>23</v>
+      </c>
+      <c r="B116" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C116">
+        <v>3187.5</v>
+      </c>
+      <c r="D116">
+        <v>199.56</v>
+      </c>
+      <c r="E116">
+        <v>3.25</v>
+      </c>
+      <c r="F116">
+        <v>69.230769230769226</v>
+      </c>
+      <c r="G116">
+        <v>69.230769230769226</v>
+      </c>
+      <c r="H116" t="s">
+        <v>11</v>
+      </c>
+      <c r="I116" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>23</v>
+      </c>
+      <c r="B117" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C117">
+        <v>3250</v>
+      </c>
+      <c r="D117">
+        <v>203.68</v>
+      </c>
+      <c r="E117">
+        <v>4.1200000000000054</v>
+      </c>
+      <c r="F117">
+        <v>54.611650485436833</v>
+      </c>
+      <c r="G117">
+        <v>54.611650485436833</v>
+      </c>
+      <c r="H117" t="s">
+        <v>11</v>
+      </c>
+      <c r="I117" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>23</v>
+      </c>
+      <c r="B118" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C118">
+        <v>3312.5</v>
+      </c>
+      <c r="D118">
+        <v>207.93</v>
+      </c>
+      <c r="E118">
+        <v>4.25</v>
+      </c>
+      <c r="F118">
+        <v>55.97</v>
+      </c>
+      <c r="G118">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H118" t="s">
+        <v>12</v>
+      </c>
+      <c r="I118" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>23</v>
+      </c>
+      <c r="B119" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C119">
+        <v>3375</v>
+      </c>
+      <c r="D119">
+        <v>211.68</v>
+      </c>
+      <c r="E119">
+        <v>3.75</v>
+      </c>
+      <c r="F119">
+        <v>60</v>
+      </c>
+      <c r="G119">
+        <v>60</v>
+      </c>
+      <c r="H119" t="s">
+        <v>11</v>
+      </c>
+      <c r="I119" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>23</v>
+      </c>
+      <c r="B120" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C120">
+        <v>3437.5</v>
+      </c>
+      <c r="D120">
+        <v>215.43</v>
+      </c>
+      <c r="E120">
+        <v>3.75</v>
+      </c>
+      <c r="F120">
+        <v>60</v>
+      </c>
+      <c r="G120">
+        <v>60</v>
+      </c>
+      <c r="H120" t="s">
+        <v>11</v>
+      </c>
+      <c r="I120" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>23</v>
+      </c>
+      <c r="B121" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C121">
+        <v>3500</v>
+      </c>
+      <c r="D121">
+        <v>219.36</v>
+      </c>
+      <c r="E121">
+        <v>3.9300000000000068</v>
+      </c>
+      <c r="F121">
+        <v>57.251908396946469</v>
+      </c>
+      <c r="G121">
+        <v>57.251908396946469</v>
+      </c>
+      <c r="H121" t="s">
+        <v>11</v>
+      </c>
+      <c r="I121" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>23</v>
+      </c>
+      <c r="B122" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C122">
+        <v>3562.5</v>
+      </c>
+      <c r="D122">
+        <v>223.44</v>
+      </c>
+      <c r="E122">
+        <v>4.0799999999999841</v>
+      </c>
+      <c r="F122">
+        <v>58.44</v>
+      </c>
+      <c r="G122">
+        <v>55.147058823529633</v>
+      </c>
+      <c r="H122" t="s">
+        <v>12</v>
+      </c>
+      <c r="I122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>23</v>
+      </c>
+      <c r="B123" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C123">
+        <v>3625</v>
+      </c>
+      <c r="D123">
+        <v>227.68899999999999</v>
+      </c>
+      <c r="E123">
+        <v>4.2490000000000236</v>
+      </c>
+      <c r="F123">
+        <v>52.953636149681977</v>
+      </c>
+      <c r="G123">
+        <v>52.953636149681977</v>
+      </c>
+      <c r="H123" t="s">
+        <v>11</v>
+      </c>
+      <c r="I123" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>23</v>
+      </c>
+      <c r="B124" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C124">
+        <v>3687.5</v>
+      </c>
+      <c r="D124">
+        <v>231.43899999999999</v>
+      </c>
+      <c r="E124">
+        <v>3.75</v>
+      </c>
+      <c r="F124">
+        <v>60</v>
+      </c>
+      <c r="G124">
+        <v>60</v>
+      </c>
+      <c r="H124" t="s">
+        <v>11</v>
+      </c>
+      <c r="I124" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>23</v>
+      </c>
+      <c r="B125" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C125">
+        <v>3750</v>
+      </c>
+      <c r="D125">
+        <v>235.93899999999999</v>
+      </c>
+      <c r="E125">
+        <v>4.5</v>
+      </c>
+      <c r="F125">
+        <v>50</v>
+      </c>
+      <c r="G125">
+        <v>50</v>
+      </c>
+      <c r="H125" t="s">
+        <v>11</v>
+      </c>
+      <c r="I125" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>23</v>
+      </c>
+      <c r="B126" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C126">
+        <v>3812.5</v>
+      </c>
+      <c r="D126">
+        <v>239.52</v>
+      </c>
+      <c r="E126">
+        <v>3.5810000000000168</v>
+      </c>
+      <c r="F126">
+        <v>62.831611281764573</v>
+      </c>
+      <c r="G126">
+        <v>62.831611281764573</v>
+      </c>
+      <c r="H126" t="s">
+        <v>11</v>
+      </c>
+      <c r="I126" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>23</v>
+      </c>
+      <c r="B127" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C127">
+        <v>3875</v>
+      </c>
+      <c r="D127">
+        <v>243.77</v>
+      </c>
+      <c r="E127">
+        <v>4.25</v>
+      </c>
+      <c r="F127">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="G127">
+        <v>52.941176470588232</v>
+      </c>
+      <c r="H127" t="s">
+        <v>11</v>
+      </c>
+      <c r="I127" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>23</v>
+      </c>
+      <c r="B128" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C128">
+        <v>3937.5</v>
+      </c>
+      <c r="D128">
+        <v>247.6</v>
+      </c>
+      <c r="E128">
+        <v>3.8299999999999841</v>
+      </c>
+      <c r="F128">
+        <v>58.746736292428437</v>
+      </c>
+      <c r="G128">
+        <v>58.746736292428437</v>
+      </c>
+      <c r="H128" t="s">
+        <v>11</v>
+      </c>
+      <c r="I128" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>23</v>
+      </c>
+      <c r="B129" s="2">
+        <v>45119</v>
+      </c>
+      <c r="C129">
+        <v>4000</v>
+      </c>
+      <c r="D129">
+        <v>252.04</v>
+      </c>
+      <c r="E129">
+        <v>4.4399999999999977</v>
+      </c>
+      <c r="F129">
+        <v>50.675675675675699</v>
+      </c>
+      <c r="G129">
+        <v>50.675675675675699</v>
+      </c>
+      <c r="H129" t="s">
+        <v>11</v>
+      </c>
+      <c r="I129" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/video_analysis/TP_Master_Men.xlsx
+++ b/pages/video_analysis/TP_Master_Men.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABE7091-E2DC-4C89-A569-B97574EB6B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E01290-B010-4C93-8D6A-E84FD4592D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="9072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="25">
   <si>
     <t>Title</t>
   </si>
@@ -52,7 +52,10 @@
     <t>Video</t>
   </si>
   <si>
-    <t>Australia Milton Q</t>
+    <t>19/7/2023 Flying 3k Rep 3</t>
+  </si>
+  <si>
+    <t>19/7/2023 Flying 3k Rep 4</t>
   </si>
   <si>
     <t>No Change</t>
@@ -61,37 +64,37 @@
     <t>Change</t>
   </si>
   <si>
-    <t>Drop</t>
+    <t>Nick Kergozou</t>
   </si>
   <si>
-    <t>Start/Finish</t>
+    <t>Campbell Stewart</t>
   </si>
   <si>
-    <t>Aussie 1</t>
+    <t>Tom Sexton</t>
   </si>
   <si>
-    <t>Aussie 2</t>
+    <t>Keegan Hornblow</t>
   </si>
   <si>
-    <t>Aussie 3</t>
+    <t>George Jackson</t>
   </si>
   <si>
-    <t>Aussie 4</t>
+    <t>https://youtu.be/QCPBGRnF4sY</t>
   </si>
   <si>
-    <t>Kyle</t>
+    <t>19/7/2023 Flying 3k Rep 1</t>
   </si>
   <si>
-    <t>John</t>
+    <t>19/7/2023 Flying 3k Rep 2</t>
   </si>
   <si>
-    <t>Nick</t>
+    <t>https://youtu.be/2irZxikfi88</t>
   </si>
   <si>
-    <t>Sam</t>
+    <t>https://youtu.be/Ih39EPkj1jQ</t>
   </si>
   <si>
-    <t>Juniors WCH</t>
+    <t>https://youtu.be/fue24y7g8MI</t>
   </si>
 </sst>
 </file>
@@ -101,7 +104,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,6 +116,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -497,8 +506,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:S189"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -534,202 +554,205 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C2">
         <v>62.5</v>
       </c>
       <c r="D2">
-        <v>8.240000000000002</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="E2">
-        <v>8.24</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F2">
-        <v>27.31</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G2">
-        <v>27.31</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C3">
         <v>125</v>
       </c>
       <c r="D3">
-        <v>13.04</v>
+        <v>7.3999999999999773</v>
       </c>
       <c r="E3">
-        <v>4.8</v>
+        <v>3.6999999999999318</v>
       </c>
       <c r="F3">
-        <v>46.88</v>
+        <v>60.81081081081193</v>
       </c>
       <c r="G3">
-        <v>46.88</v>
+        <v>60.81081081081193</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C4">
         <v>187.5</v>
       </c>
       <c r="D4">
-        <v>16.96</v>
+        <v>11.12</v>
       </c>
       <c r="E4">
-        <v>3.92</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F4">
-        <v>57.4</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G4">
-        <v>57.4</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C5">
         <v>250</v>
       </c>
       <c r="D5">
-        <v>20.7</v>
+        <v>14.899999999999981</v>
       </c>
       <c r="E5">
-        <v>3.74</v>
+        <v>3.7799999999999732</v>
       </c>
       <c r="F5">
-        <v>60.16</v>
+        <v>59.523809523809952</v>
       </c>
       <c r="G5">
-        <v>60.16</v>
+        <v>59.523809523809952</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C6">
         <v>312.5</v>
       </c>
       <c r="D6">
-        <v>24.16</v>
+        <v>18.63999999999999</v>
       </c>
       <c r="E6">
-        <v>3.46</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F6">
-        <v>65.03</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G6">
-        <v>65.03</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C7">
         <v>375</v>
       </c>
       <c r="D7">
-        <v>27.84</v>
+        <v>22.540000000000081</v>
       </c>
       <c r="E7">
-        <v>3.68</v>
+        <v>3.9000000000000909</v>
       </c>
       <c r="F7">
-        <v>61.14</v>
+        <v>59.52</v>
       </c>
       <c r="G7">
-        <v>61.14</v>
+        <v>57.692307692306343</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C8">
         <v>437.5</v>
       </c>
       <c r="D8">
-        <v>31.32</v>
+        <v>26.300000000000072</v>
       </c>
       <c r="E8">
-        <v>3.48</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F8">
-        <v>64.66</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="G8">
-        <v>64.66</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
         <v>15</v>
@@ -737,28 +760,28 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C9">
         <v>500</v>
       </c>
       <c r="D9">
-        <v>34.82</v>
+        <v>30.100000000000019</v>
       </c>
       <c r="E9">
-        <v>3.5</v>
+        <v>3.799999999999955</v>
       </c>
       <c r="F9">
-        <v>64.290000000000006</v>
+        <v>59.210526315790183</v>
       </c>
       <c r="G9">
-        <v>64.290000000000006</v>
+        <v>59.210526315790183</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
         <v>15</v>
@@ -766,28 +789,28 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C10">
         <v>562.5</v>
       </c>
       <c r="D10">
-        <v>38.159999999999997</v>
+        <v>33.860000000000007</v>
       </c>
       <c r="E10">
-        <v>3.34</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F10">
-        <v>67.37</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="G10">
-        <v>67.37</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
@@ -795,28 +818,28 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C11">
         <v>625</v>
       </c>
       <c r="D11">
-        <v>41.720000000000013</v>
+        <v>37.619999999999997</v>
       </c>
       <c r="E11">
-        <v>3.56</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F11">
-        <v>63.2</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="G11">
-        <v>63.2</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
         <v>15</v>
@@ -824,25 +847,25 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C12">
         <v>687.5</v>
       </c>
       <c r="D12">
-        <v>45.24</v>
+        <v>41.380000300000013</v>
       </c>
       <c r="E12">
-        <v>3.52</v>
+        <v>3.760000300000002</v>
       </c>
       <c r="F12">
-        <v>65.41</v>
+        <v>59.840420757413213</v>
       </c>
       <c r="G12">
-        <v>63.92</v>
+        <v>59.840420757413213</v>
       </c>
       <c r="H12" t="s">
         <v>12</v>
@@ -853,57 +876,57 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C13">
         <v>750</v>
       </c>
       <c r="D13">
-        <v>48.68</v>
+        <v>45.260000300000002</v>
       </c>
       <c r="E13">
-        <v>3.44</v>
+        <v>3.879999999999995</v>
       </c>
       <c r="F13">
-        <v>65.41</v>
+        <v>59.84</v>
       </c>
       <c r="G13">
-        <v>65.41</v>
+        <v>57.989690721649552</v>
       </c>
       <c r="H13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C14">
         <v>812.5</v>
       </c>
       <c r="D14">
-        <v>51.98</v>
+        <v>49.020000299999992</v>
       </c>
       <c r="E14">
-        <v>3.3</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F14">
-        <v>68.180000000000007</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="G14">
-        <v>68.180000000000007</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I14" t="s">
         <v>16</v>
@@ -911,28 +934,28 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C15">
         <v>875</v>
       </c>
       <c r="D15">
-        <v>55.580000000000013</v>
+        <v>52.74000030000002</v>
       </c>
       <c r="E15">
-        <v>3.6</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F15">
-        <v>62.5</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G15">
-        <v>62.5</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I15" t="s">
         <v>16</v>
@@ -940,28 +963,28 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B16" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C16">
         <v>937.5</v>
       </c>
       <c r="D16">
-        <v>59.02</v>
+        <v>56.480000300000029</v>
       </c>
       <c r="E16">
-        <v>3.44</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F16">
-        <v>65.41</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G16">
-        <v>65.41</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16" t="s">
         <v>16</v>
@@ -969,28 +992,28 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B17" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C17">
         <v>1000</v>
       </c>
       <c r="D17">
-        <v>62.52</v>
+        <v>60.24000030000002</v>
       </c>
       <c r="E17">
-        <v>3.5</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F17">
-        <v>64.290000000000006</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="G17">
-        <v>64.290000000000006</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I17" t="s">
         <v>16</v>
@@ -998,28 +1021,28 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C18">
         <v>1062.5</v>
       </c>
       <c r="D18">
-        <v>65.88</v>
+        <v>63.960000300000047</v>
       </c>
       <c r="E18">
-        <v>3.36</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F18">
-        <v>66.959999999999994</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G18">
-        <v>66.959999999999994</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" t="s">
         <v>16</v>
@@ -1027,28 +1050,28 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C19">
         <v>1125</v>
       </c>
       <c r="D19">
-        <v>69.52000000000001</v>
+        <v>67.820000299999947</v>
       </c>
       <c r="E19">
-        <v>3.64</v>
+        <v>3.8599999999999</v>
       </c>
       <c r="F19">
-        <v>61.81</v>
+        <v>60.16</v>
       </c>
       <c r="G19">
-        <v>61.81</v>
+        <v>58.290155440416022</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I19" t="s">
         <v>16</v>
@@ -1056,1304 +1079,1307 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C20">
         <v>1187.5</v>
       </c>
       <c r="D20">
-        <v>73.099999999999994</v>
+        <v>71.700000300000056</v>
       </c>
       <c r="E20">
-        <v>3.58</v>
+        <v>3.8800000000001091</v>
       </c>
       <c r="F20">
-        <v>62.85</v>
+        <v>57.989690721647847</v>
       </c>
       <c r="G20">
-        <v>62.85</v>
+        <v>57.989690721647847</v>
       </c>
       <c r="H20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C21">
         <v>1250</v>
       </c>
       <c r="D21">
-        <v>76.599999999999994</v>
+        <v>75.320000299999947</v>
       </c>
       <c r="E21">
-        <v>3.5</v>
+        <v>3.6199999999998909</v>
       </c>
       <c r="F21">
-        <v>64.290000000000006</v>
+        <v>62.154696132598559</v>
       </c>
       <c r="G21">
-        <v>64.290000000000006</v>
+        <v>62.154696132598559</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C22">
         <v>1312.5</v>
       </c>
       <c r="D22">
-        <v>79.960000000000008</v>
+        <v>79.080000299999938</v>
       </c>
       <c r="E22">
-        <v>3.36</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F22">
-        <v>66.959999999999994</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="G22">
-        <v>66.959999999999994</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C23">
         <v>1375</v>
       </c>
       <c r="D23">
-        <v>83.580000000000013</v>
+        <v>82.820000299999947</v>
       </c>
       <c r="E23">
-        <v>3.62</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F23">
-        <v>62.15</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G23">
-        <v>62.15</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C24">
         <v>1437.5</v>
       </c>
       <c r="D24">
-        <v>87.06</v>
+        <v>86.480000300000029</v>
       </c>
       <c r="E24">
-        <v>3.48</v>
+        <v>3.6600000000000819</v>
       </c>
       <c r="F24">
-        <v>64.66</v>
+        <v>61.475409836064202</v>
       </c>
       <c r="G24">
-        <v>64.66</v>
+        <v>61.475409836064202</v>
       </c>
       <c r="H24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B25" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C25">
         <v>1500</v>
       </c>
       <c r="D25">
-        <v>90.52000000000001</v>
+        <v>90.400000300000102</v>
       </c>
       <c r="E25">
-        <v>3.46</v>
+        <v>3.9200000000000732</v>
       </c>
       <c r="F25">
-        <v>65.03</v>
+        <v>59.21</v>
       </c>
       <c r="G25">
-        <v>65.03</v>
+        <v>57.397959183672413</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B26" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C26">
         <v>1562.5</v>
       </c>
       <c r="D26">
-        <v>93.860000000000014</v>
+        <v>94.060000299999956</v>
       </c>
       <c r="E26">
-        <v>3.34</v>
+        <v>3.659999999999854</v>
       </c>
       <c r="F26">
-        <v>67.37</v>
+        <v>61.475409836068017</v>
       </c>
       <c r="G26">
-        <v>67.37</v>
+        <v>61.475409836068017</v>
       </c>
       <c r="H26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B27" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C27">
         <v>1625</v>
       </c>
       <c r="D27">
-        <v>97.44</v>
+        <v>97.720000300000038</v>
       </c>
       <c r="E27">
-        <v>3.58</v>
+        <v>3.6600000000000819</v>
       </c>
       <c r="F27">
-        <v>62.85</v>
+        <v>61.475409836064202</v>
       </c>
       <c r="G27">
-        <v>62.85</v>
+        <v>61.475409836064202</v>
       </c>
       <c r="H27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B28" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C28">
         <v>1687.5</v>
       </c>
       <c r="D28">
-        <v>101</v>
+        <v>101.3600003000001</v>
       </c>
       <c r="E28">
-        <v>3.56</v>
+        <v>3.6400000000001</v>
       </c>
       <c r="F28">
-        <v>64.650000000000006</v>
+        <v>61.813186813185112</v>
       </c>
       <c r="G28">
-        <v>63.2</v>
+        <v>61.813186813185112</v>
       </c>
       <c r="H28" t="s">
         <v>12</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B29" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C29">
         <v>1750</v>
       </c>
       <c r="D29">
-        <v>104.46</v>
+        <v>105.0000003</v>
       </c>
       <c r="E29">
-        <v>3.46</v>
+        <v>3.6399999999998731</v>
       </c>
       <c r="F29">
-        <v>65.03</v>
+        <v>61.813186813188977</v>
       </c>
       <c r="G29">
-        <v>65.03</v>
+        <v>61.813186813188977</v>
       </c>
       <c r="H29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B30" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C30">
         <v>1812.5</v>
       </c>
       <c r="D30">
-        <v>107.76</v>
+        <v>108.6200003000001</v>
       </c>
       <c r="E30">
-        <v>3.3</v>
+        <v>3.6200000000001178</v>
       </c>
       <c r="F30">
-        <v>68.180000000000007</v>
+        <v>62.154696132594658</v>
       </c>
       <c r="G30">
-        <v>68.180000000000007</v>
+        <v>62.154696132594658</v>
       </c>
       <c r="H30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B31" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C31">
         <v>1875</v>
       </c>
       <c r="D31">
-        <v>111.34</v>
+        <v>112.38000030000011</v>
       </c>
       <c r="E31">
-        <v>3.58</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F31">
-        <v>62.85</v>
+        <v>61.81</v>
       </c>
       <c r="G31">
-        <v>62.85</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B32" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C32">
         <v>1937.5</v>
       </c>
       <c r="D32">
-        <v>114.76</v>
+        <v>116.02000030000001</v>
       </c>
       <c r="E32">
-        <v>3.42</v>
+        <v>3.6399999999998731</v>
       </c>
       <c r="F32">
-        <v>65.790000000000006</v>
+        <v>61.813186813188977</v>
       </c>
       <c r="G32">
-        <v>65.790000000000006</v>
+        <v>61.813186813188977</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B33" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C33">
         <v>2000</v>
       </c>
       <c r="D33">
-        <v>118.18</v>
+        <v>119.6800003000001</v>
       </c>
       <c r="E33">
-        <v>3.42</v>
+        <v>3.6600000000000819</v>
       </c>
       <c r="F33">
-        <v>65.790000000000006</v>
+        <v>61.475409836064202</v>
       </c>
       <c r="G33">
-        <v>65.790000000000006</v>
+        <v>61.475409836064202</v>
       </c>
       <c r="H33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B34" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C34">
         <v>2062.5</v>
       </c>
       <c r="D34">
-        <v>121.46</v>
+        <v>123.3600003000001</v>
       </c>
       <c r="E34">
-        <v>3.28</v>
+        <v>3.6800000000000641</v>
       </c>
       <c r="F34">
-        <v>68.599999999999994</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="G34">
-        <v>68.599999999999994</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="H34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B35" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C35">
         <v>2125</v>
       </c>
       <c r="D35">
-        <v>125.06</v>
+        <v>127.0600003</v>
       </c>
       <c r="E35">
-        <v>3.6</v>
+        <v>3.6999999999998181</v>
       </c>
       <c r="F35">
-        <v>62.5</v>
+        <v>60.810810810813798</v>
       </c>
       <c r="G35">
-        <v>62.5</v>
+        <v>60.810810810813798</v>
       </c>
       <c r="H35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B36" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C36">
         <v>2187.5</v>
       </c>
       <c r="D36">
-        <v>128.62</v>
+        <v>130.7600003</v>
       </c>
       <c r="E36">
-        <v>3.56</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F36">
-        <v>64.650000000000006</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G36">
-        <v>63.2</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H36" t="s">
         <v>12</v>
       </c>
       <c r="I36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B37" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C37">
         <v>2250</v>
       </c>
       <c r="D37">
-        <v>132.08000000000001</v>
+        <v>134.60000029999989</v>
       </c>
       <c r="E37">
-        <v>3.46</v>
+        <v>3.8399999999999181</v>
       </c>
       <c r="F37">
-        <v>65.03</v>
+        <v>60.48</v>
       </c>
       <c r="G37">
-        <v>65.03</v>
+        <v>58.593750000001251</v>
       </c>
       <c r="H37" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B38" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C38">
         <v>2312.5</v>
       </c>
       <c r="D38">
-        <v>135.4</v>
+        <v>138.32000029999989</v>
       </c>
       <c r="E38">
-        <v>3.32</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F38">
-        <v>67.77</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G38">
-        <v>67.77</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B39" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C39">
         <v>2375</v>
       </c>
       <c r="D39">
-        <v>139.02000000000001</v>
+        <v>142.06000030000001</v>
       </c>
       <c r="E39">
-        <v>3.62</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F39">
-        <v>62.15</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G39">
-        <v>62.15</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B40" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C40">
         <v>2437.5</v>
       </c>
       <c r="D40">
-        <v>142.62</v>
+        <v>145.80000029999999</v>
       </c>
       <c r="E40">
-        <v>3.6</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F40">
-        <v>63.92</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G40">
-        <v>62.5</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I40" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B41" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C41">
         <v>2500</v>
       </c>
       <c r="D41">
-        <v>146.13999999999999</v>
+        <v>149.52000029999999</v>
       </c>
       <c r="E41">
-        <v>3.52</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F41">
-        <v>63.92</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G41">
-        <v>63.92</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B42" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C42">
         <v>2562.5</v>
       </c>
       <c r="D42">
-        <v>149.52000000000001</v>
+        <v>153.24000029999999</v>
       </c>
       <c r="E42">
-        <v>3.38</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F42">
-        <v>66.569999999999993</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G42">
-        <v>66.569999999999993</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B43" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C43">
         <v>2625</v>
       </c>
       <c r="D43">
-        <v>153.18</v>
+        <v>157.10000029999989</v>
       </c>
       <c r="E43">
-        <v>3.66</v>
+        <v>3.8599999999999</v>
       </c>
       <c r="F43">
-        <v>61.48</v>
+        <v>60.16</v>
       </c>
       <c r="G43">
-        <v>61.48</v>
+        <v>58.290155440416022</v>
       </c>
       <c r="H43" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B44" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C44">
         <v>2687.5</v>
       </c>
       <c r="D44">
-        <v>156.69999999999999</v>
+        <v>160.94000030000009</v>
       </c>
       <c r="E44">
-        <v>3.52</v>
+        <v>3.840000000000146</v>
       </c>
       <c r="F44">
-        <v>63.92</v>
+        <v>58.593749999997783</v>
       </c>
       <c r="G44">
-        <v>63.92</v>
+        <v>58.593749999997783</v>
       </c>
       <c r="H44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I44" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B45" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C45">
         <v>2750</v>
       </c>
       <c r="D45">
-        <v>160.24</v>
+        <v>164.52000029999999</v>
       </c>
       <c r="E45">
-        <v>3.54</v>
+        <v>3.5799999999999268</v>
       </c>
       <c r="F45">
-        <v>63.56</v>
+        <v>62.849162011174457</v>
       </c>
       <c r="G45">
-        <v>63.56</v>
+        <v>62.849162011174457</v>
       </c>
       <c r="H45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I45" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B46" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C46">
         <v>2812.5</v>
       </c>
       <c r="D46">
-        <v>163.74</v>
+        <v>168.2600003</v>
       </c>
       <c r="E46">
-        <v>3.5</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F46">
-        <v>65.790000000000006</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G46">
-        <v>64.290000000000006</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H46" t="s">
         <v>12</v>
       </c>
       <c r="I46" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B47" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C47">
         <v>2875</v>
       </c>
       <c r="D47">
-        <v>167.38</v>
+        <v>172.00000030000001</v>
       </c>
       <c r="E47">
-        <v>3.64</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F47">
-        <v>61.81</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G47">
-        <v>61.81</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B48" s="2">
-        <v>45118</v>
+        <v>45126</v>
       </c>
       <c r="C48">
         <v>2937.5</v>
       </c>
       <c r="D48">
-        <v>170.88</v>
+        <v>175.9800003</v>
       </c>
       <c r="E48">
-        <v>3.5</v>
+        <v>3.9800000000000182</v>
       </c>
       <c r="F48">
-        <v>64.290000000000006</v>
+        <v>58.29</v>
       </c>
       <c r="G48">
-        <v>64.290000000000006</v>
+        <v>56.532663316582664</v>
       </c>
       <c r="H48" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C49">
+        <v>62.5</v>
+      </c>
+      <c r="D49">
+        <v>3.6800000000000641</v>
+      </c>
+      <c r="E49">
+        <v>3.6800000000000641</v>
+      </c>
+      <c r="F49">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="G49">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="H49" t="s">
+        <v>12</v>
+      </c>
+      <c r="I49" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C50">
+        <v>125</v>
+      </c>
+      <c r="D50">
+        <v>7.3800000000001091</v>
+      </c>
+      <c r="E50">
+        <v>3.700000000000045</v>
+      </c>
+      <c r="F50">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="G50">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="H50" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C51">
+        <v>187.5</v>
+      </c>
+      <c r="D51">
+        <v>11.10000000000014</v>
+      </c>
+      <c r="E51">
+        <v>3.7200000000000268</v>
+      </c>
+      <c r="F51">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="G51">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="H51" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C52">
+        <v>250</v>
+      </c>
+      <c r="D52">
+        <v>14.82000000000016</v>
+      </c>
+      <c r="E52">
+        <v>3.7200000000000268</v>
+      </c>
+      <c r="F52">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="G52">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="H52" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C53">
+        <v>312.5</v>
+      </c>
+      <c r="D53">
+        <v>18.560000000000169</v>
+      </c>
+      <c r="E53">
+        <v>3.7400000000000091</v>
+      </c>
+      <c r="F53">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="G53">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="H53" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C54">
+        <v>375</v>
+      </c>
+      <c r="D54">
+        <v>22.420000000000069</v>
+      </c>
+      <c r="E54">
+        <v>3.8599999999999</v>
+      </c>
+      <c r="F54">
+        <v>60.16</v>
+      </c>
+      <c r="G54">
+        <v>58.290155440416022</v>
+      </c>
+      <c r="H54" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C55">
+        <v>437.5</v>
+      </c>
+      <c r="D55">
+        <v>26.160000000000078</v>
+      </c>
+      <c r="E55">
+        <v>3.7400000000000091</v>
+      </c>
+      <c r="F55">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="G55">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="H55" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C49">
-        <v>3000</v>
-      </c>
-      <c r="D49">
-        <v>174.4</v>
-      </c>
-      <c r="E49">
-        <v>3.52</v>
-      </c>
-      <c r="F49">
-        <v>63.92</v>
-      </c>
-      <c r="G49">
-        <v>63.92</v>
-      </c>
-      <c r="H49" t="s">
-        <v>11</v>
-      </c>
-      <c r="I49" t="s">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C56">
+        <v>500</v>
+      </c>
+      <c r="D56">
+        <v>29.880000000000109</v>
+      </c>
+      <c r="E56">
+        <v>3.7200000000000268</v>
+      </c>
+      <c r="F56">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="G56">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="H56" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C50">
-        <v>3062.5</v>
-      </c>
-      <c r="D50">
-        <v>177.78</v>
-      </c>
-      <c r="E50">
-        <v>3.38</v>
-      </c>
-      <c r="F50">
-        <v>66.569999999999993</v>
-      </c>
-      <c r="G50">
-        <v>66.569999999999993</v>
-      </c>
-      <c r="H50" t="s">
-        <v>11</v>
-      </c>
-      <c r="I50" t="s">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C57">
+        <v>562.5</v>
+      </c>
+      <c r="D57">
+        <v>33.600000000000144</v>
+      </c>
+      <c r="E57">
+        <v>3.7200000000000268</v>
+      </c>
+      <c r="F57">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="G57">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="H57" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C51">
-        <v>3125</v>
-      </c>
-      <c r="D51">
-        <v>181.4</v>
-      </c>
-      <c r="E51">
-        <v>3.62</v>
-      </c>
-      <c r="F51">
-        <v>62.15</v>
-      </c>
-      <c r="G51">
-        <v>62.15</v>
-      </c>
-      <c r="H51" t="s">
-        <v>11</v>
-      </c>
-      <c r="I51" t="s">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C58">
+        <v>625</v>
+      </c>
+      <c r="D58">
+        <v>37.300000000000182</v>
+      </c>
+      <c r="E58">
+        <v>3.700000000000045</v>
+      </c>
+      <c r="F58">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="G58">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="H58" t="s">
+        <v>12</v>
+      </c>
+      <c r="I58" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C52">
-        <v>3187.5</v>
-      </c>
-      <c r="D52">
-        <v>184.92</v>
-      </c>
-      <c r="E52">
-        <v>3.52</v>
-      </c>
-      <c r="F52">
-        <v>63.92</v>
-      </c>
-      <c r="G52">
-        <v>63.92</v>
-      </c>
-      <c r="H52" t="s">
-        <v>11</v>
-      </c>
-      <c r="I52" t="s">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C59">
+        <v>687.5</v>
+      </c>
+      <c r="D59">
+        <v>41.019999999999982</v>
+      </c>
+      <c r="E59">
+        <v>3.7199999999997999</v>
+      </c>
+      <c r="F59">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="G59">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="H59" t="s">
+        <v>12</v>
+      </c>
+      <c r="I59" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C53">
-        <v>3250</v>
-      </c>
-      <c r="D53">
-        <v>188.44</v>
-      </c>
-      <c r="E53">
-        <v>3.52</v>
-      </c>
-      <c r="F53">
-        <v>63.92</v>
-      </c>
-      <c r="G53">
-        <v>63.92</v>
-      </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-      <c r="I53" t="s">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C60">
+        <v>750</v>
+      </c>
+      <c r="D60">
+        <v>44.840000000000153</v>
+      </c>
+      <c r="E60">
+        <v>3.8200000000001642</v>
+      </c>
+      <c r="F60">
+        <v>60.81</v>
+      </c>
+      <c r="G60">
+        <v>58.900523560206899</v>
+      </c>
+      <c r="H60" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C54">
-        <v>3312.5</v>
-      </c>
-      <c r="D54">
-        <v>191.94</v>
-      </c>
-      <c r="E54">
-        <v>3.5</v>
-      </c>
-      <c r="F54">
-        <v>65.790000000000006</v>
-      </c>
-      <c r="G54">
-        <v>64.290000000000006</v>
-      </c>
-      <c r="H54" t="s">
-        <v>12</v>
-      </c>
-      <c r="I54" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>10</v>
-      </c>
-      <c r="B55" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C55">
-        <v>3375</v>
-      </c>
-      <c r="D55">
-        <v>195.6</v>
-      </c>
-      <c r="E55">
-        <v>3.66</v>
-      </c>
-      <c r="F55">
-        <v>61.48</v>
-      </c>
-      <c r="G55">
-        <v>61.48</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-      <c r="I55" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C56">
-        <v>3437.5</v>
-      </c>
-      <c r="D56">
-        <v>199.08</v>
-      </c>
-      <c r="E56">
-        <v>3.48</v>
-      </c>
-      <c r="F56">
-        <v>64.66</v>
-      </c>
-      <c r="G56">
-        <v>64.66</v>
-      </c>
-      <c r="H56" t="s">
-        <v>11</v>
-      </c>
-      <c r="I56" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>10</v>
-      </c>
-      <c r="B57" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C57">
-        <v>3500</v>
-      </c>
-      <c r="D57">
-        <v>202.6</v>
-      </c>
-      <c r="E57">
-        <v>3.52</v>
-      </c>
-      <c r="F57">
-        <v>63.92</v>
-      </c>
-      <c r="G57">
-        <v>63.92</v>
-      </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-      <c r="I57" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C58">
-        <v>3562.5</v>
-      </c>
-      <c r="D58">
-        <v>205.92</v>
-      </c>
-      <c r="E58">
-        <v>3.32</v>
-      </c>
-      <c r="F58">
-        <v>67.77</v>
-      </c>
-      <c r="G58">
-        <v>67.77</v>
-      </c>
-      <c r="H58" t="s">
-        <v>11</v>
-      </c>
-      <c r="I58" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C59">
-        <v>3625</v>
-      </c>
-      <c r="D59">
-        <v>209.52</v>
-      </c>
-      <c r="E59">
-        <v>3.6</v>
-      </c>
-      <c r="F59">
-        <v>62.5</v>
-      </c>
-      <c r="G59">
-        <v>62.5</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-      <c r="I59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" s="2">
-        <v>45118</v>
-      </c>
-      <c r="C60">
-        <v>3687.5</v>
-      </c>
-      <c r="D60">
-        <v>212.96</v>
-      </c>
-      <c r="E60">
-        <v>3.44</v>
-      </c>
-      <c r="F60">
-        <v>65.41</v>
-      </c>
-      <c r="G60">
-        <v>65.41</v>
-      </c>
-      <c r="H60" t="s">
-        <v>11</v>
-      </c>
-      <c r="I60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B61" s="2">
-        <v>45118</v>
+        <v>45127</v>
       </c>
       <c r="C61">
-        <v>3750</v>
+        <v>812.5</v>
       </c>
       <c r="D61">
-        <v>216.44</v>
+        <v>48.540000000000191</v>
       </c>
       <c r="E61">
-        <v>3.48</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F61">
-        <v>64.66</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G61">
-        <v>64.66</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H61" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I61" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B62" s="2">
-        <v>45118</v>
+        <v>45127</v>
       </c>
       <c r="C62">
-        <v>3812.5</v>
+        <v>875</v>
       </c>
       <c r="D62">
-        <v>219.8</v>
+        <v>52.259999999999991</v>
       </c>
       <c r="E62">
-        <v>3.36</v>
+        <v>3.7199999999997999</v>
       </c>
       <c r="F62">
-        <v>66.959999999999994</v>
+        <v>60.48387096774519</v>
       </c>
       <c r="G62">
-        <v>66.959999999999994</v>
+        <v>60.48387096774519</v>
       </c>
       <c r="H62" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I62" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B63" s="2">
-        <v>45118</v>
+        <v>45127</v>
       </c>
       <c r="C63">
-        <v>3875</v>
+        <v>937.5</v>
       </c>
       <c r="D63">
-        <v>223.44</v>
+        <v>56.019999999999982</v>
       </c>
       <c r="E63">
-        <v>3.64</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F63">
-        <v>61.81</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="G63">
-        <v>61.81</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H63" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I63" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B64" s="2">
-        <v>45118</v>
+        <v>45127</v>
       </c>
       <c r="C64">
-        <v>3937.5</v>
+        <v>1000</v>
       </c>
       <c r="D64">
-        <v>226.98</v>
+        <v>59.740000000000009</v>
       </c>
       <c r="E64">
-        <v>3.54</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F64">
-        <v>63.56</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G64">
-        <v>63.56</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I64" t="s">
         <v>17</v>
@@ -2361,28 +2387,28 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B65" s="2">
-        <v>45118</v>
+        <v>45127</v>
       </c>
       <c r="C65">
-        <v>4000</v>
+        <v>1062.5</v>
       </c>
       <c r="D65">
-        <v>230.78</v>
+        <v>63.460000000000043</v>
       </c>
       <c r="E65">
-        <v>3.8</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F65">
-        <v>59.21</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G65">
-        <v>59.21</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H65" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I65" t="s">
         <v>17</v>
@@ -2390,1861 +2416,3610 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B66" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C66">
-        <v>62.5</v>
+        <v>1125</v>
       </c>
       <c r="D66">
-        <v>8.32</v>
+        <v>67.300000000000182</v>
       </c>
       <c r="E66">
-        <v>8.32</v>
+        <v>3.840000000000146</v>
       </c>
       <c r="F66">
-        <v>27.04326923076923</v>
+        <v>60.48</v>
       </c>
       <c r="G66">
-        <v>27.04326923076923</v>
+        <v>58.593749999997783</v>
       </c>
       <c r="H66" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B67" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C67">
-        <v>125</v>
+        <v>1187.5</v>
       </c>
       <c r="D67">
-        <v>13.2</v>
+        <v>71</v>
       </c>
       <c r="E67">
-        <v>4.8799999999999946</v>
+        <v>3.6999999999998181</v>
       </c>
       <c r="F67">
-        <v>46.106557377049221</v>
+        <v>60.810810810813798</v>
       </c>
       <c r="G67">
-        <v>46.106557377049221</v>
+        <v>60.810810810813798</v>
       </c>
       <c r="H67" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B68" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C68">
-        <v>187.5</v>
+        <v>1250</v>
       </c>
       <c r="D68">
-        <v>17.239999999999998</v>
+        <v>74.700000000000045</v>
       </c>
       <c r="E68">
-        <v>4.0400000000000063</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F68">
-        <v>55.69306930693061</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G68">
-        <v>55.69306930693061</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H68" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B69" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C69">
-        <v>250</v>
+        <v>1312.5</v>
       </c>
       <c r="D69">
-        <v>21.28</v>
+        <v>78.400000000000091</v>
       </c>
       <c r="E69">
-        <v>4.0399999999999991</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F69">
-        <v>55.693069306930703</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G69">
-        <v>55.693069306930703</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H69" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B70" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C70">
-        <v>312.5</v>
+        <v>1375</v>
       </c>
       <c r="D70">
-        <v>25.03</v>
+        <v>82.100000000000136</v>
       </c>
       <c r="E70">
-        <v>3.75</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F70">
-        <v>60</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G70">
-        <v>60</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H70" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B71" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C71">
-        <v>375</v>
+        <v>1437.5</v>
       </c>
       <c r="D71">
-        <v>28.53</v>
+        <v>85.820000000000164</v>
       </c>
       <c r="E71">
-        <v>3.5</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F71">
-        <v>64.285714285714292</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G71">
-        <v>64.285714285714292</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B72" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C72">
-        <v>437.5</v>
+        <v>1500</v>
       </c>
       <c r="D72">
-        <v>32.319999999999993</v>
+        <v>89.620000000000118</v>
       </c>
       <c r="E72">
-        <v>3.789999999999992</v>
+        <v>3.799999999999955</v>
       </c>
       <c r="F72">
-        <v>63.2</v>
+        <v>61.14</v>
       </c>
       <c r="G72">
-        <v>59.366754617414372</v>
+        <v>59.210526315790183</v>
       </c>
       <c r="H72" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B73" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C73">
-        <v>500</v>
+        <v>1562.5</v>
       </c>
       <c r="D73">
-        <v>35.86</v>
+        <v>93.320000000000164</v>
       </c>
       <c r="E73">
-        <v>3.5400000000000058</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F73">
-        <v>63.559322033898191</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G73">
-        <v>63.559322033898191</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I73" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B74" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C74">
-        <v>562.5</v>
+        <v>1625</v>
       </c>
       <c r="D74">
-        <v>39.61</v>
+        <v>97.040000000000191</v>
       </c>
       <c r="E74">
-        <v>3.75</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F74">
-        <v>60</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G74">
-        <v>60</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I74" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B75" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C75">
-        <v>625</v>
+        <v>1687.5</v>
       </c>
       <c r="D75">
-        <v>43.61</v>
+        <v>100.72</v>
       </c>
       <c r="E75">
-        <v>4</v>
+        <v>3.6799999999998358</v>
       </c>
       <c r="F75">
-        <v>56.25</v>
+        <v>61.141304347828807</v>
       </c>
       <c r="G75">
-        <v>56.25</v>
+        <v>61.141304347828807</v>
       </c>
       <c r="H75" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I75" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B76" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C76">
-        <v>687.5</v>
+        <v>1750</v>
       </c>
       <c r="D76">
-        <v>47.39</v>
+        <v>104.40000000000011</v>
       </c>
       <c r="E76">
-        <v>3.7800000000000011</v>
+        <v>3.6800000000000641</v>
       </c>
       <c r="F76">
-        <v>59.523809523809497</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="G76">
-        <v>59.523809523809497</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="H76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I76" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B77" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C77">
-        <v>750</v>
+        <v>1812.5</v>
       </c>
       <c r="D77">
-        <v>51.39</v>
+        <v>108.0800000000002</v>
       </c>
       <c r="E77">
-        <v>4</v>
+        <v>3.6800000000000641</v>
       </c>
       <c r="F77">
-        <v>56.25</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="G77">
-        <v>56.25</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="H77" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I77" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B78" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C78">
-        <v>812.5</v>
+        <v>1875</v>
       </c>
       <c r="D78">
-        <v>55.14</v>
+        <v>111.88000000000009</v>
       </c>
       <c r="E78">
-        <v>3.75</v>
+        <v>3.799999999999955</v>
       </c>
       <c r="F78">
-        <v>63.92</v>
+        <v>61.14</v>
       </c>
       <c r="G78">
-        <v>60</v>
+        <v>59.210526315790183</v>
       </c>
       <c r="H78" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I78" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B79" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C79">
-        <v>875</v>
+        <v>1937.5</v>
       </c>
       <c r="D79">
-        <v>59.14</v>
+        <v>115.54000000000021</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>3.6600000000000819</v>
       </c>
       <c r="F79">
-        <v>56.25</v>
+        <v>61.475409836064202</v>
       </c>
       <c r="G79">
-        <v>56.25</v>
+        <v>61.475409836064202</v>
       </c>
       <c r="H79" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I79" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C80">
+        <v>2000</v>
+      </c>
+      <c r="D80">
+        <v>119.22</v>
+      </c>
+      <c r="E80">
+        <v>3.6799999999998358</v>
+      </c>
+      <c r="F80">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="G80">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="H80" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C81">
+        <v>2062.5</v>
+      </c>
+      <c r="D81">
+        <v>122.90000000000011</v>
+      </c>
+      <c r="E81">
+        <v>3.6800000000000641</v>
+      </c>
+      <c r="F81">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="G81">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="H81" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C82">
+        <v>2125</v>
+      </c>
+      <c r="D82">
+        <v>126.5600000000002</v>
+      </c>
+      <c r="E82">
+        <v>3.6600000000000819</v>
+      </c>
+      <c r="F82">
+        <v>61.475409836064202</v>
+      </c>
+      <c r="G82">
+        <v>61.475409836064202</v>
+      </c>
+      <c r="H82" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C83">
+        <v>2187.5</v>
+      </c>
+      <c r="D83">
+        <v>130.24</v>
+      </c>
+      <c r="E83">
+        <v>3.6799999999998358</v>
+      </c>
+      <c r="F83">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="G83">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="H83" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C84">
+        <v>2250</v>
+      </c>
+      <c r="D84">
+        <v>134.04000000000019</v>
+      </c>
+      <c r="E84">
+        <v>3.8000000000001819</v>
+      </c>
+      <c r="F84">
+        <v>61.14</v>
+      </c>
+      <c r="G84">
+        <v>59.210526315786637</v>
+      </c>
+      <c r="H84" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B85" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C85">
+        <v>2312.5</v>
+      </c>
+      <c r="D85">
+        <v>137.76</v>
+      </c>
+      <c r="E85">
+        <v>3.7199999999997999</v>
+      </c>
+      <c r="F85">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="G85">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="H85" t="s">
+        <v>12</v>
+      </c>
+      <c r="I85" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>21</v>
+      </c>
+      <c r="B86" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C86">
+        <v>2375</v>
+      </c>
+      <c r="D86">
+        <v>141.5</v>
+      </c>
+      <c r="E86">
+        <v>3.7400000000000091</v>
+      </c>
+      <c r="F86">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="G86">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="H86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>21</v>
+      </c>
+      <c r="B87" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C87">
+        <v>2437.5</v>
+      </c>
+      <c r="D87">
+        <v>145.24</v>
+      </c>
+      <c r="E87">
+        <v>3.7400000000000091</v>
+      </c>
+      <c r="F87">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="G87">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="H87" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C88">
+        <v>2500</v>
+      </c>
+      <c r="D88">
+        <v>148.97999999999999</v>
+      </c>
+      <c r="E88">
+        <v>3.7400000000000091</v>
+      </c>
+      <c r="F88">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="G88">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="H88" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C89">
+        <v>2562.5</v>
+      </c>
+      <c r="D89">
+        <v>152.72</v>
+      </c>
+      <c r="E89">
+        <v>3.7400000000000091</v>
+      </c>
+      <c r="F89">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="G89">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="H89" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>21</v>
+      </c>
+      <c r="B90" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C90">
+        <v>2625</v>
+      </c>
+      <c r="D90">
+        <v>156.5600000000002</v>
+      </c>
+      <c r="E90">
+        <v>3.840000000000146</v>
+      </c>
+      <c r="F90">
+        <v>60.48</v>
+      </c>
+      <c r="G90">
+        <v>58.593749999997783</v>
+      </c>
+      <c r="H90" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>21</v>
+      </c>
+      <c r="B91" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C91">
+        <v>2687.5</v>
+      </c>
+      <c r="D91">
+        <v>160.28</v>
+      </c>
+      <c r="E91">
+        <v>3.7199999999997999</v>
+      </c>
+      <c r="F91">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="G91">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="H91" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>21</v>
+      </c>
+      <c r="B92" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C92">
+        <v>2750</v>
+      </c>
+      <c r="D92">
+        <v>163.96</v>
+      </c>
+      <c r="E92">
+        <v>3.6800000000000641</v>
+      </c>
+      <c r="F92">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="G92">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="H92" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C93">
+        <v>2812.5</v>
+      </c>
+      <c r="D93">
+        <v>167.66000000000011</v>
+      </c>
+      <c r="E93">
+        <v>3.700000000000045</v>
+      </c>
+      <c r="F93">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="G93">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="H93" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>21</v>
+      </c>
+      <c r="B94" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C94">
+        <v>2875</v>
+      </c>
+      <c r="D94">
+        <v>171.34000000000009</v>
+      </c>
+      <c r="E94">
+        <v>3.6800000000000641</v>
+      </c>
+      <c r="F94">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="G94">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="H94" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>21</v>
+      </c>
+      <c r="B95" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C95">
+        <v>2937.5</v>
+      </c>
+      <c r="D95">
+        <v>175.30000000000021</v>
+      </c>
+      <c r="E95">
+        <v>3.9600000000000359</v>
+      </c>
+      <c r="F95">
+        <v>58.59</v>
+      </c>
+      <c r="G95">
+        <v>56.818181818181287</v>
+      </c>
+      <c r="H95" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>10</v>
+      </c>
+      <c r="B96" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C96">
+        <v>62.5</v>
+      </c>
+      <c r="D96">
+        <v>3.700000000000045</v>
+      </c>
+      <c r="E96">
+        <v>3.700000000000045</v>
+      </c>
+      <c r="F96">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="G96">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="H96" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" t="s">
         <v>23</v>
-      </c>
-      <c r="B80" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C80">
-        <v>937.5</v>
-      </c>
-      <c r="D80">
-        <v>62.64</v>
-      </c>
-      <c r="E80">
-        <v>3.5</v>
-      </c>
-      <c r="F80">
-        <v>64.285714285714292</v>
-      </c>
-      <c r="G80">
-        <v>64.285714285714292</v>
-      </c>
-      <c r="H80" t="s">
-        <v>11</v>
-      </c>
-      <c r="I80" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>23</v>
-      </c>
-      <c r="B81" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C81">
-        <v>1000</v>
-      </c>
-      <c r="D81">
-        <v>66.39</v>
-      </c>
-      <c r="E81">
-        <v>3.75</v>
-      </c>
-      <c r="F81">
-        <v>60</v>
-      </c>
-      <c r="G81">
-        <v>60</v>
-      </c>
-      <c r="H81" t="s">
-        <v>11</v>
-      </c>
-      <c r="I81" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>23</v>
-      </c>
-      <c r="B82" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C82">
-        <v>1062.5</v>
-      </c>
-      <c r="D82">
-        <v>70.64</v>
-      </c>
-      <c r="E82">
-        <v>4.25</v>
-      </c>
-      <c r="F82">
-        <v>52.941176470588232</v>
-      </c>
-      <c r="G82">
-        <v>52.941176470588232</v>
-      </c>
-      <c r="H82" t="s">
-        <v>11</v>
-      </c>
-      <c r="I82" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>23</v>
-      </c>
-      <c r="B83" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C83">
-        <v>1125</v>
-      </c>
-      <c r="D83">
-        <v>74.39</v>
-      </c>
-      <c r="E83">
-        <v>3.75</v>
-      </c>
-      <c r="F83">
-        <v>60</v>
-      </c>
-      <c r="G83">
-        <v>60</v>
-      </c>
-      <c r="H83" t="s">
-        <v>11</v>
-      </c>
-      <c r="I83" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>23</v>
-      </c>
-      <c r="B84" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C84">
-        <v>1187.5</v>
-      </c>
-      <c r="D84">
-        <v>78.14</v>
-      </c>
-      <c r="E84">
-        <v>3.75</v>
-      </c>
-      <c r="F84">
-        <v>60</v>
-      </c>
-      <c r="G84">
-        <v>60</v>
-      </c>
-      <c r="H84" t="s">
-        <v>11</v>
-      </c>
-      <c r="I84" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>23</v>
-      </c>
-      <c r="B85" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C85">
-        <v>1250</v>
-      </c>
-      <c r="D85">
-        <v>81.14</v>
-      </c>
-      <c r="E85">
-        <v>3</v>
-      </c>
-      <c r="F85">
-        <v>75</v>
-      </c>
-      <c r="G85">
-        <v>75</v>
-      </c>
-      <c r="H85" t="s">
-        <v>11</v>
-      </c>
-      <c r="I85" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>23</v>
-      </c>
-      <c r="B86" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C86">
-        <v>1312.5</v>
-      </c>
-      <c r="D86">
-        <v>85.64</v>
-      </c>
-      <c r="E86">
-        <v>4.5</v>
-      </c>
-      <c r="F86">
-        <v>52.69</v>
-      </c>
-      <c r="G86">
-        <v>50</v>
-      </c>
-      <c r="H86" t="s">
-        <v>12</v>
-      </c>
-      <c r="I86" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>23</v>
-      </c>
-      <c r="B87" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C87">
-        <v>1375</v>
-      </c>
-      <c r="D87">
-        <v>89.39</v>
-      </c>
-      <c r="E87">
-        <v>3.75</v>
-      </c>
-      <c r="F87">
-        <v>60</v>
-      </c>
-      <c r="G87">
-        <v>60</v>
-      </c>
-      <c r="H87" t="s">
-        <v>11</v>
-      </c>
-      <c r="I87" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>23</v>
-      </c>
-      <c r="B88" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C88">
-        <v>1437.5</v>
-      </c>
-      <c r="D88">
-        <v>92.89</v>
-      </c>
-      <c r="E88">
-        <v>3.5</v>
-      </c>
-      <c r="F88">
-        <v>64.285714285714292</v>
-      </c>
-      <c r="G88">
-        <v>64.285714285714292</v>
-      </c>
-      <c r="H88" t="s">
-        <v>11</v>
-      </c>
-      <c r="I88" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>23</v>
-      </c>
-      <c r="B89" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C89">
-        <v>1500</v>
-      </c>
-      <c r="D89">
-        <v>96.719999999999985</v>
-      </c>
-      <c r="E89">
-        <v>3.8299999999999841</v>
-      </c>
-      <c r="F89">
-        <v>58.746736292428437</v>
-      </c>
-      <c r="G89">
-        <v>58.746736292428437</v>
-      </c>
-      <c r="H89" t="s">
-        <v>11</v>
-      </c>
-      <c r="I89" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>23</v>
-      </c>
-      <c r="B90" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C90">
-        <v>1562.5</v>
-      </c>
-      <c r="D90">
-        <v>100.97</v>
-      </c>
-      <c r="E90">
-        <v>4.25</v>
-      </c>
-      <c r="F90">
-        <v>52.941176470588232</v>
-      </c>
-      <c r="G90">
-        <v>52.941176470588232</v>
-      </c>
-      <c r="H90" t="s">
-        <v>11</v>
-      </c>
-      <c r="I90" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>23</v>
-      </c>
-      <c r="B91" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C91">
-        <v>1625</v>
-      </c>
-      <c r="D91">
-        <v>104.76</v>
-      </c>
-      <c r="E91">
-        <v>3.79000000000002</v>
-      </c>
-      <c r="F91">
-        <v>59.366754617413918</v>
-      </c>
-      <c r="G91">
-        <v>59.366754617413918</v>
-      </c>
-      <c r="H91" t="s">
-        <v>11</v>
-      </c>
-      <c r="I91" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>23</v>
-      </c>
-      <c r="B92" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C92">
-        <v>1687.5</v>
-      </c>
-      <c r="D92">
-        <v>108.26</v>
-      </c>
-      <c r="E92">
-        <v>3.5</v>
-      </c>
-      <c r="F92">
-        <v>64.285714285714292</v>
-      </c>
-      <c r="G92">
-        <v>64.285714285714292</v>
-      </c>
-      <c r="H92" t="s">
-        <v>11</v>
-      </c>
-      <c r="I92" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>23</v>
-      </c>
-      <c r="B93" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C93">
-        <v>1750</v>
-      </c>
-      <c r="D93">
-        <v>111.76</v>
-      </c>
-      <c r="E93">
-        <v>3.5</v>
-      </c>
-      <c r="F93">
-        <v>64.285714285714292</v>
-      </c>
-      <c r="G93">
-        <v>64.285714285714292</v>
-      </c>
-      <c r="H93" t="s">
-        <v>11</v>
-      </c>
-      <c r="I93" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>23</v>
-      </c>
-      <c r="B94" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C94">
-        <v>1812.5</v>
-      </c>
-      <c r="D94">
-        <v>115.76</v>
-      </c>
-      <c r="E94">
-        <v>4</v>
-      </c>
-      <c r="F94">
-        <v>59.68</v>
-      </c>
-      <c r="G94">
-        <v>56.25</v>
-      </c>
-      <c r="H94" t="s">
-        <v>12</v>
-      </c>
-      <c r="I94" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>23</v>
-      </c>
-      <c r="B95" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C95">
-        <v>1875</v>
-      </c>
-      <c r="D95">
-        <v>120.26</v>
-      </c>
-      <c r="E95">
-        <v>4.5</v>
-      </c>
-      <c r="F95">
-        <v>50</v>
-      </c>
-      <c r="G95">
-        <v>50</v>
-      </c>
-      <c r="H95" t="s">
-        <v>11</v>
-      </c>
-      <c r="I95" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>23</v>
-      </c>
-      <c r="B96" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C96">
-        <v>1937.5</v>
-      </c>
-      <c r="D96">
-        <v>123.26</v>
-      </c>
-      <c r="E96">
-        <v>3</v>
-      </c>
-      <c r="F96">
-        <v>75</v>
-      </c>
-      <c r="G96">
-        <v>75</v>
-      </c>
-      <c r="H96" t="s">
-        <v>11</v>
-      </c>
-      <c r="I96" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B97" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C97">
-        <v>2000</v>
+        <v>125</v>
       </c>
       <c r="D97">
-        <v>127.01</v>
+        <v>7.4200000000000728</v>
       </c>
       <c r="E97">
-        <v>3.75</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F97">
-        <v>60</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G97">
-        <v>60</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H97" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B98" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C98">
-        <v>2062.5</v>
+        <v>187.5</v>
       </c>
       <c r="D98">
-        <v>130.76</v>
+        <v>11.1400000000001</v>
       </c>
       <c r="E98">
-        <v>3.7499999999999858</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F98">
-        <v>60.000000000000227</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G98">
-        <v>60.000000000000227</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H98" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B99" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C99">
-        <v>2125</v>
+        <v>250</v>
       </c>
       <c r="D99">
-        <v>135.01</v>
+        <v>14.840000000000151</v>
       </c>
       <c r="E99">
-        <v>4.25</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F99">
-        <v>52.941176470588232</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G99">
-        <v>52.941176470588232</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H99" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B100" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C100">
-        <v>2187.5</v>
+        <v>312.5</v>
       </c>
       <c r="D100">
-        <v>138.26</v>
+        <v>18.5</v>
       </c>
       <c r="E100">
-        <v>3.25</v>
+        <v>3.659999999999854</v>
       </c>
       <c r="F100">
-        <v>69.230769230769226</v>
+        <v>61.475409836068017</v>
       </c>
       <c r="G100">
-        <v>69.230769230769226</v>
+        <v>61.475409836068017</v>
       </c>
       <c r="H100" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B101" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C101">
-        <v>2250</v>
+        <v>375</v>
       </c>
       <c r="D101">
-        <v>141.51</v>
+        <v>22.32000000000016</v>
       </c>
       <c r="E101">
-        <v>3.25</v>
+        <v>3.8200000000001642</v>
       </c>
       <c r="F101">
-        <v>69.230769230769226</v>
+        <v>60.81</v>
       </c>
       <c r="G101">
-        <v>69.230769230769226</v>
+        <v>58.900523560206899</v>
       </c>
       <c r="H101" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B102" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C102">
-        <v>2312.5</v>
+        <v>437.5</v>
       </c>
       <c r="D102">
-        <v>145.76</v>
+        <v>26.019999999999978</v>
       </c>
       <c r="E102">
-        <v>4.25</v>
+        <v>3.6999999999998181</v>
       </c>
       <c r="F102">
-        <v>52.941176470588232</v>
+        <v>60.810810810813798</v>
       </c>
       <c r="G102">
-        <v>52.941176470588232</v>
+        <v>60.810810810813798</v>
       </c>
       <c r="H102" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B103" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C103">
-        <v>2375</v>
+        <v>500</v>
       </c>
       <c r="D103">
-        <v>149.51</v>
+        <v>29.720000000000031</v>
       </c>
       <c r="E103">
-        <v>3.75</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F103">
-        <v>60</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G103">
-        <v>60</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H103" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B104" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C104">
-        <v>2437.5</v>
+        <v>562.5</v>
       </c>
       <c r="D104">
-        <v>153.01</v>
+        <v>33.460000000000043</v>
       </c>
       <c r="E104">
-        <v>3.5</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F104">
-        <v>68.81</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G104">
-        <v>64.285714285714292</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B105" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C105">
-        <v>2500</v>
+        <v>625</v>
       </c>
       <c r="D105">
-        <v>156.51</v>
+        <v>37.200000000000053</v>
       </c>
       <c r="E105">
-        <v>3.5</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F105">
-        <v>64.285714285714292</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G105">
-        <v>64.285714285714292</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H105" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I105" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B106" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C106">
-        <v>2562.5</v>
+        <v>687.5</v>
       </c>
       <c r="D106">
-        <v>160.80000000000001</v>
+        <v>40.960000000000043</v>
       </c>
       <c r="E106">
-        <v>4.2900000000000196</v>
+        <v>3.7599999999999909</v>
       </c>
       <c r="F106">
-        <v>52.447552447552198</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="G106">
-        <v>52.447552447552198</v>
+        <v>59.840425531915038</v>
       </c>
       <c r="H106" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I106" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B107" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C107">
-        <v>2625</v>
+        <v>750</v>
       </c>
       <c r="D107">
-        <v>165.05</v>
+        <v>44.779999999999973</v>
       </c>
       <c r="E107">
-        <v>4.25</v>
+        <v>3.8199999999999359</v>
       </c>
       <c r="F107">
-        <v>52.941176470588232</v>
+        <v>60.81</v>
       </c>
       <c r="G107">
-        <v>52.941176470588232</v>
+        <v>58.900523560210402</v>
       </c>
       <c r="H107" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I107" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B108" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C108">
-        <v>2687.5</v>
+        <v>812.5</v>
       </c>
       <c r="D108">
-        <v>168.8</v>
+        <v>48.519999999999982</v>
       </c>
       <c r="E108">
-        <v>3.75</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F108">
-        <v>60</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G108">
-        <v>60</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H108" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I108" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B109" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C109">
-        <v>2750</v>
+        <v>875</v>
       </c>
       <c r="D109">
-        <v>172.3</v>
+        <v>52.240000000000009</v>
       </c>
       <c r="E109">
-        <v>3.5</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F109">
-        <v>64.285714285714292</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G109">
-        <v>64.285714285714292</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H109" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I109" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B110" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C110">
-        <v>2812.5</v>
+        <v>937.5</v>
       </c>
       <c r="D110">
-        <v>176.56</v>
+        <v>55.960000000000043</v>
       </c>
       <c r="E110">
-        <v>4.2599999999999909</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F110">
-        <v>55.83</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G110">
-        <v>52.816901408450818</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H110" t="s">
         <v>12</v>
       </c>
       <c r="I110" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B111" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C111">
-        <v>2875</v>
+        <v>1000</v>
       </c>
       <c r="D111">
-        <v>180.56</v>
+        <v>59.700000000000053</v>
       </c>
       <c r="E111">
-        <v>4</v>
+        <v>3.7400000000000091</v>
       </c>
       <c r="F111">
-        <v>56.25</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="G111">
-        <v>56.25</v>
+        <v>60.160427807486492</v>
       </c>
       <c r="H111" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I111" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B112" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C112">
-        <v>2937.5</v>
+        <v>1062.5</v>
       </c>
       <c r="D112">
-        <v>184.31</v>
+        <v>63.420000000000073</v>
       </c>
       <c r="E112">
-        <v>3.75</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F112">
-        <v>60</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G112">
-        <v>60</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H112" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I112" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B113" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C113">
-        <v>3000</v>
+        <v>1125</v>
       </c>
       <c r="D113">
-        <v>187.81</v>
+        <v>67.279999999999973</v>
       </c>
       <c r="E113">
-        <v>3.5</v>
+        <v>3.8599999999999</v>
       </c>
       <c r="F113">
-        <v>64.285714285714292</v>
+        <v>60.16</v>
       </c>
       <c r="G113">
-        <v>64.285714285714292</v>
+        <v>58.290155440416022</v>
       </c>
       <c r="H113" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I113" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B114" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C114">
-        <v>3062.5</v>
+        <v>1187.5</v>
       </c>
       <c r="D114">
-        <v>192.06</v>
+        <v>71</v>
       </c>
       <c r="E114">
-        <v>4.25</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F114">
-        <v>52.941176470588232</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G114">
-        <v>52.941176470588232</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H114" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I114" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B115" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C115">
-        <v>3125</v>
+        <v>1250</v>
       </c>
       <c r="D115">
-        <v>196.31</v>
+        <v>74.720000000000027</v>
       </c>
       <c r="E115">
-        <v>4.25</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F115">
-        <v>52.941176470588232</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G115">
-        <v>52.941176470588232</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H115" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I115" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B116" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C116">
-        <v>3187.5</v>
+        <v>1312.5</v>
       </c>
       <c r="D116">
-        <v>199.56</v>
+        <v>78.440000000000055</v>
       </c>
       <c r="E116">
-        <v>3.25</v>
+        <v>3.7200000000000268</v>
       </c>
       <c r="F116">
-        <v>69.230769230769226</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="G116">
-        <v>69.230769230769226</v>
+        <v>60.483870967741503</v>
       </c>
       <c r="H116" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I116" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B117" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C117">
-        <v>3250</v>
+        <v>1375</v>
       </c>
       <c r="D117">
-        <v>203.68</v>
+        <v>82.1400000000001</v>
       </c>
       <c r="E117">
-        <v>4.1200000000000054</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F117">
-        <v>54.611650485436833</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G117">
-        <v>54.611650485436833</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H117" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I117" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B118" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C118">
-        <v>3312.5</v>
+        <v>1437.5</v>
       </c>
       <c r="D118">
-        <v>207.93</v>
+        <v>85.840000000000146</v>
       </c>
       <c r="E118">
-        <v>4.25</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F118">
-        <v>55.97</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G118">
-        <v>52.941176470588232</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H118" t="s">
         <v>12</v>
       </c>
       <c r="I118" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B119" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C119">
-        <v>3375</v>
+        <v>1500</v>
       </c>
       <c r="D119">
-        <v>211.68</v>
+        <v>89.680000000000064</v>
       </c>
       <c r="E119">
-        <v>3.75</v>
+        <v>3.8399999999999181</v>
       </c>
       <c r="F119">
-        <v>60</v>
+        <v>60.48</v>
       </c>
       <c r="G119">
-        <v>60</v>
+        <v>58.593750000001251</v>
       </c>
       <c r="H119" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I119" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B120" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C120">
-        <v>3437.5</v>
+        <v>1562.5</v>
       </c>
       <c r="D120">
-        <v>215.43</v>
+        <v>93.380000000000109</v>
       </c>
       <c r="E120">
-        <v>3.75</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F120">
-        <v>60</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G120">
-        <v>60</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H120" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I120" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B121" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C121">
-        <v>3500</v>
+        <v>1625</v>
       </c>
       <c r="D121">
-        <v>219.36</v>
+        <v>97.080000000000155</v>
       </c>
       <c r="E121">
-        <v>3.9300000000000068</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F121">
-        <v>57.251908396946469</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G121">
-        <v>57.251908396946469</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H121" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I121" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B122" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C122">
-        <v>3562.5</v>
+        <v>1687.5</v>
       </c>
       <c r="D122">
-        <v>223.44</v>
+        <v>100.76</v>
       </c>
       <c r="E122">
-        <v>4.0799999999999841</v>
+        <v>3.6799999999998358</v>
       </c>
       <c r="F122">
-        <v>58.44</v>
+        <v>61.141304347828807</v>
       </c>
       <c r="G122">
-        <v>55.147058823529633</v>
+        <v>61.141304347828807</v>
       </c>
       <c r="H122" t="s">
         <v>12</v>
       </c>
       <c r="I122" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B123" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C123">
-        <v>3625</v>
+        <v>1750</v>
       </c>
       <c r="D123">
-        <v>227.68899999999999</v>
+        <v>104.46</v>
       </c>
       <c r="E123">
-        <v>4.2490000000000236</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F123">
-        <v>52.953636149681977</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G123">
-        <v>52.953636149681977</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H123" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I123" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B124" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C124">
-        <v>3687.5</v>
+        <v>1812.5</v>
       </c>
       <c r="D124">
-        <v>231.43899999999999</v>
+        <v>108.1400000000001</v>
       </c>
       <c r="E124">
-        <v>3.75</v>
+        <v>3.6800000000000641</v>
       </c>
       <c r="F124">
-        <v>60</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="G124">
-        <v>60</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="H124" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I124" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B125" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C125">
-        <v>3750</v>
+        <v>1875</v>
       </c>
       <c r="D125">
-        <v>235.93899999999999</v>
+        <v>111.9400000000001</v>
       </c>
       <c r="E125">
-        <v>4.5</v>
+        <v>3.799999999999955</v>
       </c>
       <c r="F125">
-        <v>50</v>
+        <v>61.14</v>
       </c>
       <c r="G125">
-        <v>50</v>
+        <v>59.210526315790183</v>
       </c>
       <c r="H125" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I125" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B126" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C126">
-        <v>3812.5</v>
+        <v>1937.5</v>
       </c>
       <c r="D126">
-        <v>239.52</v>
+        <v>115.6200000000001</v>
       </c>
       <c r="E126">
-        <v>3.5810000000000168</v>
+        <v>3.6800000000000641</v>
       </c>
       <c r="F126">
-        <v>62.831611281764573</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="G126">
-        <v>62.831611281764573</v>
+        <v>61.141304347825027</v>
       </c>
       <c r="H126" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I126" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B127" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C127">
-        <v>3875</v>
+        <v>2000</v>
       </c>
       <c r="D127">
-        <v>243.77</v>
+        <v>119.32000000000021</v>
       </c>
       <c r="E127">
-        <v>4.25</v>
+        <v>3.700000000000045</v>
       </c>
       <c r="F127">
-        <v>52.941176470588232</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="G127">
-        <v>52.941176470588232</v>
+        <v>60.810810810810061</v>
       </c>
       <c r="H127" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I127" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B128" s="2">
-        <v>45119</v>
+        <v>45127</v>
       </c>
       <c r="C128">
-        <v>3937.5</v>
+        <v>2062.5</v>
       </c>
       <c r="D128">
-        <v>247.6</v>
+        <v>123.02</v>
       </c>
       <c r="E128">
-        <v>3.8299999999999841</v>
+        <v>3.6999999999998181</v>
       </c>
       <c r="F128">
-        <v>58.746736292428437</v>
+        <v>60.810810810813798</v>
       </c>
       <c r="G128">
-        <v>58.746736292428437</v>
+        <v>60.810810810813798</v>
       </c>
       <c r="H128" t="s">
+        <v>12</v>
+      </c>
+      <c r="I128" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B129" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C129">
+        <v>2125</v>
+      </c>
+      <c r="D129">
+        <v>126.74</v>
+      </c>
+      <c r="E129">
+        <v>3.7200000000000268</v>
+      </c>
+      <c r="F129">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="G129">
+        <v>60.483870967741503</v>
+      </c>
+      <c r="H129" t="s">
+        <v>12</v>
+      </c>
+      <c r="I129" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>10</v>
+      </c>
+      <c r="B130" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C130">
+        <v>2187.5</v>
+      </c>
+      <c r="D130">
+        <v>130.44000000000011</v>
+      </c>
+      <c r="E130">
+        <v>3.700000000000045</v>
+      </c>
+      <c r="F130">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="G130">
+        <v>60.810810810810061</v>
+      </c>
+      <c r="H130" t="s">
+        <v>12</v>
+      </c>
+      <c r="I130" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>10</v>
+      </c>
+      <c r="B131" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C131">
+        <v>2250</v>
+      </c>
+      <c r="D131">
+        <v>134.24</v>
+      </c>
+      <c r="E131">
+        <v>3.799999999999955</v>
+      </c>
+      <c r="F131">
+        <v>61.14</v>
+      </c>
+      <c r="G131">
+        <v>59.210526315790183</v>
+      </c>
+      <c r="H131" t="s">
+        <v>13</v>
+      </c>
+      <c r="I131" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>10</v>
+      </c>
+      <c r="B132" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C132">
+        <v>2312.5</v>
+      </c>
+      <c r="D132">
+        <v>137.90000000000009</v>
+      </c>
+      <c r="E132">
+        <v>3.6600000000000819</v>
+      </c>
+      <c r="F132">
+        <v>61.475409836064202</v>
+      </c>
+      <c r="G132">
+        <v>61.475409836064202</v>
+      </c>
+      <c r="H132" t="s">
+        <v>12</v>
+      </c>
+      <c r="I132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>10</v>
+      </c>
+      <c r="B133" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C133">
+        <v>2375</v>
+      </c>
+      <c r="D133">
+        <v>141.58000000000021</v>
+      </c>
+      <c r="E133">
+        <v>3.6800000000000641</v>
+      </c>
+      <c r="F133">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="G133">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="H133" t="s">
+        <v>12</v>
+      </c>
+      <c r="I133" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>10</v>
+      </c>
+      <c r="B134" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C134">
+        <v>2437.5</v>
+      </c>
+      <c r="D134">
+        <v>145.28</v>
+      </c>
+      <c r="E134">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F134">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G134">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H134" t="s">
+        <v>12</v>
+      </c>
+      <c r="I134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>10</v>
+      </c>
+      <c r="B135" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C135">
+        <v>2500</v>
+      </c>
+      <c r="D135">
+        <v>148.96</v>
+      </c>
+      <c r="E135">
+        <v>3.6800000000000641</v>
+      </c>
+      <c r="F135">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="G135">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="H135" t="s">
+        <v>12</v>
+      </c>
+      <c r="I135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>10</v>
+      </c>
+      <c r="B136" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C136">
+        <v>2562.5</v>
+      </c>
+      <c r="D136">
+        <v>152.6400000000001</v>
+      </c>
+      <c r="E136">
+        <v>3.6800000000000641</v>
+      </c>
+      <c r="F136">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="G136">
+        <v>61.141304347825027</v>
+      </c>
+      <c r="H136" t="s">
+        <v>12</v>
+      </c>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>10</v>
+      </c>
+      <c r="B137" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C137">
+        <v>2625</v>
+      </c>
+      <c r="D137">
+        <v>156.44000000000011</v>
+      </c>
+      <c r="E137">
+        <v>3.799999999999955</v>
+      </c>
+      <c r="F137">
+        <v>61.14</v>
+      </c>
+      <c r="G137">
+        <v>59.210526315790183</v>
+      </c>
+      <c r="H137" t="s">
+        <v>13</v>
+      </c>
+      <c r="I137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>10</v>
+      </c>
+      <c r="B138" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C138">
+        <v>2687.5</v>
+      </c>
+      <c r="D138">
+        <v>160.10000000000011</v>
+      </c>
+      <c r="E138">
+        <v>3.6600000000000819</v>
+      </c>
+      <c r="F138">
+        <v>61.475409836064202</v>
+      </c>
+      <c r="G138">
+        <v>61.475409836064202</v>
+      </c>
+      <c r="H138" t="s">
+        <v>12</v>
+      </c>
+      <c r="I138" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>10</v>
+      </c>
+      <c r="B139" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C139">
+        <v>2750</v>
+      </c>
+      <c r="D139">
+        <v>163.76</v>
+      </c>
+      <c r="E139">
+        <v>3.659999999999854</v>
+      </c>
+      <c r="F139">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="G139">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="H139" t="s">
+        <v>12</v>
+      </c>
+      <c r="I139" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>10</v>
+      </c>
+      <c r="B140" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C140">
+        <v>2812.5</v>
+      </c>
+      <c r="D140">
+        <v>167.38000000000011</v>
+      </c>
+      <c r="E140">
+        <v>3.6200000000001178</v>
+      </c>
+      <c r="F140">
+        <v>62.154696132594658</v>
+      </c>
+      <c r="G140">
+        <v>62.154696132594658</v>
+      </c>
+      <c r="H140" t="s">
+        <v>12</v>
+      </c>
+      <c r="I140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>10</v>
+      </c>
+      <c r="B141" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C141">
+        <v>2875</v>
+      </c>
+      <c r="D141">
+        <v>171.04</v>
+      </c>
+      <c r="E141">
+        <v>3.659999999999854</v>
+      </c>
+      <c r="F141">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="G141">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="H141" t="s">
+        <v>12</v>
+      </c>
+      <c r="I141" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>10</v>
+      </c>
+      <c r="B142" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C142">
+        <v>2937.5</v>
+      </c>
+      <c r="D142">
+        <v>175.04</v>
+      </c>
+      <c r="E142">
+        <v>4</v>
+      </c>
+      <c r="F142">
+        <v>57.99</v>
+      </c>
+      <c r="G142">
+        <v>56.25</v>
+      </c>
+      <c r="H142" t="s">
+        <v>13</v>
+      </c>
+      <c r="I142" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>11</v>
       </c>
-      <c r="I128" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>23</v>
-      </c>
-      <c r="B129" s="2">
-        <v>45119</v>
-      </c>
-      <c r="C129">
-        <v>4000</v>
-      </c>
-      <c r="D129">
-        <v>252.04</v>
-      </c>
-      <c r="E129">
-        <v>4.4399999999999977</v>
-      </c>
-      <c r="F129">
-        <v>50.675675675675699</v>
-      </c>
-      <c r="G129">
-        <v>50.675675675675699</v>
-      </c>
-      <c r="H129" t="s">
+      <c r="B143" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C143">
+        <v>62.5</v>
+      </c>
+      <c r="D143">
+        <v>3.659999999999854</v>
+      </c>
+      <c r="E143">
+        <v>3.659999999999854</v>
+      </c>
+      <c r="F143">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="G143">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="H143" t="s">
+        <v>12</v>
+      </c>
+      <c r="I143" t="s">
+        <v>17</v>
+      </c>
+      <c r="J143" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
         <v>11</v>
       </c>
-      <c r="I129" t="s">
-        <v>20</v>
-      </c>
+      <c r="B144" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C144">
+        <v>125</v>
+      </c>
+      <c r="D144">
+        <v>7.3800000000001091</v>
+      </c>
+      <c r="E144">
+        <v>3.7200000000002551</v>
+      </c>
+      <c r="F144">
+        <v>60.483870967737793</v>
+      </c>
+      <c r="G144">
+        <v>60.483870967737793</v>
+      </c>
+      <c r="H144" t="s">
+        <v>12</v>
+      </c>
+      <c r="I144" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C145">
+        <v>187.5</v>
+      </c>
+      <c r="D145">
+        <v>11.099999999999911</v>
+      </c>
+      <c r="E145">
+        <v>3.7199999999997999</v>
+      </c>
+      <c r="F145">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="G145">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="H145" t="s">
+        <v>12</v>
+      </c>
+      <c r="I145" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>11</v>
+      </c>
+      <c r="B146" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C146">
+        <v>250</v>
+      </c>
+      <c r="D146">
+        <v>14.880000000000109</v>
+      </c>
+      <c r="E146">
+        <v>3.7800000000002001</v>
+      </c>
+      <c r="F146">
+        <v>59.523809523806371</v>
+      </c>
+      <c r="G146">
+        <v>59.523809523806371</v>
+      </c>
+      <c r="H146" t="s">
+        <v>12</v>
+      </c>
+      <c r="I146" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C147">
+        <v>312.5</v>
+      </c>
+      <c r="D147">
+        <v>18.639999999999869</v>
+      </c>
+      <c r="E147">
+        <v>3.759999999999764</v>
+      </c>
+      <c r="F147">
+        <v>59.840425531918648</v>
+      </c>
+      <c r="G147">
+        <v>59.840425531918648</v>
+      </c>
+      <c r="H147" t="s">
+        <v>12</v>
+      </c>
+      <c r="I147" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>11</v>
+      </c>
+      <c r="B148" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C148">
+        <v>375</v>
+      </c>
+      <c r="D148">
+        <v>22.5</v>
+      </c>
+      <c r="E148">
+        <v>3.8600000000001269</v>
+      </c>
+      <c r="F148">
+        <v>60.16</v>
+      </c>
+      <c r="G148">
+        <v>58.290155440412583</v>
+      </c>
+      <c r="H148" t="s">
+        <v>13</v>
+      </c>
+      <c r="I148" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>11</v>
+      </c>
+      <c r="B149" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C149">
+        <v>437.5</v>
+      </c>
+      <c r="D149">
+        <v>26.24000000000024</v>
+      </c>
+      <c r="E149">
+        <v>3.740000000000236</v>
+      </c>
+      <c r="F149">
+        <v>60.160427807482833</v>
+      </c>
+      <c r="G149">
+        <v>60.160427807482833</v>
+      </c>
+      <c r="H149" t="s">
+        <v>12</v>
+      </c>
+      <c r="I149" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C150">
+        <v>500</v>
+      </c>
+      <c r="D150">
+        <v>29.940000000000051</v>
+      </c>
+      <c r="E150">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F150">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G150">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H150" t="s">
+        <v>12</v>
+      </c>
+      <c r="I150" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>11</v>
+      </c>
+      <c r="B151" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C151">
+        <v>562.5</v>
+      </c>
+      <c r="D151">
+        <v>33.619999999999891</v>
+      </c>
+      <c r="E151">
+        <v>3.6799999999998358</v>
+      </c>
+      <c r="F151">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="G151">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="H151" t="s">
+        <v>12</v>
+      </c>
+      <c r="I151" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>11</v>
+      </c>
+      <c r="B152" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C152">
+        <v>625</v>
+      </c>
+      <c r="D152">
+        <v>37.340000000000153</v>
+      </c>
+      <c r="E152">
+        <v>3.7200000000002551</v>
+      </c>
+      <c r="F152">
+        <v>60.483870967737793</v>
+      </c>
+      <c r="G152">
+        <v>60.483870967737793</v>
+      </c>
+      <c r="H152" t="s">
+        <v>12</v>
+      </c>
+      <c r="I152" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>11</v>
+      </c>
+      <c r="B153" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C153">
+        <v>687.5</v>
+      </c>
+      <c r="D153">
+        <v>41.019999999999982</v>
+      </c>
+      <c r="E153">
+        <v>3.6799999999998358</v>
+      </c>
+      <c r="F153">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="G153">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="H153" t="s">
+        <v>12</v>
+      </c>
+      <c r="I153" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>11</v>
+      </c>
+      <c r="B154" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C154">
+        <v>750</v>
+      </c>
+      <c r="D154">
+        <v>44.820000000000157</v>
+      </c>
+      <c r="E154">
+        <v>3.8000000000001819</v>
+      </c>
+      <c r="F154">
+        <v>61.14</v>
+      </c>
+      <c r="G154">
+        <v>59.210526315786637</v>
+      </c>
+      <c r="H154" t="s">
+        <v>13</v>
+      </c>
+      <c r="I154" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C155">
+        <v>812.5</v>
+      </c>
+      <c r="D155">
+        <v>48.539999999999957</v>
+      </c>
+      <c r="E155">
+        <v>3.7199999999997999</v>
+      </c>
+      <c r="F155">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="G155">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="H155" t="s">
+        <v>12</v>
+      </c>
+      <c r="I155" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>11</v>
+      </c>
+      <c r="B156" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C156">
+        <v>875</v>
+      </c>
+      <c r="D156">
+        <v>52.260000000000218</v>
+      </c>
+      <c r="E156">
+        <v>3.7200000000002551</v>
+      </c>
+      <c r="F156">
+        <v>60.483870967737793</v>
+      </c>
+      <c r="G156">
+        <v>60.483870967737793</v>
+      </c>
+      <c r="H156" t="s">
+        <v>12</v>
+      </c>
+      <c r="I156" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>11</v>
+      </c>
+      <c r="B157" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C157">
+        <v>937.5</v>
+      </c>
+      <c r="D157">
+        <v>55.960000000000043</v>
+      </c>
+      <c r="E157">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F157">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G157">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H157" t="s">
+        <v>12</v>
+      </c>
+      <c r="I157" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>11</v>
+      </c>
+      <c r="B158" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C158">
+        <v>1000</v>
+      </c>
+      <c r="D158">
+        <v>59.659999999999847</v>
+      </c>
+      <c r="E158">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F158">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G158">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H158" t="s">
+        <v>12</v>
+      </c>
+      <c r="I158" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>11</v>
+      </c>
+      <c r="B159" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C159">
+        <v>1062.5</v>
+      </c>
+      <c r="D159">
+        <v>63.360000000000127</v>
+      </c>
+      <c r="E159">
+        <v>3.7000000000002728</v>
+      </c>
+      <c r="F159">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="G159">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="H159" t="s">
+        <v>12</v>
+      </c>
+      <c r="I159" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>11</v>
+      </c>
+      <c r="B160" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C160">
+        <v>1125</v>
+      </c>
+      <c r="D160">
+        <v>67.179999999999836</v>
+      </c>
+      <c r="E160">
+        <v>3.819999999999709</v>
+      </c>
+      <c r="F160">
+        <v>60.81</v>
+      </c>
+      <c r="G160">
+        <v>58.900523560213912</v>
+      </c>
+      <c r="H160" t="s">
+        <v>13</v>
+      </c>
+      <c r="I160" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>11</v>
+      </c>
+      <c r="B161" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C161">
+        <v>1187.5</v>
+      </c>
+      <c r="D161">
+        <v>70.880000000000109</v>
+      </c>
+      <c r="E161">
+        <v>3.7000000000002728</v>
+      </c>
+      <c r="F161">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="G161">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="H161" t="s">
+        <v>12</v>
+      </c>
+      <c r="I161" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>11</v>
+      </c>
+      <c r="B162" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C162">
+        <v>1250</v>
+      </c>
+      <c r="D162">
+        <v>74.579999999999927</v>
+      </c>
+      <c r="E162">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F162">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G162">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H162" t="s">
+        <v>12</v>
+      </c>
+      <c r="I162" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>11</v>
+      </c>
+      <c r="B163" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C163">
+        <v>1312.5</v>
+      </c>
+      <c r="D163">
+        <v>78.2800000000002</v>
+      </c>
+      <c r="E163">
+        <v>3.7000000000002728</v>
+      </c>
+      <c r="F163">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="G163">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="H163" t="s">
+        <v>12</v>
+      </c>
+      <c r="I163" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>11</v>
+      </c>
+      <c r="B164" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C164">
+        <v>1375</v>
+      </c>
+      <c r="D164">
+        <v>81.980000000000018</v>
+      </c>
+      <c r="E164">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F164">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G164">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H164" t="s">
+        <v>12</v>
+      </c>
+      <c r="I164" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>11</v>
+      </c>
+      <c r="B165" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C165">
+        <v>1437.5</v>
+      </c>
+      <c r="D165">
+        <v>85.659999999999854</v>
+      </c>
+      <c r="E165">
+        <v>3.6799999999998358</v>
+      </c>
+      <c r="F165">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="G165">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="H165" t="s">
+        <v>12</v>
+      </c>
+      <c r="I165" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>11</v>
+      </c>
+      <c r="B166" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C166">
+        <v>1500</v>
+      </c>
+      <c r="D166">
+        <v>89.5</v>
+      </c>
+      <c r="E166">
+        <v>3.840000000000146</v>
+      </c>
+      <c r="F166">
+        <v>60.48</v>
+      </c>
+      <c r="G166">
+        <v>58.593749999997783</v>
+      </c>
+      <c r="H166" t="s">
+        <v>13</v>
+      </c>
+      <c r="I166" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>11</v>
+      </c>
+      <c r="B167" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C167">
+        <v>1562.5</v>
+      </c>
+      <c r="D167">
+        <v>93.199999999999818</v>
+      </c>
+      <c r="E167">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F167">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G167">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H167" t="s">
+        <v>12</v>
+      </c>
+      <c r="I167" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>11</v>
+      </c>
+      <c r="B168" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C168">
+        <v>1625</v>
+      </c>
+      <c r="D168">
+        <v>96.900000000000091</v>
+      </c>
+      <c r="E168">
+        <v>3.7000000000002728</v>
+      </c>
+      <c r="F168">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="G168">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="H168" t="s">
+        <v>12</v>
+      </c>
+      <c r="I168" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>11</v>
+      </c>
+      <c r="B169" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C169">
+        <v>1687.5</v>
+      </c>
+      <c r="D169">
+        <v>100.61999999999991</v>
+      </c>
+      <c r="E169">
+        <v>3.7199999999997999</v>
+      </c>
+      <c r="F169">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="G169">
+        <v>60.48387096774519</v>
+      </c>
+      <c r="H169" t="s">
+        <v>12</v>
+      </c>
+      <c r="I169" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>11</v>
+      </c>
+      <c r="B170" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C170">
+        <v>1750</v>
+      </c>
+      <c r="D170">
+        <v>104.32000000000021</v>
+      </c>
+      <c r="E170">
+        <v>3.7000000000002728</v>
+      </c>
+      <c r="F170">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="G170">
+        <v>60.810810810806323</v>
+      </c>
+      <c r="H170" t="s">
+        <v>12</v>
+      </c>
+      <c r="I170" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>11</v>
+      </c>
+      <c r="B171" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C171">
+        <v>1812.5</v>
+      </c>
+      <c r="D171">
+        <v>108.02</v>
+      </c>
+      <c r="E171">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F171">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G171">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H171" t="s">
+        <v>12</v>
+      </c>
+      <c r="I171" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C172">
+        <v>1875</v>
+      </c>
+      <c r="D172">
+        <v>111.82000000000021</v>
+      </c>
+      <c r="E172">
+        <v>3.8000000000001819</v>
+      </c>
+      <c r="F172">
+        <v>61.14</v>
+      </c>
+      <c r="G172">
+        <v>59.210526315786637</v>
+      </c>
+      <c r="H172" t="s">
+        <v>13</v>
+      </c>
+      <c r="I172" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>11</v>
+      </c>
+      <c r="B173" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C173">
+        <v>1937.5</v>
+      </c>
+      <c r="D173">
+        <v>115.46</v>
+      </c>
+      <c r="E173">
+        <v>3.6399999999998731</v>
+      </c>
+      <c r="F173">
+        <v>61.813186813188977</v>
+      </c>
+      <c r="G173">
+        <v>61.813186813188977</v>
+      </c>
+      <c r="H173" t="s">
+        <v>12</v>
+      </c>
+      <c r="I173" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>11</v>
+      </c>
+      <c r="B174" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C174">
+        <v>2000</v>
+      </c>
+      <c r="D174">
+        <v>119.1399999999999</v>
+      </c>
+      <c r="E174">
+        <v>3.6799999999998358</v>
+      </c>
+      <c r="F174">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="G174">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="H174" t="s">
+        <v>12</v>
+      </c>
+      <c r="I174" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>11</v>
+      </c>
+      <c r="B175" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C175">
+        <v>2062.5</v>
+      </c>
+      <c r="D175">
+        <v>122.82000000000021</v>
+      </c>
+      <c r="E175">
+        <v>3.680000000000291</v>
+      </c>
+      <c r="F175">
+        <v>61.141304347821247</v>
+      </c>
+      <c r="G175">
+        <v>61.141304347821247</v>
+      </c>
+      <c r="H175" t="s">
+        <v>12</v>
+      </c>
+      <c r="I175" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>11</v>
+      </c>
+      <c r="B176" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C176">
+        <v>2125</v>
+      </c>
+      <c r="D176">
+        <v>126.48</v>
+      </c>
+      <c r="E176">
+        <v>3.659999999999854</v>
+      </c>
+      <c r="F176">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="G176">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="H176" t="s">
+        <v>12</v>
+      </c>
+      <c r="I176" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>11</v>
+      </c>
+      <c r="B177" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C177">
+        <v>2187.5</v>
+      </c>
+      <c r="D177">
+        <v>130.17999999999981</v>
+      </c>
+      <c r="E177">
+        <v>3.6999999999998181</v>
+      </c>
+      <c r="F177">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="G177">
+        <v>60.810810810813798</v>
+      </c>
+      <c r="H177" t="s">
+        <v>12</v>
+      </c>
+      <c r="I177" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>11</v>
+      </c>
+      <c r="B178" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C178">
+        <v>2250</v>
+      </c>
+      <c r="D178">
+        <v>133.97999999999999</v>
+      </c>
+      <c r="E178">
+        <v>3.8000000000001819</v>
+      </c>
+      <c r="F178">
+        <v>61.14</v>
+      </c>
+      <c r="G178">
+        <v>59.210526315786637</v>
+      </c>
+      <c r="H178" t="s">
+        <v>13</v>
+      </c>
+      <c r="I178" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>11</v>
+      </c>
+      <c r="B179" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C179">
+        <v>2312.5</v>
+      </c>
+      <c r="D179">
+        <v>137.6399999999999</v>
+      </c>
+      <c r="E179">
+        <v>3.659999999999854</v>
+      </c>
+      <c r="F179">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="G179">
+        <v>61.475409836068017</v>
+      </c>
+      <c r="H179" t="s">
+        <v>12</v>
+      </c>
+      <c r="I179" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>11</v>
+      </c>
+      <c r="B180" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C180">
+        <v>2375</v>
+      </c>
+      <c r="D180">
+        <v>141.2800000000002</v>
+      </c>
+      <c r="E180">
+        <v>3.640000000000327</v>
+      </c>
+      <c r="F180">
+        <v>61.813186813181247</v>
+      </c>
+      <c r="G180">
+        <v>61.813186813181247</v>
+      </c>
+      <c r="H180" t="s">
+        <v>12</v>
+      </c>
+      <c r="I180" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>11</v>
+      </c>
+      <c r="B181" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C181">
+        <v>2437.5</v>
+      </c>
+      <c r="D181">
+        <v>144.90000000000009</v>
+      </c>
+      <c r="E181">
+        <v>3.6199999999998909</v>
+      </c>
+      <c r="F181">
+        <v>62.154696132598559</v>
+      </c>
+      <c r="G181">
+        <v>62.154696132598559</v>
+      </c>
+      <c r="H181" t="s">
+        <v>12</v>
+      </c>
+      <c r="I181" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>11</v>
+      </c>
+      <c r="B182" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C182">
+        <v>2500</v>
+      </c>
+      <c r="D182">
+        <v>148.54</v>
+      </c>
+      <c r="E182">
+        <v>3.6399999999998731</v>
+      </c>
+      <c r="F182">
+        <v>61.813186813188977</v>
+      </c>
+      <c r="G182">
+        <v>61.813186813188977</v>
+      </c>
+      <c r="H182" t="s">
+        <v>12</v>
+      </c>
+      <c r="I182" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>11</v>
+      </c>
+      <c r="B183" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C183">
+        <v>2562.5</v>
+      </c>
+      <c r="D183">
+        <v>152.1399999999999</v>
+      </c>
+      <c r="E183">
+        <v>3.5999999999999091</v>
+      </c>
+      <c r="F183">
+        <v>62.500000000001577</v>
+      </c>
+      <c r="G183">
+        <v>62.500000000001577</v>
+      </c>
+      <c r="H183" t="s">
+        <v>12</v>
+      </c>
+      <c r="I183" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>11</v>
+      </c>
+      <c r="B184" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C184">
+        <v>2625</v>
+      </c>
+      <c r="D184">
+        <v>155.8600000000001</v>
+      </c>
+      <c r="E184">
+        <v>3.7200000000002551</v>
+      </c>
+      <c r="F184">
+        <v>62.5</v>
+      </c>
+      <c r="G184">
+        <v>60.483870967737793</v>
+      </c>
+      <c r="H184" t="s">
+        <v>13</v>
+      </c>
+      <c r="I184" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>11</v>
+      </c>
+      <c r="B185" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C185">
+        <v>2687.5</v>
+      </c>
+      <c r="D185">
+        <v>159.46</v>
+      </c>
+      <c r="E185">
+        <v>3.5999999999999091</v>
+      </c>
+      <c r="F185">
+        <v>62.500000000001577</v>
+      </c>
+      <c r="G185">
+        <v>62.500000000001577</v>
+      </c>
+      <c r="H185" t="s">
+        <v>12</v>
+      </c>
+      <c r="I185" t="s">
+        <v>15</v>
+      </c>
+      <c r="K185" t="s">
+        <v>11</v>
+      </c>
+      <c r="L185" s="2">
+        <v>45127</v>
+      </c>
+      <c r="M185">
+        <v>2875</v>
+      </c>
+      <c r="N185">
+        <v>170.44000000000011</v>
+      </c>
+      <c r="O185">
+        <v>3.6799999999998358</v>
+      </c>
+      <c r="P185">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="Q185">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="R185" t="s">
+        <v>12</v>
+      </c>
+      <c r="S185" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>11</v>
+      </c>
+      <c r="B186" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C186">
+        <v>2750</v>
+      </c>
+      <c r="D186">
+        <v>163.09999999999991</v>
+      </c>
+      <c r="E186">
+        <v>3.6399999999998731</v>
+      </c>
+      <c r="F186">
+        <v>61.813186813188977</v>
+      </c>
+      <c r="G186">
+        <v>61.813186813188977</v>
+      </c>
+      <c r="H186" t="s">
+        <v>12</v>
+      </c>
+      <c r="I186" t="s">
+        <v>15</v>
+      </c>
+      <c r="K186" t="s">
+        <v>11</v>
+      </c>
+      <c r="L186" s="2">
+        <v>45127</v>
+      </c>
+      <c r="M186">
+        <v>2937.5</v>
+      </c>
+      <c r="N186">
+        <v>174.3600000000001</v>
+      </c>
+      <c r="O186">
+        <v>3.9200000000000732</v>
+      </c>
+      <c r="P186">
+        <v>59.21</v>
+      </c>
+      <c r="Q186">
+        <v>57.397959183672413</v>
+      </c>
+      <c r="R186" t="s">
+        <v>13</v>
+      </c>
+      <c r="S186" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C187">
+        <v>2812.5</v>
+      </c>
+      <c r="D187">
+        <v>166.76000000000019</v>
+      </c>
+      <c r="E187">
+        <v>3.6600000000003088</v>
+      </c>
+      <c r="F187">
+        <v>61.475409836060379</v>
+      </c>
+      <c r="G187">
+        <v>61.475409836060379</v>
+      </c>
+      <c r="H187" t="s">
+        <v>12</v>
+      </c>
+      <c r="I187" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B188" s="2"/>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B189" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/video_analysis/TP_Master_Men.xlsx
+++ b/pages/video_analysis/TP_Master_Men.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E01290-B010-4C93-8D6A-E84FD4592D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA945E7C-7BA6-4B29-ACB5-90BE95BEA7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="9072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S189"/>
+  <dimension ref="A1:J189"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
@@ -5639,7 +5639,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>11</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>11</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>11</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>11</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>11</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>11</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>11</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>11</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>11</v>
       </c>
@@ -5899,35 +5899,8 @@
       <c r="I185" t="s">
         <v>15</v>
       </c>
-      <c r="K185" t="s">
-        <v>11</v>
-      </c>
-      <c r="L185" s="2">
-        <v>45127</v>
-      </c>
-      <c r="M185">
-        <v>2875</v>
-      </c>
-      <c r="N185">
-        <v>170.44000000000011</v>
-      </c>
-      <c r="O185">
-        <v>3.6799999999998358</v>
-      </c>
-      <c r="P185">
-        <v>61.141304347828807</v>
-      </c>
-      <c r="Q185">
-        <v>61.141304347828807</v>
-      </c>
-      <c r="R185" t="s">
-        <v>12</v>
-      </c>
-      <c r="S185" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>11</v>
       </c>
@@ -5955,35 +5928,8 @@
       <c r="I186" t="s">
         <v>15</v>
       </c>
-      <c r="K186" t="s">
-        <v>11</v>
-      </c>
-      <c r="L186" s="2">
-        <v>45127</v>
-      </c>
-      <c r="M186">
-        <v>2937.5</v>
-      </c>
-      <c r="N186">
-        <v>174.3600000000001</v>
-      </c>
-      <c r="O186">
-        <v>3.9200000000000732</v>
-      </c>
-      <c r="P186">
-        <v>59.21</v>
-      </c>
-      <c r="Q186">
-        <v>57.397959183672413</v>
-      </c>
-      <c r="R186" t="s">
-        <v>13</v>
-      </c>
-      <c r="S186" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>11</v>
       </c>
@@ -6012,11 +5958,63 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B188" s="2"/>
-    </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B189" s="2"/>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>11</v>
+      </c>
+      <c r="B188" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C188">
+        <v>2875</v>
+      </c>
+      <c r="D188">
+        <v>170.44000000000011</v>
+      </c>
+      <c r="E188">
+        <v>3.6799999999998358</v>
+      </c>
+      <c r="F188">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="G188">
+        <v>61.141304347828807</v>
+      </c>
+      <c r="H188" t="s">
+        <v>12</v>
+      </c>
+      <c r="I188" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" s="2">
+        <v>45127</v>
+      </c>
+      <c r="C189">
+        <v>2937.5</v>
+      </c>
+      <c r="D189">
+        <v>174.3600000000001</v>
+      </c>
+      <c r="E189">
+        <v>3.9200000000000732</v>
+      </c>
+      <c r="F189">
+        <v>59.21</v>
+      </c>
+      <c r="G189">
+        <v>57.397959183672413</v>
+      </c>
+      <c r="H189" t="s">
+        <v>13</v>
+      </c>
+      <c r="I189" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/pages/video_analysis/TP_Master_Men.xlsx
+++ b/pages/video_analysis/TP_Master_Men.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA945E7C-7BA6-4B29-ACB5-90BE95BEA7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675F64F7-305B-4680-979B-66FE148C3E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="9072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="34">
   <si>
     <t>Title</t>
   </si>
@@ -52,10 +52,28 @@
     <t>Video</t>
   </si>
   <si>
+    <t>19/7/2023 Flying 3k Rep 1</t>
+  </si>
+  <si>
+    <t>19/7/2023 Flying 3k Rep 2</t>
+  </si>
+  <si>
     <t>19/7/2023 Flying 3k Rep 3</t>
   </si>
   <si>
     <t>19/7/2023 Flying 3k Rep 4</t>
+  </si>
+  <si>
+    <t>20/7/2023 Flying 1 turn Rep 4</t>
+  </si>
+  <si>
+    <t>20/7/2023 Flying 1 turn Rep 1</t>
+  </si>
+  <si>
+    <t>20/7/2023 Flying 1 turn Rep 2</t>
+  </si>
+  <si>
+    <t>20/7/2023 Flying 1 turn Rep 3</t>
   </si>
   <si>
     <t>No Change</t>
@@ -79,13 +97,10 @@
     <t>George Jackson</t>
   </si>
   <si>
-    <t>https://youtu.be/QCPBGRnF4sY</t>
+    <t>Aaron Gate</t>
   </si>
   <si>
-    <t>19/7/2023 Flying 3k Rep 1</t>
-  </si>
-  <si>
-    <t>19/7/2023 Flying 3k Rep 2</t>
+    <t>https://youtu.be/QCPBGRnF4sY</t>
   </si>
   <si>
     <t>https://youtu.be/2irZxikfi88</t>
@@ -95,6 +110,18 @@
   </si>
   <si>
     <t>https://youtu.be/fue24y7g8MI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FT__JcsgjgQ</t>
+  </si>
+  <si>
+    <t>https://youtu.be/aEqbB55uJIw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/5AAaclU8BKY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2TKgV2oDrD0</t>
   </si>
 </sst>
 </file>
@@ -121,10 +148,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,17 +187,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -186,9 +220,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -226,9 +260,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -261,26 +295,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -313,26 +330,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -506,10 +506,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J189"/>
+  <dimension ref="A1:J329"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
@@ -517,7 +517,7 @@
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -554,7 +554,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2">
         <v>45126</v>
@@ -575,18 +575,18 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
         <v>45126</v>
@@ -607,15 +607,15 @@
         <v>60.81081081081193</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
         <v>45126</v>
@@ -636,15 +636,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
         <v>45126</v>
@@ -665,15 +665,15 @@
         <v>59.523809523809952</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
         <v>45126</v>
@@ -694,15 +694,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2">
         <v>45126</v>
@@ -723,15 +723,15 @@
         <v>57.692307692306343</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2">
         <v>45126</v>
@@ -752,15 +752,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2">
         <v>45126</v>
@@ -781,15 +781,15 @@
         <v>59.210526315790183</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2">
         <v>45126</v>
@@ -810,15 +810,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2">
         <v>45126</v>
@@ -839,15 +839,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
         <v>45126</v>
@@ -868,15 +868,15 @@
         <v>59.840420757413213</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2">
         <v>45126</v>
@@ -897,15 +897,15 @@
         <v>57.989690721649552</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2">
         <v>45126</v>
@@ -926,15 +926,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2">
         <v>45126</v>
@@ -955,15 +955,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H15" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2">
         <v>45126</v>
@@ -984,15 +984,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H16" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2">
         <v>45126</v>
@@ -1013,15 +1013,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H17" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2">
         <v>45126</v>
@@ -1042,15 +1042,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B19" s="2">
         <v>45126</v>
@@ -1071,15 +1071,15 @@
         <v>58.290155440416022</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2">
         <v>45126</v>
@@ -1100,15 +1100,15 @@
         <v>57.989690721647847</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2">
         <v>45126</v>
@@ -1129,15 +1129,15 @@
         <v>62.154696132598559</v>
       </c>
       <c r="H21" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B22" s="2">
         <v>45126</v>
@@ -1158,15 +1158,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H22" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B23" s="2">
         <v>45126</v>
@@ -1187,15 +1187,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H23" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B24" s="2">
         <v>45126</v>
@@ -1216,15 +1216,15 @@
         <v>61.475409836064202</v>
       </c>
       <c r="H24" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B25" s="2">
         <v>45126</v>
@@ -1245,15 +1245,15 @@
         <v>57.397959183672413</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B26" s="2">
         <v>45126</v>
@@ -1274,15 +1274,15 @@
         <v>61.475409836068017</v>
       </c>
       <c r="H26" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B27" s="2">
         <v>45126</v>
@@ -1303,15 +1303,15 @@
         <v>61.475409836064202</v>
       </c>
       <c r="H27" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B28" s="2">
         <v>45126</v>
@@ -1332,15 +1332,15 @@
         <v>61.813186813185112</v>
       </c>
       <c r="H28" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B29" s="2">
         <v>45126</v>
@@ -1361,15 +1361,15 @@
         <v>61.813186813188977</v>
       </c>
       <c r="H29" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B30" s="2">
         <v>45126</v>
@@ -1390,15 +1390,15 @@
         <v>62.154696132594658</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B31" s="2">
         <v>45126</v>
@@ -1419,15 +1419,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H31" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B32" s="2">
         <v>45126</v>
@@ -1448,15 +1448,15 @@
         <v>61.813186813188977</v>
       </c>
       <c r="H32" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B33" s="2">
         <v>45126</v>
@@ -1477,15 +1477,15 @@
         <v>61.475409836064202</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B34" s="2">
         <v>45126</v>
@@ -1506,15 +1506,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H34" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B35" s="2">
         <v>45126</v>
@@ -1535,15 +1535,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H35" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B36" s="2">
         <v>45126</v>
@@ -1564,15 +1564,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H36" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B37" s="2">
         <v>45126</v>
@@ -1593,15 +1593,15 @@
         <v>58.593750000001251</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I37" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B38" s="2">
         <v>45126</v>
@@ -1622,15 +1622,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B39" s="2">
         <v>45126</v>
@@ -1651,15 +1651,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H39" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B40" s="2">
         <v>45126</v>
@@ -1680,15 +1680,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H40" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B41" s="2">
         <v>45126</v>
@@ -1709,15 +1709,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H41" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B42" s="2">
         <v>45126</v>
@@ -1738,15 +1738,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H42" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B43" s="2">
         <v>45126</v>
@@ -1767,15 +1767,15 @@
         <v>58.290155440416022</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B44" s="2">
         <v>45126</v>
@@ -1796,15 +1796,15 @@
         <v>58.593749999997783</v>
       </c>
       <c r="H44" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B45" s="2">
         <v>45126</v>
@@ -1825,15 +1825,15 @@
         <v>62.849162011174457</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B46" s="2">
         <v>45126</v>
@@ -1854,15 +1854,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H46" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B47" s="2">
         <v>45126</v>
@@ -1883,15 +1883,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H47" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B48" s="2">
         <v>45126</v>
@@ -1912,15 +1912,15 @@
         <v>56.532663316582664</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B49" s="2">
         <v>45127</v>
@@ -1941,18 +1941,18 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H49" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
-      </c>
-      <c r="J49" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B50" s="2">
         <v>45127</v>
@@ -1973,15 +1973,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H50" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B51" s="2">
         <v>45127</v>
@@ -2002,15 +2002,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H51" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B52" s="2">
         <v>45127</v>
@@ -2031,15 +2031,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H52" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B53" s="2">
         <v>45127</v>
@@ -2060,15 +2060,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H53" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B54" s="2">
         <v>45127</v>
@@ -2089,15 +2089,15 @@
         <v>58.290155440416022</v>
       </c>
       <c r="H54" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I54" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B55" s="2">
         <v>45127</v>
@@ -2118,15 +2118,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H55" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B56" s="2">
         <v>45127</v>
@@ -2147,15 +2147,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H56" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B57" s="2">
         <v>45127</v>
@@ -2176,15 +2176,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H57" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B58" s="2">
         <v>45127</v>
@@ -2205,15 +2205,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H58" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B59" s="2">
         <v>45127</v>
@@ -2234,15 +2234,15 @@
         <v>60.48387096774519</v>
       </c>
       <c r="H59" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B60" s="2">
         <v>45127</v>
@@ -2263,15 +2263,15 @@
         <v>58.900523560206899</v>
       </c>
       <c r="H60" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I60" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B61" s="2">
         <v>45127</v>
@@ -2292,15 +2292,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H61" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B62" s="2">
         <v>45127</v>
@@ -2321,15 +2321,15 @@
         <v>60.48387096774519</v>
       </c>
       <c r="H62" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B63" s="2">
         <v>45127</v>
@@ -2350,15 +2350,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H63" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B64" s="2">
         <v>45127</v>
@@ -2379,15 +2379,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H64" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B65" s="2">
         <v>45127</v>
@@ -2408,15 +2408,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H65" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B66" s="2">
         <v>45127</v>
@@ -2437,15 +2437,15 @@
         <v>58.593749999997783</v>
       </c>
       <c r="H66" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I66" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B67" s="2">
         <v>45127</v>
@@ -2466,15 +2466,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H67" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B68" s="2">
         <v>45127</v>
@@ -2495,15 +2495,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H68" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B69" s="2">
         <v>45127</v>
@@ -2524,15 +2524,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H69" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B70" s="2">
         <v>45127</v>
@@ -2553,15 +2553,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H70" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B71" s="2">
         <v>45127</v>
@@ -2582,15 +2582,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H71" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B72" s="2">
         <v>45127</v>
@@ -2611,15 +2611,15 @@
         <v>59.210526315790183</v>
       </c>
       <c r="H72" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I72" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B73" s="2">
         <v>45127</v>
@@ -2640,15 +2640,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H73" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B74" s="2">
         <v>45127</v>
@@ -2669,15 +2669,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H74" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B75" s="2">
         <v>45127</v>
@@ -2698,15 +2698,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H75" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B76" s="2">
         <v>45127</v>
@@ -2727,15 +2727,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H76" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B77" s="2">
         <v>45127</v>
@@ -2756,15 +2756,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H77" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B78" s="2">
         <v>45127</v>
@@ -2785,15 +2785,15 @@
         <v>59.210526315790183</v>
       </c>
       <c r="H78" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I78" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B79" s="2">
         <v>45127</v>
@@ -2814,15 +2814,15 @@
         <v>61.475409836064202</v>
       </c>
       <c r="H79" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B80" s="2">
         <v>45127</v>
@@ -2843,15 +2843,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H80" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B81" s="2">
         <v>45127</v>
@@ -2872,15 +2872,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H81" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B82" s="2">
         <v>45127</v>
@@ -2901,15 +2901,15 @@
         <v>61.475409836064202</v>
       </c>
       <c r="H82" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B83" s="2">
         <v>45127</v>
@@ -2930,15 +2930,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H83" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I83" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B84" s="2">
         <v>45127</v>
@@ -2959,15 +2959,15 @@
         <v>59.210526315786637</v>
       </c>
       <c r="H84" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I84" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B85" s="2">
         <v>45127</v>
@@ -2988,15 +2988,15 @@
         <v>60.48387096774519</v>
       </c>
       <c r="H85" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B86" s="2">
         <v>45127</v>
@@ -3017,15 +3017,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H86" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B87" s="2">
         <v>45127</v>
@@ -3046,15 +3046,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H87" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B88" s="2">
         <v>45127</v>
@@ -3075,15 +3075,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H88" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B89" s="2">
         <v>45127</v>
@@ -3104,15 +3104,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H89" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B90" s="2">
         <v>45127</v>
@@ -3133,15 +3133,15 @@
         <v>58.593749999997783</v>
       </c>
       <c r="H90" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I90" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B91" s="2">
         <v>45127</v>
@@ -3162,15 +3162,15 @@
         <v>60.48387096774519</v>
       </c>
       <c r="H91" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B92" s="2">
         <v>45127</v>
@@ -3191,15 +3191,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H92" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B93" s="2">
         <v>45127</v>
@@ -3220,15 +3220,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H93" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B94" s="2">
         <v>45127</v>
@@ -3249,15 +3249,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H94" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B95" s="2">
         <v>45127</v>
@@ -3278,15 +3278,15 @@
         <v>56.818181818181287</v>
       </c>
       <c r="H95" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I95" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B96" s="2">
         <v>45127</v>
@@ -3307,18 +3307,18 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H96" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>16</v>
-      </c>
-      <c r="J96" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B97" s="2">
         <v>45127</v>
@@ -3339,15 +3339,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H97" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B98" s="2">
         <v>45127</v>
@@ -3368,15 +3368,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H98" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B99" s="2">
         <v>45127</v>
@@ -3397,15 +3397,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H99" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B100" s="2">
         <v>45127</v>
@@ -3426,15 +3426,15 @@
         <v>61.475409836068017</v>
       </c>
       <c r="H100" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B101" s="2">
         <v>45127</v>
@@ -3455,15 +3455,15 @@
         <v>58.900523560206899</v>
       </c>
       <c r="H101" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I101" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B102" s="2">
         <v>45127</v>
@@ -3484,15 +3484,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H102" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B103" s="2">
         <v>45127</v>
@@ -3513,15 +3513,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H103" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B104" s="2">
         <v>45127</v>
@@ -3542,15 +3542,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H104" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B105" s="2">
         <v>45127</v>
@@ -3571,15 +3571,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H105" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B106" s="2">
         <v>45127</v>
@@ -3600,15 +3600,15 @@
         <v>59.840425531915038</v>
       </c>
       <c r="H106" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B107" s="2">
         <v>45127</v>
@@ -3629,15 +3629,15 @@
         <v>58.900523560210402</v>
       </c>
       <c r="H107" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I107" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B108" s="2">
         <v>45127</v>
@@ -3658,15 +3658,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H108" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B109" s="2">
         <v>45127</v>
@@ -3687,15 +3687,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H109" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B110" s="2">
         <v>45127</v>
@@ -3716,15 +3716,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H110" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B111" s="2">
         <v>45127</v>
@@ -3745,15 +3745,15 @@
         <v>60.160427807486492</v>
       </c>
       <c r="H111" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B112" s="2">
         <v>45127</v>
@@ -3774,15 +3774,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H112" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B113" s="2">
         <v>45127</v>
@@ -3803,15 +3803,15 @@
         <v>58.290155440416022</v>
       </c>
       <c r="H113" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I113" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B114" s="2">
         <v>45127</v>
@@ -3832,15 +3832,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H114" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B115" s="2">
         <v>45127</v>
@@ -3861,15 +3861,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H115" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B116" s="2">
         <v>45127</v>
@@ -3890,15 +3890,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H116" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B117" s="2">
         <v>45127</v>
@@ -3919,15 +3919,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H117" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B118" s="2">
         <v>45127</v>
@@ -3948,15 +3948,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H118" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B119" s="2">
         <v>45127</v>
@@ -3977,15 +3977,15 @@
         <v>58.593750000001251</v>
       </c>
       <c r="H119" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I119" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B120" s="2">
         <v>45127</v>
@@ -4006,15 +4006,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H120" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B121" s="2">
         <v>45127</v>
@@ -4035,15 +4035,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H121" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B122" s="2">
         <v>45127</v>
@@ -4064,15 +4064,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H122" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B123" s="2">
         <v>45127</v>
@@ -4093,15 +4093,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H123" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B124" s="2">
         <v>45127</v>
@@ -4122,15 +4122,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H124" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B125" s="2">
         <v>45127</v>
@@ -4151,15 +4151,15 @@
         <v>59.210526315790183</v>
       </c>
       <c r="H125" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I125" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B126" s="2">
         <v>45127</v>
@@ -4180,15 +4180,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H126" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B127" s="2">
         <v>45127</v>
@@ -4209,15 +4209,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H127" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B128" s="2">
         <v>45127</v>
@@ -4238,15 +4238,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H128" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B129" s="2">
         <v>45127</v>
@@ -4267,15 +4267,15 @@
         <v>60.483870967741503</v>
       </c>
       <c r="H129" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B130" s="2">
         <v>45127</v>
@@ -4296,15 +4296,15 @@
         <v>60.810810810810061</v>
       </c>
       <c r="H130" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B131" s="2">
         <v>45127</v>
@@ -4325,15 +4325,15 @@
         <v>59.210526315790183</v>
       </c>
       <c r="H131" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I131" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B132" s="2">
         <v>45127</v>
@@ -4354,15 +4354,15 @@
         <v>61.475409836064202</v>
       </c>
       <c r="H132" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B133" s="2">
         <v>45127</v>
@@ -4383,15 +4383,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H133" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B134" s="2">
         <v>45127</v>
@@ -4412,15 +4412,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H134" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B135" s="2">
         <v>45127</v>
@@ -4441,15 +4441,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H135" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B136" s="2">
         <v>45127</v>
@@ -4470,15 +4470,15 @@
         <v>61.141304347825027</v>
       </c>
       <c r="H136" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B137" s="2">
         <v>45127</v>
@@ -4499,15 +4499,15 @@
         <v>59.210526315790183</v>
       </c>
       <c r="H137" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I137" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B138" s="2">
         <v>45127</v>
@@ -4528,15 +4528,15 @@
         <v>61.475409836064202</v>
       </c>
       <c r="H138" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B139" s="2">
         <v>45127</v>
@@ -4557,15 +4557,15 @@
         <v>61.475409836068017</v>
       </c>
       <c r="H139" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I139" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B140" s="2">
         <v>45127</v>
@@ -4586,15 +4586,15 @@
         <v>62.154696132594658</v>
       </c>
       <c r="H140" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B141" s="2">
         <v>45127</v>
@@ -4615,15 +4615,15 @@
         <v>61.475409836068017</v>
       </c>
       <c r="H141" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I141" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B142" s="2">
         <v>45127</v>
@@ -4644,15 +4644,15 @@
         <v>56.25</v>
       </c>
       <c r="H142" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I142" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B143" s="2">
         <v>45127</v>
@@ -4673,18 +4673,18 @@
         <v>61.475409836068017</v>
       </c>
       <c r="H143" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>17</v>
-      </c>
-      <c r="J143" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B144" s="2">
         <v>45127</v>
@@ -4705,15 +4705,15 @@
         <v>60.483870967737793</v>
       </c>
       <c r="H144" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B145" s="2">
         <v>45127</v>
@@ -4734,15 +4734,15 @@
         <v>60.48387096774519</v>
       </c>
       <c r="H145" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B146" s="2">
         <v>45127</v>
@@ -4763,15 +4763,15 @@
         <v>59.523809523806371</v>
       </c>
       <c r="H146" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B147" s="2">
         <v>45127</v>
@@ -4792,15 +4792,15 @@
         <v>59.840425531918648</v>
       </c>
       <c r="H147" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B148" s="2">
         <v>45127</v>
@@ -4821,15 +4821,15 @@
         <v>58.290155440412583</v>
       </c>
       <c r="H148" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I148" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B149" s="2">
         <v>45127</v>
@@ -4850,15 +4850,15 @@
         <v>60.160427807482833</v>
       </c>
       <c r="H149" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B150" s="2">
         <v>45127</v>
@@ -4879,15 +4879,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H150" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B151" s="2">
         <v>45127</v>
@@ -4908,15 +4908,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H151" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B152" s="2">
         <v>45127</v>
@@ -4937,15 +4937,15 @@
         <v>60.483870967737793</v>
       </c>
       <c r="H152" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B153" s="2">
         <v>45127</v>
@@ -4966,15 +4966,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H153" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B154" s="2">
         <v>45127</v>
@@ -4995,15 +4995,15 @@
         <v>59.210526315786637</v>
       </c>
       <c r="H154" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I154" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B155" s="2">
         <v>45127</v>
@@ -5024,15 +5024,15 @@
         <v>60.48387096774519</v>
       </c>
       <c r="H155" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B156" s="2">
         <v>45127</v>
@@ -5053,15 +5053,15 @@
         <v>60.483870967737793</v>
       </c>
       <c r="H156" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B157" s="2">
         <v>45127</v>
@@ -5082,15 +5082,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H157" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B158" s="2">
         <v>45127</v>
@@ -5111,15 +5111,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H158" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B159" s="2">
         <v>45127</v>
@@ -5140,15 +5140,15 @@
         <v>60.810810810806323</v>
       </c>
       <c r="H159" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B160" s="2">
         <v>45127</v>
@@ -5169,15 +5169,15 @@
         <v>58.900523560213912</v>
       </c>
       <c r="H160" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I160" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B161" s="2">
         <v>45127</v>
@@ -5198,15 +5198,15 @@
         <v>60.810810810806323</v>
       </c>
       <c r="H161" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I161" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B162" s="2">
         <v>45127</v>
@@ -5227,15 +5227,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H162" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B163" s="2">
         <v>45127</v>
@@ -5256,15 +5256,15 @@
         <v>60.810810810806323</v>
       </c>
       <c r="H163" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B164" s="2">
         <v>45127</v>
@@ -5285,15 +5285,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H164" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B165" s="2">
         <v>45127</v>
@@ -5314,15 +5314,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H165" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B166" s="2">
         <v>45127</v>
@@ -5343,15 +5343,15 @@
         <v>58.593749999997783</v>
       </c>
       <c r="H166" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I166" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B167" s="2">
         <v>45127</v>
@@ -5372,15 +5372,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H167" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I167" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B168" s="2">
         <v>45127</v>
@@ -5401,15 +5401,15 @@
         <v>60.810810810806323</v>
       </c>
       <c r="H168" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B169" s="2">
         <v>45127</v>
@@ -5430,15 +5430,15 @@
         <v>60.48387096774519</v>
       </c>
       <c r="H169" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I169" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B170" s="2">
         <v>45127</v>
@@ -5459,15 +5459,15 @@
         <v>60.810810810806323</v>
       </c>
       <c r="H170" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B171" s="2">
         <v>45127</v>
@@ -5488,15 +5488,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H171" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B172" s="2">
         <v>45127</v>
@@ -5517,15 +5517,15 @@
         <v>59.210526315786637</v>
       </c>
       <c r="H172" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I172" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B173" s="2">
         <v>45127</v>
@@ -5546,15 +5546,15 @@
         <v>61.813186813188977</v>
       </c>
       <c r="H173" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B174" s="2">
         <v>45127</v>
@@ -5575,15 +5575,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H174" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I174" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B175" s="2">
         <v>45127</v>
@@ -5604,15 +5604,15 @@
         <v>61.141304347821247</v>
       </c>
       <c r="H175" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I175" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B176" s="2">
         <v>45127</v>
@@ -5633,15 +5633,15 @@
         <v>61.475409836068017</v>
       </c>
       <c r="H176" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B177" s="2">
         <v>45127</v>
@@ -5662,15 +5662,15 @@
         <v>60.810810810813798</v>
       </c>
       <c r="H177" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I177" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B178" s="2">
         <v>45127</v>
@@ -5691,15 +5691,15 @@
         <v>59.210526315786637</v>
       </c>
       <c r="H178" t="s">
+        <v>19</v>
+      </c>
+      <c r="I178" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
         <v>13</v>
-      </c>
-      <c r="I178" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>11</v>
       </c>
       <c r="B179" s="2">
         <v>45127</v>
@@ -5720,15 +5720,15 @@
         <v>61.475409836068017</v>
       </c>
       <c r="H179" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I179" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B180" s="2">
         <v>45127</v>
@@ -5749,15 +5749,15 @@
         <v>61.813186813181247</v>
       </c>
       <c r="H180" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B181" s="2">
         <v>45127</v>
@@ -5778,15 +5778,15 @@
         <v>62.154696132598559</v>
       </c>
       <c r="H181" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B182" s="2">
         <v>45127</v>
@@ -5807,15 +5807,15 @@
         <v>61.813186813188977</v>
       </c>
       <c r="H182" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I182" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B183" s="2">
         <v>45127</v>
@@ -5836,15 +5836,15 @@
         <v>62.500000000001577</v>
       </c>
       <c r="H183" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B184" s="2">
         <v>45127</v>
@@ -5865,15 +5865,15 @@
         <v>60.483870967737793</v>
       </c>
       <c r="H184" t="s">
+        <v>19</v>
+      </c>
+      <c r="I184" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
         <v>13</v>
-      </c>
-      <c r="I184" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>11</v>
       </c>
       <c r="B185" s="2">
         <v>45127</v>
@@ -5894,15 +5894,15 @@
         <v>62.500000000001577</v>
       </c>
       <c r="H185" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B186" s="2">
         <v>45127</v>
@@ -5923,15 +5923,15 @@
         <v>61.813186813188977</v>
       </c>
       <c r="H186" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I186" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B187" s="2">
         <v>45127</v>
@@ -5952,15 +5952,15 @@
         <v>61.475409836060379</v>
       </c>
       <c r="H187" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I187" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B188" s="2">
         <v>45127</v>
@@ -5981,15 +5981,15 @@
         <v>61.141304347828807</v>
       </c>
       <c r="H188" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I188" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B189" s="2">
         <v>45127</v>
@@ -6010,14 +6010,4091 @@
         <v>57.397959183672413</v>
       </c>
       <c r="H189" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I189" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
         <v>15</v>
       </c>
+      <c r="B190" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C190">
+        <v>62.5</v>
+      </c>
+      <c r="D190">
+        <v>3.340000000000003</v>
+      </c>
+      <c r="E190">
+        <v>3.340000000000003</v>
+      </c>
+      <c r="F190">
+        <v>67.365269461077773</v>
+      </c>
+      <c r="G190">
+        <v>67.365269461077773</v>
+      </c>
+      <c r="H190" t="s">
+        <v>18</v>
+      </c>
+      <c r="I190" t="s">
+        <v>20</v>
+      </c>
+      <c r="J190" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C191">
+        <v>125</v>
+      </c>
+      <c r="D191">
+        <v>6.6800000000000068</v>
+      </c>
+      <c r="E191">
+        <v>3.340000000000003</v>
+      </c>
+      <c r="F191">
+        <v>67.365269461077773</v>
+      </c>
+      <c r="G191">
+        <v>67.365269461077773</v>
+      </c>
+      <c r="H191" t="s">
+        <v>18</v>
+      </c>
+      <c r="I191" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C192">
+        <v>187.5</v>
+      </c>
+      <c r="D192">
+        <v>10.06</v>
+      </c>
+      <c r="E192">
+        <v>3.379999999999995</v>
+      </c>
+      <c r="F192">
+        <v>66.568047337278202</v>
+      </c>
+      <c r="G192">
+        <v>66.568047337278202</v>
+      </c>
+      <c r="H192" t="s">
+        <v>18</v>
+      </c>
+      <c r="I192" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C193">
+        <v>250</v>
+      </c>
+      <c r="D193">
+        <v>13.400000000000009</v>
+      </c>
+      <c r="E193">
+        <v>3.340000000000003</v>
+      </c>
+      <c r="F193">
+        <v>67.365269461077773</v>
+      </c>
+      <c r="G193">
+        <v>67.365269461077773</v>
+      </c>
+      <c r="H193" t="s">
+        <v>18</v>
+      </c>
+      <c r="I193" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C194">
+        <v>312.5</v>
+      </c>
+      <c r="D194">
+        <v>16.800000000000011</v>
+      </c>
+      <c r="E194">
+        <v>3.4000000000000061</v>
+      </c>
+      <c r="F194">
+        <v>66.17647058823519</v>
+      </c>
+      <c r="G194">
+        <v>66.17647058823519</v>
+      </c>
+      <c r="H194" t="s">
+        <v>18</v>
+      </c>
+      <c r="I194" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C195">
+        <v>375</v>
+      </c>
+      <c r="D195">
+        <v>20.199999999999989</v>
+      </c>
+      <c r="E195">
+        <v>3.3999999999999768</v>
+      </c>
+      <c r="F195">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="G195">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="H195" t="s">
+        <v>18</v>
+      </c>
+      <c r="I195" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C196">
+        <v>437.5</v>
+      </c>
+      <c r="D196">
+        <v>23.640000000000011</v>
+      </c>
+      <c r="E196">
+        <v>3.4400000000000261</v>
+      </c>
+      <c r="F196">
+        <v>65.406976744185556</v>
+      </c>
+      <c r="G196">
+        <v>65.406976744185556</v>
+      </c>
+      <c r="H196" t="s">
+        <v>18</v>
+      </c>
+      <c r="I196" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C197">
+        <v>500</v>
+      </c>
+      <c r="D197">
+        <v>27.16</v>
+      </c>
+      <c r="E197">
+        <v>3.5199999999999818</v>
+      </c>
+      <c r="F197">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="G197">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="H197" t="s">
+        <v>18</v>
+      </c>
+      <c r="I197" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C198">
+        <v>562.5</v>
+      </c>
+      <c r="D198">
+        <v>30.78</v>
+      </c>
+      <c r="E198">
+        <v>3.620000000000005</v>
+      </c>
+      <c r="F198">
+        <v>63.56</v>
+      </c>
+      <c r="G198">
+        <v>62.154696132596612</v>
+      </c>
+      <c r="H198" t="s">
+        <v>19</v>
+      </c>
+      <c r="I198" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C199">
+        <v>625</v>
+      </c>
+      <c r="D199">
+        <v>34.340000000000003</v>
+      </c>
+      <c r="E199">
+        <v>3.5600000000000018</v>
+      </c>
+      <c r="F199">
+        <v>63.202247191011203</v>
+      </c>
+      <c r="G199">
+        <v>63.202247191011203</v>
+      </c>
+      <c r="H199" t="s">
+        <v>18</v>
+      </c>
+      <c r="I199" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C200">
+        <v>687.5</v>
+      </c>
+      <c r="D200">
+        <v>37.840000000000003</v>
+      </c>
+      <c r="E200">
+        <v>3.5</v>
+      </c>
+      <c r="F200">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G200">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H200" t="s">
+        <v>18</v>
+      </c>
+      <c r="I200" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C201">
+        <v>750</v>
+      </c>
+      <c r="D201">
+        <v>41.319999999999993</v>
+      </c>
+      <c r="E201">
+        <v>3.4799999999999902</v>
+      </c>
+      <c r="F201">
+        <v>64.655172413793295</v>
+      </c>
+      <c r="G201">
+        <v>64.655172413793295</v>
+      </c>
+      <c r="H201" t="s">
+        <v>18</v>
+      </c>
+      <c r="I201" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>15</v>
+      </c>
+      <c r="B202" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C202">
+        <v>812.5</v>
+      </c>
+      <c r="D202">
+        <v>44.819999999999993</v>
+      </c>
+      <c r="E202">
+        <v>3.5</v>
+      </c>
+      <c r="F202">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G202">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H202" t="s">
+        <v>18</v>
+      </c>
+      <c r="I202" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>15</v>
+      </c>
+      <c r="B203" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C203">
+        <v>875</v>
+      </c>
+      <c r="D203">
+        <v>48.259999999999991</v>
+      </c>
+      <c r="E203">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F203">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G203">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H203" t="s">
+        <v>18</v>
+      </c>
+      <c r="I203" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>15</v>
+      </c>
+      <c r="B204" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C204">
+        <v>937.5</v>
+      </c>
+      <c r="D204">
+        <v>51.740000000000009</v>
+      </c>
+      <c r="E204">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F204">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G204">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H204" t="s">
+        <v>18</v>
+      </c>
+      <c r="I204" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>15</v>
+      </c>
+      <c r="B205" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C205">
+        <v>1000</v>
+      </c>
+      <c r="D205">
+        <v>55.180000000000007</v>
+      </c>
+      <c r="E205">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F205">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G205">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H205" t="s">
+        <v>18</v>
+      </c>
+      <c r="I205" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>15</v>
+      </c>
+      <c r="B206" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C206">
+        <v>1062.5</v>
+      </c>
+      <c r="D206">
+        <v>58.759999999999991</v>
+      </c>
+      <c r="E206">
+        <v>3.5799999999999841</v>
+      </c>
+      <c r="F206">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="G206">
+        <v>62.849162011173462</v>
+      </c>
+      <c r="H206" t="s">
+        <v>19</v>
+      </c>
+      <c r="I206" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>15</v>
+      </c>
+      <c r="B207" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C207">
+        <v>1125</v>
+      </c>
+      <c r="D207">
+        <v>62.199999999999989</v>
+      </c>
+      <c r="E207">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F207">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G207">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H207" t="s">
+        <v>18</v>
+      </c>
+      <c r="I207" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>15</v>
+      </c>
+      <c r="B208" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C208">
+        <v>1187.5</v>
+      </c>
+      <c r="D208">
+        <v>65.66</v>
+      </c>
+      <c r="E208">
+        <v>3.460000000000008</v>
+      </c>
+      <c r="F208">
+        <v>65.028901734103897</v>
+      </c>
+      <c r="G208">
+        <v>65.028901734103897</v>
+      </c>
+      <c r="H208" t="s">
+        <v>18</v>
+      </c>
+      <c r="I208" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>15</v>
+      </c>
+      <c r="B209" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C209">
+        <v>1250</v>
+      </c>
+      <c r="D209">
+        <v>69.12</v>
+      </c>
+      <c r="E209">
+        <v>3.460000000000008</v>
+      </c>
+      <c r="F209">
+        <v>65.028901734103897</v>
+      </c>
+      <c r="G209">
+        <v>65.028901734103897</v>
+      </c>
+      <c r="H209" t="s">
+        <v>18</v>
+      </c>
+      <c r="I209" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>15</v>
+      </c>
+      <c r="B210" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C210">
+        <v>1312.5</v>
+      </c>
+      <c r="D210">
+        <v>72.580000000000013</v>
+      </c>
+      <c r="E210">
+        <v>3.460000000000008</v>
+      </c>
+      <c r="F210">
+        <v>65.028901734103897</v>
+      </c>
+      <c r="G210">
+        <v>65.028901734103897</v>
+      </c>
+      <c r="H210" t="s">
+        <v>18</v>
+      </c>
+      <c r="I210" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>15</v>
+      </c>
+      <c r="B211" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C211">
+        <v>1375</v>
+      </c>
+      <c r="D211">
+        <v>76.019999999999982</v>
+      </c>
+      <c r="E211">
+        <v>3.4399999999999689</v>
+      </c>
+      <c r="F211">
+        <v>65.406976744186636</v>
+      </c>
+      <c r="G211">
+        <v>65.406976744186636</v>
+      </c>
+      <c r="H211" t="s">
+        <v>18</v>
+      </c>
+      <c r="I211" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>15</v>
+      </c>
+      <c r="B212" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C212">
+        <v>1437.5</v>
+      </c>
+      <c r="D212">
+        <v>79.45999999999998</v>
+      </c>
+      <c r="E212">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F212">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G212">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H212" t="s">
+        <v>18</v>
+      </c>
+      <c r="I212" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>15</v>
+      </c>
+      <c r="B213" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C213">
+        <v>1500</v>
+      </c>
+      <c r="D213">
+        <v>82.899999999999977</v>
+      </c>
+      <c r="E213">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F213">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G213">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H213" t="s">
+        <v>18</v>
+      </c>
+      <c r="I213" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>15</v>
+      </c>
+      <c r="B214" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C214">
+        <v>1562.5</v>
+      </c>
+      <c r="D214">
+        <v>86.480000000000018</v>
+      </c>
+      <c r="E214">
+        <v>3.5800000000000409</v>
+      </c>
+      <c r="F214">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="G214">
+        <v>62.849162011172467</v>
+      </c>
+      <c r="H214" t="s">
+        <v>19</v>
+      </c>
+      <c r="I214" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>15</v>
+      </c>
+      <c r="B215" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C215">
+        <v>1625</v>
+      </c>
+      <c r="D215">
+        <v>89.918916599999989</v>
+      </c>
+      <c r="E215">
+        <v>3.43891659999997</v>
+      </c>
+      <c r="F215">
+        <v>65.427582628785458</v>
+      </c>
+      <c r="G215">
+        <v>65.427582628785458</v>
+      </c>
+      <c r="H215" t="s">
+        <v>18</v>
+      </c>
+      <c r="I215" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>15</v>
+      </c>
+      <c r="B216" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C216">
+        <v>1687.5</v>
+      </c>
+      <c r="D216">
+        <v>93.360000000000014</v>
+      </c>
+      <c r="E216">
+        <v>3.441083400000025</v>
+      </c>
+      <c r="F216">
+        <v>65.386383834811554</v>
+      </c>
+      <c r="G216">
+        <v>65.386383834811554</v>
+      </c>
+      <c r="H216" t="s">
+        <v>18</v>
+      </c>
+      <c r="I216" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>15</v>
+      </c>
+      <c r="B217" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C217">
+        <v>1750</v>
+      </c>
+      <c r="D217">
+        <v>96.82</v>
+      </c>
+      <c r="E217">
+        <v>3.45999999999998</v>
+      </c>
+      <c r="F217">
+        <v>65.028901734104437</v>
+      </c>
+      <c r="G217">
+        <v>65.028901734104437</v>
+      </c>
+      <c r="H217" t="s">
+        <v>18</v>
+      </c>
+      <c r="I217" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>15</v>
+      </c>
+      <c r="B218" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C218">
+        <v>1812.5</v>
+      </c>
+      <c r="D218">
+        <v>100.3</v>
+      </c>
+      <c r="E218">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F218">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G218">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H218" t="s">
+        <v>18</v>
+      </c>
+      <c r="I218" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>15</v>
+      </c>
+      <c r="B219" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C219">
+        <v>1875</v>
+      </c>
+      <c r="D219">
+        <v>103.7</v>
+      </c>
+      <c r="E219">
+        <v>3.3999999999999768</v>
+      </c>
+      <c r="F219">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="G219">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="H219" t="s">
+        <v>18</v>
+      </c>
+      <c r="I219" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>15</v>
+      </c>
+      <c r="B220" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C220">
+        <v>1937.5</v>
+      </c>
+      <c r="D220">
+        <v>107.12</v>
+      </c>
+      <c r="E220">
+        <v>3.4200000000000159</v>
+      </c>
+      <c r="F220">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="G220">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="H220" t="s">
+        <v>18</v>
+      </c>
+      <c r="I220" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>15</v>
+      </c>
+      <c r="B221" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C221">
+        <v>2000</v>
+      </c>
+      <c r="D221">
+        <v>110.56</v>
+      </c>
+      <c r="E221">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F221">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G221">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H221" t="s">
+        <v>18</v>
+      </c>
+      <c r="I221" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>15</v>
+      </c>
+      <c r="B222" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C222">
+        <v>2062.5</v>
+      </c>
+      <c r="D222">
+        <v>114</v>
+      </c>
+      <c r="E222">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F222">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G222">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H222" t="s">
+        <v>18</v>
+      </c>
+      <c r="I222" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>15</v>
+      </c>
+      <c r="B223" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C223">
+        <v>2125</v>
+      </c>
+      <c r="D223">
+        <v>117.42</v>
+      </c>
+      <c r="E223">
+        <v>3.4200000000000159</v>
+      </c>
+      <c r="F223">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="G223">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="H223" t="s">
+        <v>18</v>
+      </c>
+      <c r="I223" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>15</v>
+      </c>
+      <c r="B224" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C224">
+        <v>2187.5</v>
+      </c>
+      <c r="D224">
+        <v>120.88</v>
+      </c>
+      <c r="E224">
+        <v>3.45999999999998</v>
+      </c>
+      <c r="F224">
+        <v>65.028901734104437</v>
+      </c>
+      <c r="G224">
+        <v>65.028901734104437</v>
+      </c>
+      <c r="H224" t="s">
+        <v>18</v>
+      </c>
+      <c r="I224" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>15</v>
+      </c>
+      <c r="B225" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C225">
+        <v>2250</v>
+      </c>
+      <c r="D225">
+        <v>124.62</v>
+      </c>
+      <c r="E225">
+        <v>3.7400000000000091</v>
+      </c>
+      <c r="F225">
+        <v>61.48</v>
+      </c>
+      <c r="G225">
+        <v>60.160427807486492</v>
+      </c>
+      <c r="H225" t="s">
+        <v>19</v>
+      </c>
+      <c r="I225" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>16</v>
+      </c>
+      <c r="B226" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C226">
+        <v>62.5</v>
+      </c>
+      <c r="D226">
+        <v>3.54000000000002</v>
+      </c>
+      <c r="E226">
+        <v>3.54000000000002</v>
+      </c>
+      <c r="F226">
+        <v>63.559322033897942</v>
+      </c>
+      <c r="G226">
+        <v>63.559322033897942</v>
+      </c>
+      <c r="H226" t="s">
+        <v>18</v>
+      </c>
+      <c r="I226" t="s">
+        <v>24</v>
+      </c>
+      <c r="J226" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>16</v>
+      </c>
+      <c r="B227" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C227">
+        <v>125</v>
+      </c>
+      <c r="D227">
+        <v>7.0400000000000196</v>
+      </c>
+      <c r="E227">
+        <v>3.5</v>
+      </c>
+      <c r="F227">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G227">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H227" t="s">
+        <v>18</v>
+      </c>
+      <c r="I227" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>16</v>
+      </c>
+      <c r="B228" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C228">
+        <v>187.5</v>
+      </c>
+      <c r="D228">
+        <v>10.52000000000004</v>
+      </c>
+      <c r="E228">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F228">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G228">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H228" t="s">
+        <v>18</v>
+      </c>
+      <c r="I228" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C229">
+        <v>250</v>
+      </c>
+      <c r="D229">
+        <v>14</v>
+      </c>
+      <c r="E229">
+        <v>3.4799999999999609</v>
+      </c>
+      <c r="F229">
+        <v>64.655172413793821</v>
+      </c>
+      <c r="G229">
+        <v>64.655172413793821</v>
+      </c>
+      <c r="H229" t="s">
+        <v>18</v>
+      </c>
+      <c r="I229" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>16</v>
+      </c>
+      <c r="B230" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C230">
+        <v>312.5</v>
+      </c>
+      <c r="D230">
+        <v>17.480000000000022</v>
+      </c>
+      <c r="E230">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F230">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G230">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H230" t="s">
+        <v>18</v>
+      </c>
+      <c r="I230" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>16</v>
+      </c>
+      <c r="B231" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C231">
+        <v>375</v>
+      </c>
+      <c r="D231">
+        <v>20.94</v>
+      </c>
+      <c r="E231">
+        <v>3.45999999999998</v>
+      </c>
+      <c r="F231">
+        <v>65.028901734104437</v>
+      </c>
+      <c r="G231">
+        <v>65.028901734104437</v>
+      </c>
+      <c r="H231" t="s">
+        <v>18</v>
+      </c>
+      <c r="I231" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>16</v>
+      </c>
+      <c r="B232" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C232">
+        <v>437.5</v>
+      </c>
+      <c r="D232">
+        <v>24.38</v>
+      </c>
+      <c r="E232">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F232">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G232">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H232" t="s">
+        <v>18</v>
+      </c>
+      <c r="I232" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>16</v>
+      </c>
+      <c r="B233" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C233">
+        <v>500</v>
+      </c>
+      <c r="D233">
+        <v>27.81999999999999</v>
+      </c>
+      <c r="E233">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F233">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G233">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H233" t="s">
+        <v>18</v>
+      </c>
+      <c r="I233" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>16</v>
+      </c>
+      <c r="B234" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C234">
+        <v>562.5</v>
+      </c>
+      <c r="D234">
+        <v>31.38</v>
+      </c>
+      <c r="E234">
+        <v>3.5600000000000018</v>
+      </c>
+      <c r="F234">
+        <v>65.41</v>
+      </c>
+      <c r="G234">
+        <v>63.202247191011203</v>
+      </c>
+      <c r="H234" t="s">
+        <v>19</v>
+      </c>
+      <c r="I234" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>16</v>
+      </c>
+      <c r="B235" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C235">
+        <v>625</v>
+      </c>
+      <c r="D235">
+        <v>34.819999999999993</v>
+      </c>
+      <c r="E235">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F235">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G235">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H235" t="s">
+        <v>18</v>
+      </c>
+      <c r="I235" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>16</v>
+      </c>
+      <c r="B236" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C236">
+        <v>687.5</v>
+      </c>
+      <c r="D236">
+        <v>38.300000000000011</v>
+      </c>
+      <c r="E236">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F236">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G236">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H236" t="s">
+        <v>18</v>
+      </c>
+      <c r="I236" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>16</v>
+      </c>
+      <c r="B237" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C237">
+        <v>750</v>
+      </c>
+      <c r="D237">
+        <v>41.720000000000027</v>
+      </c>
+      <c r="E237">
+        <v>3.4200000000000159</v>
+      </c>
+      <c r="F237">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="G237">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="H237" t="s">
+        <v>18</v>
+      </c>
+      <c r="I237" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>16</v>
+      </c>
+      <c r="B238" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C238">
+        <v>812.5</v>
+      </c>
+      <c r="D238">
+        <v>45.160000000000032</v>
+      </c>
+      <c r="E238">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F238">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G238">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H238" t="s">
+        <v>18</v>
+      </c>
+      <c r="I238" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>16</v>
+      </c>
+      <c r="B239" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C239">
+        <v>875</v>
+      </c>
+      <c r="D239">
+        <v>48.600000000000023</v>
+      </c>
+      <c r="E239">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F239">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G239">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H239" t="s">
+        <v>18</v>
+      </c>
+      <c r="I239" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>16</v>
+      </c>
+      <c r="B240" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C240">
+        <v>937.5</v>
+      </c>
+      <c r="D240">
+        <v>52</v>
+      </c>
+      <c r="E240">
+        <v>3.3999999999999768</v>
+      </c>
+      <c r="F240">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="G240">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="H240" t="s">
+        <v>18</v>
+      </c>
+      <c r="I240" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>16</v>
+      </c>
+      <c r="B241" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C241">
+        <v>1000</v>
+      </c>
+      <c r="D241">
+        <v>55.44</v>
+      </c>
+      <c r="E241">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F241">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G241">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H241" t="s">
+        <v>18</v>
+      </c>
+      <c r="I241" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>16</v>
+      </c>
+      <c r="B242" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C242">
+        <v>1062.5</v>
+      </c>
+      <c r="D242">
+        <v>58.980000000000018</v>
+      </c>
+      <c r="E242">
+        <v>3.54000000000002</v>
+      </c>
+      <c r="F242">
+        <v>65.790000000000006</v>
+      </c>
+      <c r="G242">
+        <v>63.559322033897942</v>
+      </c>
+      <c r="H242" t="s">
+        <v>19</v>
+      </c>
+      <c r="I242" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>16</v>
+      </c>
+      <c r="B243" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C243">
+        <v>1125</v>
+      </c>
+      <c r="D243">
+        <v>62.400000000000027</v>
+      </c>
+      <c r="E243">
+        <v>3.4200000000000159</v>
+      </c>
+      <c r="F243">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="G243">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="H243" t="s">
+        <v>18</v>
+      </c>
+      <c r="I243" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>16</v>
+      </c>
+      <c r="B244" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C244">
+        <v>1187.5</v>
+      </c>
+      <c r="D244">
+        <v>65.860000000000014</v>
+      </c>
+      <c r="E244">
+        <v>3.45999999999998</v>
+      </c>
+      <c r="F244">
+        <v>65.028901734104437</v>
+      </c>
+      <c r="G244">
+        <v>65.028901734104437</v>
+      </c>
+      <c r="H244" t="s">
+        <v>18</v>
+      </c>
+      <c r="I244" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>16</v>
+      </c>
+      <c r="B245" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C245">
+        <v>1250</v>
+      </c>
+      <c r="D245">
+        <v>69.28000000000003</v>
+      </c>
+      <c r="E245">
+        <v>3.4200000000000159</v>
+      </c>
+      <c r="F245">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="G245">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="H245" t="s">
+        <v>18</v>
+      </c>
+      <c r="I245" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>16</v>
+      </c>
+      <c r="B246" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C246">
+        <v>1312.5</v>
+      </c>
+      <c r="D246">
+        <v>72.699999999999989</v>
+      </c>
+      <c r="E246">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F246">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G246">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H246" t="s">
+        <v>18</v>
+      </c>
+      <c r="I246" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>16</v>
+      </c>
+      <c r="B247" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C247">
+        <v>1375</v>
+      </c>
+      <c r="D247">
+        <v>76.12</v>
+      </c>
+      <c r="E247">
+        <v>3.4200000000000159</v>
+      </c>
+      <c r="F247">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="G247">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="H247" t="s">
+        <v>18</v>
+      </c>
+      <c r="I247" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>16</v>
+      </c>
+      <c r="B248" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C248">
+        <v>1437.5</v>
+      </c>
+      <c r="D248">
+        <v>79.54000000000002</v>
+      </c>
+      <c r="E248">
+        <v>3.4200000000000159</v>
+      </c>
+      <c r="F248">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="G248">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="H248" t="s">
+        <v>18</v>
+      </c>
+      <c r="I248" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>16</v>
+      </c>
+      <c r="B249" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C249">
+        <v>1500</v>
+      </c>
+      <c r="D249">
+        <v>82.960000000000036</v>
+      </c>
+      <c r="E249">
+        <v>3.4200000000000159</v>
+      </c>
+      <c r="F249">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="G249">
+        <v>65.789473684210222</v>
+      </c>
+      <c r="H249" t="s">
+        <v>18</v>
+      </c>
+      <c r="I249" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>16</v>
+      </c>
+      <c r="B250" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C250">
+        <v>1562.5</v>
+      </c>
+      <c r="D250">
+        <v>86.5</v>
+      </c>
+      <c r="E250">
+        <v>3.5399999999999641</v>
+      </c>
+      <c r="F250">
+        <v>65.790000000000006</v>
+      </c>
+      <c r="G250">
+        <v>63.559322033898958</v>
+      </c>
+      <c r="H250" t="s">
+        <v>19</v>
+      </c>
+      <c r="I250" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>16</v>
+      </c>
+      <c r="B251" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C251">
+        <v>1625</v>
+      </c>
+      <c r="D251">
+        <v>89.94</v>
+      </c>
+      <c r="E251">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F251">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G251">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H251" t="s">
+        <v>18</v>
+      </c>
+      <c r="I251" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>16</v>
+      </c>
+      <c r="B252" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C252">
+        <v>1687.5</v>
+      </c>
+      <c r="D252">
+        <v>93.38</v>
+      </c>
+      <c r="E252">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F252">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G252">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H252" t="s">
+        <v>18</v>
+      </c>
+      <c r="I252" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>16</v>
+      </c>
+      <c r="B253" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C253">
+        <v>1750</v>
+      </c>
+      <c r="D253">
+        <v>96.82</v>
+      </c>
+      <c r="E253">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F253">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G253">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H253" t="s">
+        <v>18</v>
+      </c>
+      <c r="I253" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>16</v>
+      </c>
+      <c r="B254" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C254">
+        <v>1812.5</v>
+      </c>
+      <c r="D254">
+        <v>100.3</v>
+      </c>
+      <c r="E254">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F254">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G254">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H254" t="s">
+        <v>18</v>
+      </c>
+      <c r="I254" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>16</v>
+      </c>
+      <c r="B255" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C255">
+        <v>1875</v>
+      </c>
+      <c r="D255">
+        <v>103.7</v>
+      </c>
+      <c r="E255">
+        <v>3.3999999999999768</v>
+      </c>
+      <c r="F255">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="G255">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="H255" t="s">
+        <v>18</v>
+      </c>
+      <c r="I255" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>16</v>
+      </c>
+      <c r="B256" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C256">
+        <v>1937.5</v>
+      </c>
+      <c r="D256">
+        <v>107.14</v>
+      </c>
+      <c r="E256">
+        <v>3.4399999999999982</v>
+      </c>
+      <c r="F256">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="G256">
+        <v>65.406976744186096</v>
+      </c>
+      <c r="H256" t="s">
+        <v>18</v>
+      </c>
+      <c r="I256" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>16</v>
+      </c>
+      <c r="B257" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C257">
+        <v>2000</v>
+      </c>
+      <c r="D257">
+        <v>110.58</v>
+      </c>
+      <c r="E257">
+        <v>3.440000000000055</v>
+      </c>
+      <c r="F257">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="G257">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="H257" t="s">
+        <v>18</v>
+      </c>
+      <c r="I257" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>16</v>
+      </c>
+      <c r="B258" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C258">
+        <v>2062.5</v>
+      </c>
+      <c r="D258">
+        <v>114.0600000000001</v>
+      </c>
+      <c r="E258">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F258">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G258">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H258" t="s">
+        <v>18</v>
+      </c>
+      <c r="I258" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>16</v>
+      </c>
+      <c r="B259" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C259">
+        <v>2125</v>
+      </c>
+      <c r="D259">
+        <v>117.46</v>
+      </c>
+      <c r="E259">
+        <v>3.3999999999999768</v>
+      </c>
+      <c r="F259">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="G259">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="H259" t="s">
+        <v>18</v>
+      </c>
+      <c r="I259" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>16</v>
+      </c>
+      <c r="B260" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C260">
+        <v>2187.5</v>
+      </c>
+      <c r="D260">
+        <v>120.9</v>
+      </c>
+      <c r="E260">
+        <v>3.4399999999999409</v>
+      </c>
+      <c r="F260">
+        <v>65.406976744187176</v>
+      </c>
+      <c r="G260">
+        <v>65.406976744187176</v>
+      </c>
+      <c r="H260" t="s">
+        <v>18</v>
+      </c>
+      <c r="I260" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>16</v>
+      </c>
+      <c r="B261" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C261">
+        <v>2250</v>
+      </c>
+      <c r="D261">
+        <v>124.5600000000001</v>
+      </c>
+      <c r="E261">
+        <v>3.6600000000000819</v>
+      </c>
+      <c r="F261">
+        <v>63.56</v>
+      </c>
+      <c r="G261">
+        <v>61.475409836064202</v>
+      </c>
+      <c r="H261" t="s">
+        <v>19</v>
+      </c>
+      <c r="I261" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>17</v>
+      </c>
+      <c r="B262" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C262">
+        <v>62.5</v>
+      </c>
+      <c r="D262">
+        <v>3.5400000000000769</v>
+      </c>
+      <c r="E262">
+        <v>3.5400000000000769</v>
+      </c>
+      <c r="F262">
+        <v>63.559322033896919</v>
+      </c>
+      <c r="G262">
+        <v>63.559322033896919</v>
+      </c>
+      <c r="H262" t="s">
+        <v>18</v>
+      </c>
+      <c r="I262" t="s">
+        <v>24</v>
+      </c>
+      <c r="J262" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>17</v>
+      </c>
+      <c r="B263" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C263">
+        <v>125</v>
+      </c>
+      <c r="D263">
+        <v>7.0600000000000591</v>
+      </c>
+      <c r="E263">
+        <v>3.5199999999999818</v>
+      </c>
+      <c r="F263">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="G263">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="H263" t="s">
+        <v>18</v>
+      </c>
+      <c r="I263" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>17</v>
+      </c>
+      <c r="B264" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C264">
+        <v>187.5</v>
+      </c>
+      <c r="D264">
+        <v>10.600000000000019</v>
+      </c>
+      <c r="E264">
+        <v>3.5399999999999641</v>
+      </c>
+      <c r="F264">
+        <v>63.559322033898958</v>
+      </c>
+      <c r="G264">
+        <v>63.559322033898958</v>
+      </c>
+      <c r="H264" t="s">
+        <v>18</v>
+      </c>
+      <c r="I264" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>17</v>
+      </c>
+      <c r="B265" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C265">
+        <v>250</v>
+      </c>
+      <c r="D265">
+        <v>14.080000000000039</v>
+      </c>
+      <c r="E265">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F265">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G265">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H265" t="s">
+        <v>18</v>
+      </c>
+      <c r="I265" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>17</v>
+      </c>
+      <c r="B266" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C266">
+        <v>312.5</v>
+      </c>
+      <c r="D266">
+        <v>17.580000000000041</v>
+      </c>
+      <c r="E266">
+        <v>3.5</v>
+      </c>
+      <c r="F266">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G266">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H266" t="s">
+        <v>18</v>
+      </c>
+      <c r="I266" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>17</v>
+      </c>
+      <c r="B267" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C267">
+        <v>375</v>
+      </c>
+      <c r="D267">
+        <v>21.060000000000059</v>
+      </c>
+      <c r="E267">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F267">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G267">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H267" t="s">
+        <v>18</v>
+      </c>
+      <c r="I267" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>17</v>
+      </c>
+      <c r="B268" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C268">
+        <v>437.5</v>
+      </c>
+      <c r="D268">
+        <v>24.540000000000081</v>
+      </c>
+      <c r="E268">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F268">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G268">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H268" t="s">
+        <v>18</v>
+      </c>
+      <c r="I268" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>17</v>
+      </c>
+      <c r="B269" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C269">
+        <v>500</v>
+      </c>
+      <c r="D269">
+        <v>28.040000000000081</v>
+      </c>
+      <c r="E269">
+        <v>3.5</v>
+      </c>
+      <c r="F269">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G269">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H269" t="s">
+        <v>18</v>
+      </c>
+      <c r="I269" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>17</v>
+      </c>
+      <c r="B270" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C270">
+        <v>562.5</v>
+      </c>
+      <c r="D270">
+        <v>31.659999999999972</v>
+      </c>
+      <c r="E270">
+        <v>3.6199999999998909</v>
+      </c>
+      <c r="F270">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="G270">
+        <v>62.154696132598559</v>
+      </c>
+      <c r="H270" t="s">
+        <v>19</v>
+      </c>
+      <c r="I270" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>17</v>
+      </c>
+      <c r="B271" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C271">
+        <v>625</v>
+      </c>
+      <c r="D271">
+        <v>35.200000000000053</v>
+      </c>
+      <c r="E271">
+        <v>3.5400000000000769</v>
+      </c>
+      <c r="F271">
+        <v>63.559322033896919</v>
+      </c>
+      <c r="G271">
+        <v>63.559322033896919</v>
+      </c>
+      <c r="H271" t="s">
+        <v>18</v>
+      </c>
+      <c r="I271" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>17</v>
+      </c>
+      <c r="B272" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C272">
+        <v>687.5</v>
+      </c>
+      <c r="D272">
+        <v>38.680000000000057</v>
+      </c>
+      <c r="E272">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F272">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G272">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H272" t="s">
+        <v>18</v>
+      </c>
+      <c r="I272" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>17</v>
+      </c>
+      <c r="B273" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C273">
+        <v>750</v>
+      </c>
+      <c r="D273">
+        <v>42.159999999999968</v>
+      </c>
+      <c r="E273">
+        <v>3.4799999999999049</v>
+      </c>
+      <c r="F273">
+        <v>64.655172413794872</v>
+      </c>
+      <c r="G273">
+        <v>64.655172413794872</v>
+      </c>
+      <c r="H273" t="s">
+        <v>18</v>
+      </c>
+      <c r="I273" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>17</v>
+      </c>
+      <c r="B274" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C274">
+        <v>812.5</v>
+      </c>
+      <c r="D274">
+        <v>45.659999999999968</v>
+      </c>
+      <c r="E274">
+        <v>3.5</v>
+      </c>
+      <c r="F274">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G274">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H274" t="s">
+        <v>18</v>
+      </c>
+      <c r="I274" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>17</v>
+      </c>
+      <c r="B275" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C275">
+        <v>875</v>
+      </c>
+      <c r="D275">
+        <v>49.139999999999993</v>
+      </c>
+      <c r="E275">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F275">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G275">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H275" t="s">
+        <v>18</v>
+      </c>
+      <c r="I275" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>17</v>
+      </c>
+      <c r="B276" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C276">
+        <v>937.5</v>
+      </c>
+      <c r="D276">
+        <v>52.639999999999993</v>
+      </c>
+      <c r="E276">
+        <v>3.5</v>
+      </c>
+      <c r="F276">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G276">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H276" t="s">
+        <v>18</v>
+      </c>
+      <c r="I276" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>17</v>
+      </c>
+      <c r="B277" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C277">
+        <v>1000</v>
+      </c>
+      <c r="D277">
+        <v>56.080000000000041</v>
+      </c>
+      <c r="E277">
+        <v>3.440000000000055</v>
+      </c>
+      <c r="F277">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="G277">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="H277" t="s">
+        <v>18</v>
+      </c>
+      <c r="I277" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>17</v>
+      </c>
+      <c r="B278" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C278">
+        <v>1062.5</v>
+      </c>
+      <c r="D278">
+        <v>59.700000000000053</v>
+      </c>
+      <c r="E278">
+        <v>3.620000000000005</v>
+      </c>
+      <c r="F278">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="G278">
+        <v>62.154696132596612</v>
+      </c>
+      <c r="H278" t="s">
+        <v>19</v>
+      </c>
+      <c r="I278" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>17</v>
+      </c>
+      <c r="B279" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C279">
+        <v>1125</v>
+      </c>
+      <c r="D279">
+        <v>63.139999999999993</v>
+      </c>
+      <c r="E279">
+        <v>3.4399999999999409</v>
+      </c>
+      <c r="F279">
+        <v>65.406976744187176</v>
+      </c>
+      <c r="G279">
+        <v>65.406976744187176</v>
+      </c>
+      <c r="H279" t="s">
+        <v>18</v>
+      </c>
+      <c r="I279" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>17</v>
+      </c>
+      <c r="B280" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C280">
+        <v>1187.5</v>
+      </c>
+      <c r="D280">
+        <v>66.62</v>
+      </c>
+      <c r="E280">
+        <v>3.4800000000000182</v>
+      </c>
+      <c r="F280">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="G280">
+        <v>64.655172413792769</v>
+      </c>
+      <c r="H280" t="s">
+        <v>18</v>
+      </c>
+      <c r="I280" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>17</v>
+      </c>
+      <c r="B281" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C281">
+        <v>1250</v>
+      </c>
+      <c r="D281">
+        <v>70.060000000000059</v>
+      </c>
+      <c r="E281">
+        <v>3.440000000000055</v>
+      </c>
+      <c r="F281">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="G281">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="H281" t="s">
+        <v>18</v>
+      </c>
+      <c r="I281" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>17</v>
+      </c>
+      <c r="B282" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C282">
+        <v>1312.5</v>
+      </c>
+      <c r="D282">
+        <v>73.480000000000018</v>
+      </c>
+      <c r="E282">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F282">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G282">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H282" t="s">
+        <v>18</v>
+      </c>
+      <c r="I282" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>17</v>
+      </c>
+      <c r="B283" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C283">
+        <v>1375</v>
+      </c>
+      <c r="D283">
+        <v>76.920000000000073</v>
+      </c>
+      <c r="E283">
+        <v>3.440000000000055</v>
+      </c>
+      <c r="F283">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="G283">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="H283" t="s">
+        <v>18</v>
+      </c>
+      <c r="I283" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>17</v>
+      </c>
+      <c r="B284" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C284">
+        <v>1437.5</v>
+      </c>
+      <c r="D284">
+        <v>80.340000000000032</v>
+      </c>
+      <c r="E284">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F284">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G284">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H284" t="s">
+        <v>18</v>
+      </c>
+      <c r="I284" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>17</v>
+      </c>
+      <c r="B285" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C285">
+        <v>1500</v>
+      </c>
+      <c r="D285">
+        <v>83.779999999999973</v>
+      </c>
+      <c r="E285">
+        <v>3.4399999999999409</v>
+      </c>
+      <c r="F285">
+        <v>65.406976744187176</v>
+      </c>
+      <c r="G285">
+        <v>65.406976744187176</v>
+      </c>
+      <c r="H285" t="s">
+        <v>18</v>
+      </c>
+      <c r="I285" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>17</v>
+      </c>
+      <c r="B286" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C286">
+        <v>1562.5</v>
+      </c>
+      <c r="D286">
+        <v>87.360000000000014</v>
+      </c>
+      <c r="E286">
+        <v>3.5800000000000409</v>
+      </c>
+      <c r="F286">
+        <v>65.03</v>
+      </c>
+      <c r="G286">
+        <v>62.849162011172467</v>
+      </c>
+      <c r="H286" t="s">
+        <v>19</v>
+      </c>
+      <c r="I286" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>17</v>
+      </c>
+      <c r="B287" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C287">
+        <v>1625</v>
+      </c>
+      <c r="D287">
+        <v>90.779999999999973</v>
+      </c>
+      <c r="E287">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F287">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G287">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H287" t="s">
+        <v>18</v>
+      </c>
+      <c r="I287" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>17</v>
+      </c>
+      <c r="B288" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C288">
+        <v>1687.5</v>
+      </c>
+      <c r="D288">
+        <v>94.200000000000045</v>
+      </c>
+      <c r="E288">
+        <v>3.4200000000000732</v>
+      </c>
+      <c r="F288">
+        <v>65.789473684209128</v>
+      </c>
+      <c r="G288">
+        <v>65.789473684209128</v>
+      </c>
+      <c r="H288" t="s">
+        <v>18</v>
+      </c>
+      <c r="I288" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>17</v>
+      </c>
+      <c r="B289" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C289">
+        <v>1750</v>
+      </c>
+      <c r="D289">
+        <v>97.62</v>
+      </c>
+      <c r="E289">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F289">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G289">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H289" t="s">
+        <v>18</v>
+      </c>
+      <c r="I289" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>17</v>
+      </c>
+      <c r="B290" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C290">
+        <v>1812.5</v>
+      </c>
+      <c r="D290">
+        <v>101.0600000000001</v>
+      </c>
+      <c r="E290">
+        <v>3.440000000000055</v>
+      </c>
+      <c r="F290">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="G290">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="H290" t="s">
+        <v>18</v>
+      </c>
+      <c r="I290" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>17</v>
+      </c>
+      <c r="B291" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C291">
+        <v>1875</v>
+      </c>
+      <c r="D291">
+        <v>104.4400000000001</v>
+      </c>
+      <c r="E291">
+        <v>3.379999999999995</v>
+      </c>
+      <c r="F291">
+        <v>66.568047337278202</v>
+      </c>
+      <c r="G291">
+        <v>66.568047337278202</v>
+      </c>
+      <c r="H291" t="s">
+        <v>18</v>
+      </c>
+      <c r="I291" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>17</v>
+      </c>
+      <c r="B292" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C292">
+        <v>1937.5</v>
+      </c>
+      <c r="D292">
+        <v>107.86</v>
+      </c>
+      <c r="E292">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F292">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G292">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H292" t="s">
+        <v>18</v>
+      </c>
+      <c r="I292" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>17</v>
+      </c>
+      <c r="B293" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C293">
+        <v>2000</v>
+      </c>
+      <c r="D293">
+        <v>111.76</v>
+      </c>
+      <c r="E293">
+        <v>3.8999999999999768</v>
+      </c>
+      <c r="F293">
+        <v>59.52</v>
+      </c>
+      <c r="G293">
+        <v>57.692307692308027</v>
+      </c>
+      <c r="H293" t="s">
+        <v>19</v>
+      </c>
+      <c r="I293" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>14</v>
+      </c>
+      <c r="B294" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C294">
+        <v>62.5</v>
+      </c>
+      <c r="D294">
+        <v>3.5399999999999641</v>
+      </c>
+      <c r="E294">
+        <v>3.5399999999999641</v>
+      </c>
+      <c r="F294">
+        <v>63.559322033898958</v>
+      </c>
+      <c r="G294">
+        <v>63.559322033898958</v>
+      </c>
+      <c r="H294" t="s">
+        <v>18</v>
+      </c>
+      <c r="I294" t="s">
+        <v>20</v>
+      </c>
+      <c r="J294" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>14</v>
+      </c>
+      <c r="B295" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C295">
+        <v>125</v>
+      </c>
+      <c r="D295">
+        <v>7.0800000000000409</v>
+      </c>
+      <c r="E295">
+        <v>3.5400000000000769</v>
+      </c>
+      <c r="F295">
+        <v>63.559322033896919</v>
+      </c>
+      <c r="G295">
+        <v>63.559322033896919</v>
+      </c>
+      <c r="H295" t="s">
+        <v>18</v>
+      </c>
+      <c r="I295" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>14</v>
+      </c>
+      <c r="B296" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C296">
+        <v>187.5</v>
+      </c>
+      <c r="D296">
+        <v>10.600000000000019</v>
+      </c>
+      <c r="E296">
+        <v>3.5199999999999818</v>
+      </c>
+      <c r="F296">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="G296">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="H296" t="s">
+        <v>18</v>
+      </c>
+      <c r="I296" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>14</v>
+      </c>
+      <c r="B297" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C297">
+        <v>250</v>
+      </c>
+      <c r="D297">
+        <v>14.12</v>
+      </c>
+      <c r="E297">
+        <v>3.5199999999999818</v>
+      </c>
+      <c r="F297">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="G297">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="H297" t="s">
+        <v>18</v>
+      </c>
+      <c r="I297" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>14</v>
+      </c>
+      <c r="B298" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C298">
+        <v>312.5</v>
+      </c>
+      <c r="D298">
+        <v>17.63999999999999</v>
+      </c>
+      <c r="E298">
+        <v>3.5199999999999818</v>
+      </c>
+      <c r="F298">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="G298">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="H298" t="s">
+        <v>18</v>
+      </c>
+      <c r="I298" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>14</v>
+      </c>
+      <c r="B299" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C299">
+        <v>375</v>
+      </c>
+      <c r="D299">
+        <v>21.159999999999972</v>
+      </c>
+      <c r="E299">
+        <v>3.5199999999999818</v>
+      </c>
+      <c r="F299">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="G299">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="H299" t="s">
+        <v>18</v>
+      </c>
+      <c r="I299" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>14</v>
+      </c>
+      <c r="B300" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C300">
+        <v>437.5</v>
+      </c>
+      <c r="D300">
+        <v>24.68000000000006</v>
+      </c>
+      <c r="E300">
+        <v>3.5200000000000951</v>
+      </c>
+      <c r="F300">
+        <v>63.920454545452813</v>
+      </c>
+      <c r="G300">
+        <v>63.920454545452813</v>
+      </c>
+      <c r="H300" t="s">
+        <v>18</v>
+      </c>
+      <c r="I300" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>14</v>
+      </c>
+      <c r="B301" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C301">
+        <v>500</v>
+      </c>
+      <c r="D301">
+        <v>28.18000000000006</v>
+      </c>
+      <c r="E301">
+        <v>3.5</v>
+      </c>
+      <c r="F301">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G301">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H301" t="s">
+        <v>18</v>
+      </c>
+      <c r="I301" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>14</v>
+      </c>
+      <c r="B302" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C302">
+        <v>562.5</v>
+      </c>
+      <c r="D302">
+        <v>31.82000000000005</v>
+      </c>
+      <c r="E302">
+        <v>3.6399999999999859</v>
+      </c>
+      <c r="F302">
+        <v>63.92</v>
+      </c>
+      <c r="G302">
+        <v>61.813186813187038</v>
+      </c>
+      <c r="H302" t="s">
+        <v>19</v>
+      </c>
+      <c r="I302" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A303" t="s">
+        <v>14</v>
+      </c>
+      <c r="B303" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C303">
+        <v>625</v>
+      </c>
+      <c r="D303">
+        <v>35.360000000000007</v>
+      </c>
+      <c r="E303">
+        <v>3.5399999999999641</v>
+      </c>
+      <c r="F303">
+        <v>63.559322033898958</v>
+      </c>
+      <c r="G303">
+        <v>63.559322033898958</v>
+      </c>
+      <c r="H303" t="s">
+        <v>18</v>
+      </c>
+      <c r="I303" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>14</v>
+      </c>
+      <c r="B304" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C304">
+        <v>687.5</v>
+      </c>
+      <c r="D304">
+        <v>38.880000000000003</v>
+      </c>
+      <c r="E304">
+        <v>3.5199999999999818</v>
+      </c>
+      <c r="F304">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="G304">
+        <v>63.920454545454866</v>
+      </c>
+      <c r="H304" t="s">
+        <v>18</v>
+      </c>
+      <c r="I304" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A305" t="s">
+        <v>14</v>
+      </c>
+      <c r="B305" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C305">
+        <v>750</v>
+      </c>
+      <c r="D305">
+        <v>42.38</v>
+      </c>
+      <c r="E305">
+        <v>3.5</v>
+      </c>
+      <c r="F305">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G305">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H305" t="s">
+        <v>18</v>
+      </c>
+      <c r="I305" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A306" t="s">
+        <v>14</v>
+      </c>
+      <c r="B306" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C306">
+        <v>812.5</v>
+      </c>
+      <c r="D306">
+        <v>45.82000000000005</v>
+      </c>
+      <c r="E306">
+        <v>3.440000000000055</v>
+      </c>
+      <c r="F306">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="G306">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="H306" t="s">
+        <v>18</v>
+      </c>
+      <c r="I306" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A307" t="s">
+        <v>14</v>
+      </c>
+      <c r="B307" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C307">
+        <v>875</v>
+      </c>
+      <c r="D307">
+        <v>49.279999999999973</v>
+      </c>
+      <c r="E307">
+        <v>3.4599999999999231</v>
+      </c>
+      <c r="F307">
+        <v>65.028901734105503</v>
+      </c>
+      <c r="G307">
+        <v>65.028901734105503</v>
+      </c>
+      <c r="H307" t="s">
+        <v>18</v>
+      </c>
+      <c r="I307" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A308" t="s">
+        <v>14</v>
+      </c>
+      <c r="B308" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C308">
+        <v>937.5</v>
+      </c>
+      <c r="D308">
+        <v>52.700000000000053</v>
+      </c>
+      <c r="E308">
+        <v>3.4200000000000732</v>
+      </c>
+      <c r="F308">
+        <v>65.789473684209128</v>
+      </c>
+      <c r="G308">
+        <v>65.789473684209128</v>
+      </c>
+      <c r="H308" t="s">
+        <v>18</v>
+      </c>
+      <c r="I308" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A309" t="s">
+        <v>14</v>
+      </c>
+      <c r="B309" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C309">
+        <v>1000</v>
+      </c>
+      <c r="D309">
+        <v>56.12</v>
+      </c>
+      <c r="E309">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F309">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G309">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H309" t="s">
+        <v>18</v>
+      </c>
+      <c r="I309" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A310" t="s">
+        <v>14</v>
+      </c>
+      <c r="B310" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C310">
+        <v>1062.5</v>
+      </c>
+      <c r="D310">
+        <v>59.560000000000059</v>
+      </c>
+      <c r="E310">
+        <v>3.440000000000055</v>
+      </c>
+      <c r="F310">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="G310">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="H310" t="s">
+        <v>18</v>
+      </c>
+      <c r="I310" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A311" t="s">
+        <v>14</v>
+      </c>
+      <c r="B311" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C311">
+        <v>1125</v>
+      </c>
+      <c r="D311">
+        <v>62.980000000000018</v>
+      </c>
+      <c r="E311">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F311">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G311">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H311" t="s">
+        <v>18</v>
+      </c>
+      <c r="I311" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A312" t="s">
+        <v>14</v>
+      </c>
+      <c r="B312" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C312">
+        <v>1187.5</v>
+      </c>
+      <c r="D312">
+        <v>66.519999999999982</v>
+      </c>
+      <c r="E312">
+        <v>3.5399999999999641</v>
+      </c>
+      <c r="F312">
+        <v>65.790000000000006</v>
+      </c>
+      <c r="G312">
+        <v>63.559322033898958</v>
+      </c>
+      <c r="H312" t="s">
+        <v>19</v>
+      </c>
+      <c r="I312" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A313" t="s">
+        <v>14</v>
+      </c>
+      <c r="B313" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C313">
+        <v>1250</v>
+      </c>
+      <c r="D313">
+        <v>69.980000000000018</v>
+      </c>
+      <c r="E313">
+        <v>3.4600000000000359</v>
+      </c>
+      <c r="F313">
+        <v>65.028901734103357</v>
+      </c>
+      <c r="G313">
+        <v>65.028901734103357</v>
+      </c>
+      <c r="H313" t="s">
+        <v>18</v>
+      </c>
+      <c r="I313" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A314" t="s">
+        <v>14</v>
+      </c>
+      <c r="B314" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C314">
+        <v>1312.5</v>
+      </c>
+      <c r="D314">
+        <v>73.440000000000055</v>
+      </c>
+      <c r="E314">
+        <v>3.4600000000000359</v>
+      </c>
+      <c r="F314">
+        <v>65.028901734103357</v>
+      </c>
+      <c r="G314">
+        <v>65.028901734103357</v>
+      </c>
+      <c r="H314" t="s">
+        <v>18</v>
+      </c>
+      <c r="I314" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A315" t="s">
+        <v>14</v>
+      </c>
+      <c r="B315" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C315">
+        <v>1375</v>
+      </c>
+      <c r="D315">
+        <v>76.940000000000055</v>
+      </c>
+      <c r="E315">
+        <v>3.5</v>
+      </c>
+      <c r="F315">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G315">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H315" t="s">
+        <v>18</v>
+      </c>
+      <c r="I315" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A316" t="s">
+        <v>14</v>
+      </c>
+      <c r="B316" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C316">
+        <v>1437.5</v>
+      </c>
+      <c r="D316">
+        <v>80.560000000000059</v>
+      </c>
+      <c r="E316">
+        <v>3.620000000000005</v>
+      </c>
+      <c r="F316">
+        <v>64.290000000000006</v>
+      </c>
+      <c r="G316">
+        <v>62.154696132596612</v>
+      </c>
+      <c r="H316" t="s">
+        <v>19</v>
+      </c>
+      <c r="I316" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A317" t="s">
+        <v>14</v>
+      </c>
+      <c r="B317" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C317">
+        <v>1500</v>
+      </c>
+      <c r="D317">
+        <v>84.060000000000059</v>
+      </c>
+      <c r="E317">
+        <v>3.5</v>
+      </c>
+      <c r="F317">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="G317">
+        <v>64.285714285714292</v>
+      </c>
+      <c r="H317" t="s">
+        <v>18</v>
+      </c>
+      <c r="I317" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A318" t="s">
+        <v>14</v>
+      </c>
+      <c r="B318" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C318">
+        <v>1562.5</v>
+      </c>
+      <c r="D318">
+        <v>87.519999999999982</v>
+      </c>
+      <c r="E318">
+        <v>3.4599999999999231</v>
+      </c>
+      <c r="F318">
+        <v>65.028901734105503</v>
+      </c>
+      <c r="G318">
+        <v>65.028901734105503</v>
+      </c>
+      <c r="H318" t="s">
+        <v>18</v>
+      </c>
+      <c r="I318" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A319" t="s">
+        <v>14</v>
+      </c>
+      <c r="B319" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C319">
+        <v>1625</v>
+      </c>
+      <c r="D319">
+        <v>90.980000000000018</v>
+      </c>
+      <c r="E319">
+        <v>3.4600000000000359</v>
+      </c>
+      <c r="F319">
+        <v>65.028901734103357</v>
+      </c>
+      <c r="G319">
+        <v>65.028901734103357</v>
+      </c>
+      <c r="H319" t="s">
+        <v>18</v>
+      </c>
+      <c r="I319" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A320" t="s">
+        <v>14</v>
+      </c>
+      <c r="B320" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C320">
+        <v>1687.5</v>
+      </c>
+      <c r="D320">
+        <v>94.399999999999977</v>
+      </c>
+      <c r="E320">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F320">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G320">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H320" t="s">
+        <v>18</v>
+      </c>
+      <c r="I320" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A321" t="s">
+        <v>14</v>
+      </c>
+      <c r="B321" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C321">
+        <v>1750</v>
+      </c>
+      <c r="D321">
+        <v>97.82000000000005</v>
+      </c>
+      <c r="E321">
+        <v>3.4200000000000732</v>
+      </c>
+      <c r="F321">
+        <v>65.789473684209128</v>
+      </c>
+      <c r="G321">
+        <v>65.789473684209128</v>
+      </c>
+      <c r="H321" t="s">
+        <v>18</v>
+      </c>
+      <c r="I321" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A322" t="s">
+        <v>14</v>
+      </c>
+      <c r="B322" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C322">
+        <v>1812.5</v>
+      </c>
+      <c r="D322">
+        <v>101.26</v>
+      </c>
+      <c r="E322">
+        <v>3.4399999999999409</v>
+      </c>
+      <c r="F322">
+        <v>65.406976744187176</v>
+      </c>
+      <c r="G322">
+        <v>65.406976744187176</v>
+      </c>
+      <c r="H322" t="s">
+        <v>18</v>
+      </c>
+      <c r="I322" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A323" t="s">
+        <v>14</v>
+      </c>
+      <c r="B323" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C323">
+        <v>1875</v>
+      </c>
+      <c r="D323">
+        <v>104.68000000000011</v>
+      </c>
+      <c r="E323">
+        <v>3.4200000000000732</v>
+      </c>
+      <c r="F323">
+        <v>65.789473684209128</v>
+      </c>
+      <c r="G323">
+        <v>65.789473684209128</v>
+      </c>
+      <c r="H323" t="s">
+        <v>18</v>
+      </c>
+      <c r="I323" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A324" t="s">
+        <v>14</v>
+      </c>
+      <c r="B324" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C324">
+        <v>1937.5</v>
+      </c>
+      <c r="D324">
+        <v>108.08</v>
+      </c>
+      <c r="E324">
+        <v>3.3999999999999768</v>
+      </c>
+      <c r="F324">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="G324">
+        <v>66.17647058823573</v>
+      </c>
+      <c r="H324" t="s">
+        <v>18</v>
+      </c>
+      <c r="I324" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A325" t="s">
+        <v>14</v>
+      </c>
+      <c r="B325" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C325">
+        <v>2000</v>
+      </c>
+      <c r="D325">
+        <v>111.4400000000001</v>
+      </c>
+      <c r="E325">
+        <v>3.3600000000000141</v>
+      </c>
+      <c r="F325">
+        <v>66.964285714285438</v>
+      </c>
+      <c r="G325">
+        <v>66.964285714285438</v>
+      </c>
+      <c r="H325" t="s">
+        <v>18</v>
+      </c>
+      <c r="I325" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A326" t="s">
+        <v>14</v>
+      </c>
+      <c r="B326" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C326">
+        <v>2062.5</v>
+      </c>
+      <c r="D326">
+        <v>114.86</v>
+      </c>
+      <c r="E326">
+        <v>3.4199999999999591</v>
+      </c>
+      <c r="F326">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="G326">
+        <v>65.789473684211316</v>
+      </c>
+      <c r="H326" t="s">
+        <v>18</v>
+      </c>
+      <c r="I326" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A327" t="s">
+        <v>14</v>
+      </c>
+      <c r="B327" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C327">
+        <v>2125</v>
+      </c>
+      <c r="D327">
+        <v>118.24</v>
+      </c>
+      <c r="E327">
+        <v>3.379999999999995</v>
+      </c>
+      <c r="F327">
+        <v>66.568047337278202</v>
+      </c>
+      <c r="G327">
+        <v>66.568047337278202</v>
+      </c>
+      <c r="H327" t="s">
+        <v>18</v>
+      </c>
+      <c r="I327" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>14</v>
+      </c>
+      <c r="B328" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C328">
+        <v>2187.5</v>
+      </c>
+      <c r="D328">
+        <v>121.68000000000011</v>
+      </c>
+      <c r="E328">
+        <v>3.440000000000055</v>
+      </c>
+      <c r="F328">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="G328">
+        <v>65.406976744185002</v>
+      </c>
+      <c r="H328" t="s">
+        <v>18</v>
+      </c>
+      <c r="I328" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>14</v>
+      </c>
+      <c r="B329" s="2">
+        <v>45128</v>
+      </c>
+      <c r="C329">
+        <v>2250</v>
+      </c>
+      <c r="D329">
+        <v>125.36</v>
+      </c>
+      <c r="E329">
+        <v>3.67999999999995</v>
+      </c>
+      <c r="F329">
+        <v>63.2</v>
+      </c>
+      <c r="G329">
+        <v>61.141304347826917</v>
+      </c>
+      <c r="H329" t="s">
+        <v>19</v>
+      </c>
+      <c r="I329" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="J49" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="J96" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="J143" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/video_analysis/TP_Master_Men.xlsx
+++ b/pages/video_analysis/TP_Master_Men.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F76D4A4-1AF8-4850-8949-431DF9173D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72707CBA-59D6-4570-A1BF-01D3BB570B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19395" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89833,7 +89833,7 @@
         <v>59.523809523809497</v>
       </c>
       <c r="H2405" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I2405" t="s">
         <v>67</v>
@@ -89865,7 +89865,7 @@
         <v>60</v>
       </c>
       <c r="I2406" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2407" spans="1:9" x14ac:dyDescent="0.45">
@@ -89894,7 +89894,7 @@
         <v>60</v>
       </c>
       <c r="I2407" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2408" spans="1:9" x14ac:dyDescent="0.45">
@@ -89923,7 +89923,7 @@
         <v>60</v>
       </c>
       <c r="I2408" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2409" spans="1:9" x14ac:dyDescent="0.45">
@@ -89952,7 +89952,7 @@
         <v>61</v>
       </c>
       <c r="I2409" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2410" spans="1:9" x14ac:dyDescent="0.45">
@@ -89981,7 +89981,7 @@
         <v>60</v>
       </c>
       <c r="I2410" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2411" spans="1:9" x14ac:dyDescent="0.45">
@@ -90010,7 +90010,7 @@
         <v>60</v>
       </c>
       <c r="I2411" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2412" spans="1:9" x14ac:dyDescent="0.45">
@@ -90039,7 +90039,7 @@
         <v>60</v>
       </c>
       <c r="I2412" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2413" spans="1:9" x14ac:dyDescent="0.45">
@@ -90068,7 +90068,7 @@
         <v>60</v>
       </c>
       <c r="I2413" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2414" spans="1:9" x14ac:dyDescent="0.45">
@@ -90097,7 +90097,7 @@
         <v>60</v>
       </c>
       <c r="I2414" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2415" spans="1:9" x14ac:dyDescent="0.45">
@@ -90126,7 +90126,7 @@
         <v>60</v>
       </c>
       <c r="I2415" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2416" spans="1:9" x14ac:dyDescent="0.45">
@@ -90155,7 +90155,7 @@
         <v>60</v>
       </c>
       <c r="I2416" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2417" spans="1:13" x14ac:dyDescent="0.45">
@@ -90184,7 +90184,7 @@
         <v>60</v>
       </c>
       <c r="I2417" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2418" spans="1:13" x14ac:dyDescent="0.45">
@@ -90213,7 +90213,7 @@
         <v>60</v>
       </c>
       <c r="I2418" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2419" spans="1:13" x14ac:dyDescent="0.45">
@@ -90242,7 +90242,7 @@
         <v>60</v>
       </c>
       <c r="I2419" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2420" spans="1:13" x14ac:dyDescent="0.45">
@@ -90271,7 +90271,7 @@
         <v>60</v>
       </c>
       <c r="I2420" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2421" spans="1:13" x14ac:dyDescent="0.45">
@@ -90300,7 +90300,7 @@
         <v>60</v>
       </c>
       <c r="I2421" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2422" spans="1:13" x14ac:dyDescent="0.45">
@@ -90329,7 +90329,7 @@
         <v>60</v>
       </c>
       <c r="I2422" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2423" spans="1:13" x14ac:dyDescent="0.45">
@@ -90358,7 +90358,7 @@
         <v>61</v>
       </c>
       <c r="I2423" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2424" spans="1:13" x14ac:dyDescent="0.45">
@@ -90387,7 +90387,7 @@
         <v>60</v>
       </c>
       <c r="I2424" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2425" spans="1:13" x14ac:dyDescent="0.45">
@@ -90416,7 +90416,7 @@
         <v>60</v>
       </c>
       <c r="I2425" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2426" spans="1:13" x14ac:dyDescent="0.45">
@@ -90445,7 +90445,7 @@
         <v>60</v>
       </c>
       <c r="I2426" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2427" spans="1:13" x14ac:dyDescent="0.45">
@@ -90474,7 +90474,7 @@
         <v>60</v>
       </c>
       <c r="I2427" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2428" spans="1:13" x14ac:dyDescent="0.45">
@@ -90503,7 +90503,7 @@
         <v>61</v>
       </c>
       <c r="I2428" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2429" spans="1:13" x14ac:dyDescent="0.45">
